--- a/hall/resources/sample/EmployeeStar.xlsx
+++ b/hall/resources/sample/EmployeeStar.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Map&lt;int{_}int&gt;{|}</t>
+  </si>
+  <si>
+    <t>id</t>
   </si>
   <si>
     <t>EmployeeID</t>
@@ -1320,22 +1323,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1364,7 +1367,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1516,7 +1519,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1740,7 +1743,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1947,7 +1950,7 @@
         <v>4</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2154,7 +2157,7 @@
         <v>6</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2471,7 +2474,7 @@
         <v>10</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2678,7 +2681,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:6">

--- a/hall/resources/sample/EmployeeStar.xlsx
+++ b/hall/resources/sample/EmployeeStar.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -72,6 +72,18 @@
   </si>
   <si>
     <t>3_200</t>
+  </si>
+  <si>
+    <t>1_100</t>
+  </si>
+  <si>
+    <t>2_300</t>
+  </si>
+  <si>
+    <t>4_400</t>
+  </si>
+  <si>
+    <t>5_600</t>
   </si>
 </sst>
 </file>
@@ -708,7 +720,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -740,9 +752,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1387,7 +1396,9 @@
       <c r="E6" s="6">
         <v>4</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F6" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3">
@@ -1406,7 +1417,9 @@
       <c r="E7" s="6">
         <v>6</v>
       </c>
-      <c r="F7" s="7"/>
+      <c r="F7" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3">
@@ -1425,7 +1438,9 @@
       <c r="E8" s="6">
         <v>8</v>
       </c>
-      <c r="F8" s="7"/>
+      <c r="F8" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3">
@@ -1442,7 +1457,9 @@
       <c r="E9" s="6">
         <v>10</v>
       </c>
-      <c r="F9" s="7"/>
+      <c r="F9" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3">
@@ -1461,7 +1478,9 @@
       <c r="E10" s="10">
         <v>2</v>
       </c>
-      <c r="F10" s="11"/>
+      <c r="F10" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3">
@@ -1480,7 +1499,9 @@
       <c r="E11" s="10">
         <v>4</v>
       </c>
-      <c r="F11" s="11"/>
+      <c r="F11" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3">
@@ -1499,7 +1520,9 @@
       <c r="E12" s="10">
         <v>6</v>
       </c>
-      <c r="F12" s="11"/>
+      <c r="F12" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3">
@@ -1519,7 +1542,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1537,7 +1560,9 @@
       <c r="E14" s="10">
         <v>10</v>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3">
@@ -1556,7 +1581,9 @@
       <c r="E15" s="10">
         <v>2</v>
       </c>
-      <c r="F15" s="11"/>
+      <c r="F15" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3">
@@ -1575,7 +1602,9 @@
       <c r="E16" s="10">
         <v>4</v>
       </c>
-      <c r="F16" s="11"/>
+      <c r="F16" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3">
@@ -1594,7 +1623,9 @@
       <c r="E17" s="10">
         <v>6</v>
       </c>
-      <c r="F17" s="11"/>
+      <c r="F17" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3">
@@ -1613,7 +1644,9 @@
       <c r="E18" s="10">
         <v>8</v>
       </c>
-      <c r="F18" s="11"/>
+      <c r="F18" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3">
@@ -1630,7 +1663,9 @@
       <c r="E19" s="10">
         <v>10</v>
       </c>
-      <c r="F19" s="11"/>
+      <c r="F19" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3">
@@ -1649,7 +1684,9 @@
       <c r="E20" s="10">
         <v>2</v>
       </c>
-      <c r="F20" s="11"/>
+      <c r="F20" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3">
@@ -1668,7 +1705,9 @@
       <c r="E21" s="10">
         <v>4</v>
       </c>
-      <c r="F21" s="11"/>
+      <c r="F21" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3">
@@ -1687,7 +1726,9 @@
       <c r="E22" s="10">
         <v>6</v>
       </c>
-      <c r="F22" s="11"/>
+      <c r="F22" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3">
@@ -1706,7 +1747,9 @@
       <c r="E23" s="10">
         <v>8</v>
       </c>
-      <c r="F23" s="11"/>
+      <c r="F23" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3">
@@ -1723,7 +1766,9 @@
       <c r="E24" s="10">
         <v>10</v>
       </c>
-      <c r="F24" s="11"/>
+      <c r="F24" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3">
@@ -1763,7 +1808,9 @@
       <c r="E26" s="10">
         <v>4</v>
       </c>
-      <c r="F26" s="11"/>
+      <c r="F26" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3">
@@ -1782,7 +1829,9 @@
       <c r="E27" s="10">
         <v>6</v>
       </c>
-      <c r="F27" s="11"/>
+      <c r="F27" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3">
@@ -1801,7 +1850,9 @@
       <c r="E28" s="10">
         <v>8</v>
       </c>
-      <c r="F28" s="11"/>
+      <c r="F28" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3">
@@ -1818,7 +1869,9 @@
       <c r="E29" s="10">
         <v>10</v>
       </c>
-      <c r="F29" s="11"/>
+      <c r="F29" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="3">
@@ -1837,7 +1890,9 @@
       <c r="E30" s="10">
         <v>2</v>
       </c>
-      <c r="F30" s="11"/>
+      <c r="F30" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="3">
@@ -1856,7 +1911,9 @@
       <c r="E31" s="10">
         <v>4</v>
       </c>
-      <c r="F31" s="11"/>
+      <c r="F31" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="3">
@@ -1875,7 +1932,9 @@
       <c r="E32" s="10">
         <v>6</v>
       </c>
-      <c r="F32" s="11"/>
+      <c r="F32" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="3">
@@ -1894,7 +1953,9 @@
       <c r="E33" s="10">
         <v>8</v>
       </c>
-      <c r="F33" s="11"/>
+      <c r="F33" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="3">
@@ -1911,7 +1972,9 @@
       <c r="E34" s="10">
         <v>10</v>
       </c>
-      <c r="F34" s="11"/>
+      <c r="F34" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3">
@@ -1930,7 +1993,9 @@
       <c r="E35" s="10">
         <v>2</v>
       </c>
-      <c r="F35" s="11"/>
+      <c r="F35" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3">
@@ -1950,7 +2015,7 @@
         <v>4</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1970,7 +2035,9 @@
       <c r="E37" s="10">
         <v>6</v>
       </c>
-      <c r="F37" s="11"/>
+      <c r="F37" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="3">
@@ -1989,7 +2056,9 @@
       <c r="E38" s="10">
         <v>8</v>
       </c>
-      <c r="F38" s="11"/>
+      <c r="F38" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="3">
@@ -2006,7 +2075,9 @@
       <c r="E39" s="10">
         <v>10</v>
       </c>
-      <c r="F39" s="11"/>
+      <c r="F39" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="3">
@@ -2025,7 +2096,9 @@
       <c r="E40" s="10">
         <v>2</v>
       </c>
-      <c r="F40" s="11"/>
+      <c r="F40" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="3">
@@ -2044,7 +2117,9 @@
       <c r="E41" s="10">
         <v>4</v>
       </c>
-      <c r="F41" s="11"/>
+      <c r="F41" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3">
@@ -2063,7 +2138,9 @@
       <c r="E42" s="10">
         <v>6</v>
       </c>
-      <c r="F42" s="11"/>
+      <c r="F42" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3">
@@ -2082,7 +2159,9 @@
       <c r="E43" s="10">
         <v>8</v>
       </c>
-      <c r="F43" s="11"/>
+      <c r="F43" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3">
@@ -2099,7 +2178,9 @@
       <c r="E44" s="10">
         <v>10</v>
       </c>
-      <c r="F44" s="11"/>
+      <c r="F44" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="3">
@@ -2118,7 +2199,9 @@
       <c r="E45" s="10">
         <v>2</v>
       </c>
-      <c r="F45" s="11"/>
+      <c r="F45" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3">
@@ -2137,7 +2220,9 @@
       <c r="E46" s="10">
         <v>4</v>
       </c>
-      <c r="F46" s="11"/>
+      <c r="F46" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3">
@@ -2157,7 +2242,7 @@
         <v>6</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2177,7 +2262,9 @@
       <c r="E48" s="10">
         <v>8</v>
       </c>
-      <c r="F48" s="11"/>
+      <c r="F48" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="3">
@@ -2194,7 +2281,9 @@
       <c r="E49" s="10">
         <v>10</v>
       </c>
-      <c r="F49" s="11"/>
+      <c r="F49" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="3">
@@ -2213,7 +2302,9 @@
       <c r="E50" s="10">
         <v>2</v>
       </c>
-      <c r="F50" s="11"/>
+      <c r="F50" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="3">
@@ -2232,7 +2323,9 @@
       <c r="E51" s="10">
         <v>4</v>
       </c>
-      <c r="F51" s="11"/>
+      <c r="F51" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3">
@@ -2251,7 +2344,9 @@
       <c r="E52" s="10">
         <v>6</v>
       </c>
-      <c r="F52" s="11"/>
+      <c r="F52" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="3">
@@ -2270,7 +2365,9 @@
       <c r="E53" s="10">
         <v>8</v>
       </c>
-      <c r="F53" s="11"/>
+      <c r="F53" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="3">
@@ -2287,7 +2384,9 @@
       <c r="E54" s="10">
         <v>10</v>
       </c>
-      <c r="F54" s="11"/>
+      <c r="F54" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3">
@@ -2306,7 +2405,9 @@
       <c r="E55" s="10">
         <v>2</v>
       </c>
-      <c r="F55" s="11"/>
+      <c r="F55" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3">
@@ -2325,7 +2426,9 @@
       <c r="E56" s="10">
         <v>4</v>
       </c>
-      <c r="F56" s="11"/>
+      <c r="F56" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="3">
@@ -2344,7 +2447,9 @@
       <c r="E57" s="10">
         <v>6</v>
       </c>
-      <c r="F57" s="11"/>
+      <c r="F57" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="3">
@@ -2363,7 +2468,9 @@
       <c r="E58" s="10">
         <v>8</v>
       </c>
-      <c r="F58" s="11"/>
+      <c r="F58" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="3">
@@ -2380,7 +2487,9 @@
       <c r="E59" s="10">
         <v>10</v>
       </c>
-      <c r="F59" s="11"/>
+      <c r="F59" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="3">
@@ -2399,7 +2508,9 @@
       <c r="E60" s="10">
         <v>2</v>
       </c>
-      <c r="F60" s="11"/>
+      <c r="F60" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="3">
@@ -2418,7 +2529,9 @@
       <c r="E61" s="10">
         <v>4</v>
       </c>
-      <c r="F61" s="11"/>
+      <c r="F61" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="3">
@@ -2437,7 +2550,9 @@
       <c r="E62" s="10">
         <v>6</v>
       </c>
-      <c r="F62" s="11"/>
+      <c r="F62" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="3">
@@ -2456,7 +2571,9 @@
       <c r="E63" s="10">
         <v>8</v>
       </c>
-      <c r="F63" s="11"/>
+      <c r="F63" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="3">
@@ -2474,7 +2591,7 @@
         <v>10</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2494,7 +2611,9 @@
       <c r="E65" s="10">
         <v>2</v>
       </c>
-      <c r="F65" s="11"/>
+      <c r="F65" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="3">
@@ -2513,7 +2632,9 @@
       <c r="E66" s="10">
         <v>4</v>
       </c>
-      <c r="F66" s="11"/>
+      <c r="F66" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="3">
@@ -2532,7 +2653,9 @@
       <c r="E67" s="10">
         <v>6</v>
       </c>
-      <c r="F67" s="11"/>
+      <c r="F67" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="3">
@@ -2551,7 +2674,9 @@
       <c r="E68" s="10">
         <v>8</v>
       </c>
-      <c r="F68" s="11"/>
+      <c r="F68" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="3">
@@ -2568,7 +2693,9 @@
       <c r="E69" s="10">
         <v>10</v>
       </c>
-      <c r="F69" s="11"/>
+      <c r="F69" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="3">
@@ -2587,7 +2714,9 @@
       <c r="E70" s="10">
         <v>2</v>
       </c>
-      <c r="F70" s="11"/>
+      <c r="F70" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="3">
@@ -2606,7 +2735,9 @@
       <c r="E71" s="10">
         <v>4</v>
       </c>
-      <c r="F71" s="11"/>
+      <c r="F71" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="3">
@@ -2625,7 +2756,9 @@
       <c r="E72" s="10">
         <v>6</v>
       </c>
-      <c r="F72" s="11"/>
+      <c r="F72" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="3">
@@ -2644,7 +2777,9 @@
       <c r="E73" s="10">
         <v>8</v>
       </c>
-      <c r="F73" s="11"/>
+      <c r="F73" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="3">
@@ -2661,7 +2796,9 @@
       <c r="E74" s="10">
         <v>10</v>
       </c>
-      <c r="F74" s="11"/>
+      <c r="F74" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="3">
@@ -2701,7 +2838,9 @@
       <c r="E76" s="10">
         <v>4</v>
       </c>
-      <c r="F76" s="11"/>
+      <c r="F76" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="3">
@@ -2720,7 +2859,9 @@
       <c r="E77" s="10">
         <v>6</v>
       </c>
-      <c r="F77" s="11"/>
+      <c r="F77" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="3">
@@ -2739,7 +2880,9 @@
       <c r="E78" s="10">
         <v>8</v>
       </c>
-      <c r="F78" s="11"/>
+      <c r="F78" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="3">
@@ -2756,7 +2899,9 @@
       <c r="E79" s="10">
         <v>10</v>
       </c>
-      <c r="F79" s="11"/>
+      <c r="F79" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/EmployeeStar.xlsx
+++ b/hall/resources/sample/EmployeeStar.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -74,16 +74,169 @@
     <t>3_200</t>
   </si>
   <si>
-    <t>1_100</t>
-  </si>
-  <si>
-    <t>2_300</t>
-  </si>
-  <si>
-    <t>4_400</t>
+    <t>3_400</t>
+  </si>
+  <si>
+    <t>3_600</t>
+  </si>
+  <si>
+    <t>3_800</t>
+  </si>
+  <si>
+    <t>3_1000</t>
+  </si>
+  <si>
+    <t>3_300</t>
+  </si>
+  <si>
+    <t>3_900</t>
+  </si>
+  <si>
+    <t>3_1200</t>
+  </si>
+  <si>
+    <t>3_1500</t>
+  </si>
+  <si>
+    <t>3_1600</t>
+  </si>
+  <si>
+    <t>3_2000</t>
+  </si>
+  <si>
+    <t>3_500</t>
+  </si>
+  <si>
+    <t>3_2500</t>
+  </si>
+  <si>
+    <t>3_1800</t>
+  </si>
+  <si>
+    <t>3_2400</t>
+  </si>
+  <si>
+    <t>3_3000</t>
+  </si>
+  <si>
+    <t>5_100</t>
+  </si>
+  <si>
+    <t>5_150</t>
+  </si>
+  <si>
+    <t>5_200</t>
+  </si>
+  <si>
+    <t>5_250</t>
+  </si>
+  <si>
+    <t>5_300</t>
+  </si>
+  <si>
+    <t>5_180</t>
+  </si>
+  <si>
+    <t>5_240</t>
+  </si>
+  <si>
+    <t>5_360</t>
+  </si>
+  <si>
+    <t>5_420</t>
+  </si>
+  <si>
+    <t>5_280</t>
+  </si>
+  <si>
+    <t>5_440</t>
+  </si>
+  <si>
+    <t>5_520</t>
+  </si>
+  <si>
+    <t>5_400</t>
+  </si>
+  <si>
+    <t>5_500</t>
   </si>
   <si>
     <t>5_600</t>
+  </si>
+  <si>
+    <t>5_700</t>
+  </si>
+  <si>
+    <t>5_650</t>
+  </si>
+  <si>
+    <t>5_800</t>
+  </si>
+  <si>
+    <t>5_950</t>
+  </si>
+  <si>
+    <t>5_1100</t>
+  </si>
+  <si>
+    <t>4_50</t>
+  </si>
+  <si>
+    <t>4_80</t>
+  </si>
+  <si>
+    <t>4_110</t>
+  </si>
+  <si>
+    <t>4_140</t>
+  </si>
+  <si>
+    <t>4_170</t>
+  </si>
+  <si>
+    <t>4_120</t>
+  </si>
+  <si>
+    <t>4_160</t>
+  </si>
+  <si>
+    <t>4_200</t>
+  </si>
+  <si>
+    <t>4_240</t>
+  </si>
+  <si>
+    <t>4_100</t>
+  </si>
+  <si>
+    <t>4_150</t>
+  </si>
+  <si>
+    <t>4_250</t>
+  </si>
+  <si>
+    <t>4_300</t>
+  </si>
+  <si>
+    <t>4_260</t>
+  </si>
+  <si>
+    <t>4_320</t>
+  </si>
+  <si>
+    <t>4_380</t>
+  </si>
+  <si>
+    <t>4_440</t>
+  </si>
+  <si>
+    <t>4_460</t>
+  </si>
+  <si>
+    <t>4_540</t>
+  </si>
+  <si>
+    <t>4_620</t>
   </si>
 </sst>
 </file>
@@ -249,7 +402,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -259,6 +412,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,7 +761,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -620,16 +785,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -638,89 +803,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -752,6 +917,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1279,7 +1450,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
@@ -1479,7 +1650,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1500,7 +1671,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1521,7 +1692,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1542,7 +1713,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1561,7 +1732,7 @@
         <v>10</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1582,7 +1753,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1603,7 +1774,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1624,7 +1795,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1645,7 +1816,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1664,7 +1835,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1685,7 +1856,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1706,7 +1877,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1727,7 +1898,7 @@
         <v>6</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1748,7 +1919,7 @@
         <v>8</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1767,7 +1938,7 @@
         <v>10</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1788,7 +1959,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1809,7 +1980,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1830,7 +2001,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1851,7 +2022,7 @@
         <v>8</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1870,7 +2041,7 @@
         <v>10</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1890,8 +2061,8 @@
       <c r="E30" s="10">
         <v>2</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>14</v>
+      <c r="F30" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1911,8 +2082,8 @@
       <c r="E31" s="10">
         <v>4</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>15</v>
+      <c r="F31" s="11" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1932,8 +2103,8 @@
       <c r="E32" s="10">
         <v>6</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>16</v>
+      <c r="F32" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1953,8 +2124,8 @@
       <c r="E33" s="10">
         <v>8</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>17</v>
+      <c r="F33" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1972,8 +2143,8 @@
       <c r="E34" s="10">
         <v>10</v>
       </c>
-      <c r="F34" s="7" t="s">
-        <v>18</v>
+      <c r="F34" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1993,8 +2164,8 @@
       <c r="E35" s="10">
         <v>2</v>
       </c>
-      <c r="F35" s="7" t="s">
-        <v>14</v>
+      <c r="F35" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2014,8 +2185,8 @@
       <c r="E36" s="10">
         <v>4</v>
       </c>
-      <c r="F36" s="7" t="s">
-        <v>15</v>
+      <c r="F36" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2035,8 +2206,8 @@
       <c r="E37" s="10">
         <v>6</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>16</v>
+      <c r="F37" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2056,8 +2227,8 @@
       <c r="E38" s="10">
         <v>8</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>17</v>
+      <c r="F38" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2075,8 +2246,8 @@
       <c r="E39" s="10">
         <v>10</v>
       </c>
-      <c r="F39" s="7" t="s">
-        <v>18</v>
+      <c r="F39" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2096,8 +2267,8 @@
       <c r="E40" s="10">
         <v>2</v>
       </c>
-      <c r="F40" s="7" t="s">
-        <v>14</v>
+      <c r="F40" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2117,8 +2288,8 @@
       <c r="E41" s="10">
         <v>4</v>
       </c>
-      <c r="F41" s="7" t="s">
-        <v>15</v>
+      <c r="F41" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2138,8 +2309,8 @@
       <c r="E42" s="10">
         <v>6</v>
       </c>
-      <c r="F42" s="7" t="s">
-        <v>16</v>
+      <c r="F42" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2159,8 +2330,8 @@
       <c r="E43" s="10">
         <v>8</v>
       </c>
-      <c r="F43" s="7" t="s">
-        <v>17</v>
+      <c r="F43" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2178,8 +2349,8 @@
       <c r="E44" s="10">
         <v>10</v>
       </c>
-      <c r="F44" s="7" t="s">
-        <v>18</v>
+      <c r="F44" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2199,8 +2370,8 @@
       <c r="E45" s="10">
         <v>2</v>
       </c>
-      <c r="F45" s="7" t="s">
-        <v>14</v>
+      <c r="F45" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2220,8 +2391,8 @@
       <c r="E46" s="10">
         <v>4</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>15</v>
+      <c r="F46" s="11" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2241,8 +2412,8 @@
       <c r="E47" s="10">
         <v>6</v>
       </c>
-      <c r="F47" s="7" t="s">
-        <v>16</v>
+      <c r="F47" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2262,8 +2433,8 @@
       <c r="E48" s="10">
         <v>8</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>17</v>
+      <c r="F48" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2281,8 +2452,8 @@
       <c r="E49" s="10">
         <v>10</v>
       </c>
-      <c r="F49" s="7" t="s">
-        <v>18</v>
+      <c r="F49" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2302,8 +2473,8 @@
       <c r="E50" s="10">
         <v>2</v>
       </c>
-      <c r="F50" s="7" t="s">
-        <v>14</v>
+      <c r="F50" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2323,8 +2494,8 @@
       <c r="E51" s="10">
         <v>4</v>
       </c>
-      <c r="F51" s="7" t="s">
-        <v>15</v>
+      <c r="F51" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2344,8 +2515,8 @@
       <c r="E52" s="10">
         <v>6</v>
       </c>
-      <c r="F52" s="7" t="s">
-        <v>16</v>
+      <c r="F52" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2365,8 +2536,8 @@
       <c r="E53" s="10">
         <v>8</v>
       </c>
-      <c r="F53" s="7" t="s">
-        <v>17</v>
+      <c r="F53" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2384,8 +2555,8 @@
       <c r="E54" s="10">
         <v>10</v>
       </c>
-      <c r="F54" s="7" t="s">
-        <v>18</v>
+      <c r="F54" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2406,7 +2577,7 @@
         <v>2</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2427,7 +2598,7 @@
         <v>4</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2448,7 +2619,7 @@
         <v>6</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2469,7 +2640,7 @@
         <v>8</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2488,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2509,7 +2680,7 @@
         <v>2</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2530,7 +2701,7 @@
         <v>4</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2551,7 +2722,7 @@
         <v>6</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2572,7 +2743,7 @@
         <v>8</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2591,7 +2762,7 @@
         <v>10</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2612,7 +2783,7 @@
         <v>2</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2633,7 +2804,7 @@
         <v>4</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2654,7 +2825,7 @@
         <v>6</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2675,7 +2846,7 @@
         <v>8</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2694,7 +2865,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2715,7 +2886,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2736,7 +2907,7 @@
         <v>4</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2757,7 +2928,7 @@
         <v>6</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2778,7 +2949,7 @@
         <v>8</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2797,7 +2968,7 @@
         <v>10</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2818,7 +2989,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2839,7 +3010,7 @@
         <v>4</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2860,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2881,7 +3052,7 @@
         <v>8</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2900,7 +3071,1552 @@
         <v>10</v>
       </c>
       <c r="F79" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="3">
+        <f t="shared" ref="A80:A111" si="2">B80*100+C80</f>
+        <v>10101601</v>
+      </c>
+      <c r="B80" s="4">
+        <v>101016</v>
+      </c>
+      <c r="C80" s="4">
+        <v>1</v>
+      </c>
+      <c r="D80" s="5">
+        <v>10</v>
+      </c>
+      <c r="E80" s="6">
+        <v>2</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="3">
+        <f t="shared" si="2"/>
+        <v>10101602</v>
+      </c>
+      <c r="B81" s="4">
+        <v>101016</v>
+      </c>
+      <c r="C81" s="4">
+        <v>2</v>
+      </c>
+      <c r="D81" s="5">
+        <v>30</v>
+      </c>
+      <c r="E81" s="6">
+        <v>4</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="3">
+        <f t="shared" si="2"/>
+        <v>10101603</v>
+      </c>
+      <c r="B82" s="4">
+        <v>101016</v>
+      </c>
+      <c r="C82" s="4">
+        <v>3</v>
+      </c>
+      <c r="D82" s="5">
+        <v>60</v>
+      </c>
+      <c r="E82" s="6">
+        <v>6</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="3">
+        <f t="shared" si="2"/>
+        <v>10101604</v>
+      </c>
+      <c r="B83" s="4">
+        <v>101016</v>
+      </c>
+      <c r="C83" s="4">
+        <v>4</v>
+      </c>
+      <c r="D83" s="5">
+        <v>100</v>
+      </c>
+      <c r="E83" s="6">
+        <v>8</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="3">
+        <f t="shared" si="2"/>
+        <v>10101605</v>
+      </c>
+      <c r="B84" s="4">
+        <v>101016</v>
+      </c>
+      <c r="C84" s="4">
+        <v>5</v>
+      </c>
+      <c r="D84" s="4"/>
+      <c r="E84" s="6">
+        <v>10</v>
+      </c>
+      <c r="F84" s="12" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="3">
+        <f t="shared" si="2"/>
+        <v>10201701</v>
+      </c>
+      <c r="B85" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C85" s="8">
+        <v>1</v>
+      </c>
+      <c r="D85" s="9">
+        <v>10</v>
+      </c>
+      <c r="E85" s="10">
+        <v>2</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="3">
+        <f t="shared" si="2"/>
+        <v>10201702</v>
+      </c>
+      <c r="B86" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C86" s="8">
+        <v>2</v>
+      </c>
+      <c r="D86" s="9">
+        <v>30</v>
+      </c>
+      <c r="E86" s="10">
+        <v>4</v>
+      </c>
+      <c r="F86" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="3">
+        <f t="shared" si="2"/>
+        <v>10201703</v>
+      </c>
+      <c r="B87" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C87" s="8">
+        <v>3</v>
+      </c>
+      <c r="D87" s="9">
+        <v>60</v>
+      </c>
+      <c r="E87" s="10">
+        <v>6</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="3">
+        <f t="shared" si="2"/>
+        <v>10201704</v>
+      </c>
+      <c r="B88" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C88" s="8">
+        <v>4</v>
+      </c>
+      <c r="D88" s="9">
+        <v>100</v>
+      </c>
+      <c r="E88" s="10">
+        <v>8</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="3">
+        <f t="shared" si="2"/>
+        <v>10201705</v>
+      </c>
+      <c r="B89" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C89" s="8">
+        <v>5</v>
+      </c>
+      <c r="D89" s="8"/>
+      <c r="E89" s="10">
+        <v>10</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="3">
+        <f t="shared" si="2"/>
+        <v>10301801</v>
+      </c>
+      <c r="B90" s="8">
+        <v>103018</v>
+      </c>
+      <c r="C90" s="8">
+        <v>1</v>
+      </c>
+      <c r="D90" s="9">
+        <v>10</v>
+      </c>
+      <c r="E90" s="10">
+        <v>2</v>
+      </c>
+      <c r="F90" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="3">
+        <f t="shared" si="2"/>
+        <v>10301802</v>
+      </c>
+      <c r="B91" s="8">
+        <v>103018</v>
+      </c>
+      <c r="C91" s="8">
+        <v>2</v>
+      </c>
+      <c r="D91" s="9">
+        <v>30</v>
+      </c>
+      <c r="E91" s="10">
+        <v>4</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="3">
+        <f t="shared" si="2"/>
+        <v>10301803</v>
+      </c>
+      <c r="B92" s="8">
+        <v>103018</v>
+      </c>
+      <c r="C92" s="8">
+        <v>3</v>
+      </c>
+      <c r="D92" s="9">
+        <v>60</v>
+      </c>
+      <c r="E92" s="10">
+        <v>6</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="3">
+        <f t="shared" si="2"/>
+        <v>10301804</v>
+      </c>
+      <c r="B93" s="8">
+        <v>103018</v>
+      </c>
+      <c r="C93" s="8">
+        <v>4</v>
+      </c>
+      <c r="D93" s="9">
+        <v>100</v>
+      </c>
+      <c r="E93" s="10">
+        <v>8</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="3">
+        <f t="shared" si="2"/>
+        <v>10301805</v>
+      </c>
+      <c r="B94" s="8">
+        <v>103018</v>
+      </c>
+      <c r="C94" s="8">
+        <v>5</v>
+      </c>
+      <c r="D94" s="8"/>
+      <c r="E94" s="10">
+        <v>10</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="3">
+        <f t="shared" si="2"/>
+        <v>10401901</v>
+      </c>
+      <c r="B95" s="8">
+        <v>104019</v>
+      </c>
+      <c r="C95" s="8">
+        <v>1</v>
+      </c>
+      <c r="D95" s="9">
+        <v>10</v>
+      </c>
+      <c r="E95" s="10">
+        <v>2</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="3">
+        <f t="shared" si="2"/>
+        <v>10401902</v>
+      </c>
+      <c r="B96" s="8">
+        <v>104019</v>
+      </c>
+      <c r="C96" s="8">
+        <v>2</v>
+      </c>
+      <c r="D96" s="9">
+        <v>30</v>
+      </c>
+      <c r="E96" s="10">
+        <v>4</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="3">
+        <f t="shared" si="2"/>
+        <v>10401903</v>
+      </c>
+      <c r="B97" s="8">
+        <v>104019</v>
+      </c>
+      <c r="C97" s="8">
+        <v>3</v>
+      </c>
+      <c r="D97" s="9">
+        <v>60</v>
+      </c>
+      <c r="E97" s="10">
+        <v>6</v>
+      </c>
+      <c r="F97" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="3">
+        <f t="shared" si="2"/>
+        <v>10401904</v>
+      </c>
+      <c r="B98" s="8">
+        <v>104019</v>
+      </c>
+      <c r="C98" s="8">
+        <v>4</v>
+      </c>
+      <c r="D98" s="9">
+        <v>100</v>
+      </c>
+      <c r="E98" s="10">
+        <v>8</v>
+      </c>
+      <c r="F98" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="3">
+        <f t="shared" si="2"/>
+        <v>10401905</v>
+      </c>
+      <c r="B99" s="8">
+        <v>104019</v>
+      </c>
+      <c r="C99" s="8">
+        <v>5</v>
+      </c>
+      <c r="D99" s="8"/>
+      <c r="E99" s="10">
+        <v>10</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="3">
+        <f t="shared" si="2"/>
+        <v>10502001</v>
+      </c>
+      <c r="B100" s="8">
+        <v>105020</v>
+      </c>
+      <c r="C100" s="8">
+        <v>1</v>
+      </c>
+      <c r="D100" s="9">
+        <v>10</v>
+      </c>
+      <c r="E100" s="10">
+        <v>2</v>
+      </c>
+      <c r="F100" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="3">
+        <f t="shared" si="2"/>
+        <v>10502002</v>
+      </c>
+      <c r="B101" s="8">
+        <v>105020</v>
+      </c>
+      <c r="C101" s="8">
+        <v>2</v>
+      </c>
+      <c r="D101" s="9">
+        <v>30</v>
+      </c>
+      <c r="E101" s="10">
+        <v>4</v>
+      </c>
+      <c r="F101" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="3">
+        <f t="shared" si="2"/>
+        <v>10502003</v>
+      </c>
+      <c r="B102" s="8">
+        <v>105020</v>
+      </c>
+      <c r="C102" s="8">
+        <v>3</v>
+      </c>
+      <c r="D102" s="9">
+        <v>60</v>
+      </c>
+      <c r="E102" s="10">
+        <v>6</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="3">
+        <f t="shared" si="2"/>
+        <v>10502004</v>
+      </c>
+      <c r="B103" s="8">
+        <v>105020</v>
+      </c>
+      <c r="C103" s="8">
+        <v>4</v>
+      </c>
+      <c r="D103" s="9">
+        <v>100</v>
+      </c>
+      <c r="E103" s="10">
+        <v>8</v>
+      </c>
+      <c r="F103" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="3">
+        <f t="shared" si="2"/>
+        <v>10502005</v>
+      </c>
+      <c r="B104" s="8">
+        <v>105020</v>
+      </c>
+      <c r="C104" s="8">
+        <v>5</v>
+      </c>
+      <c r="D104" s="8"/>
+      <c r="E104" s="10">
+        <v>10</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="3">
+        <f t="shared" si="2"/>
+        <v>20102101</v>
+      </c>
+      <c r="B105" s="8">
+        <v>201021</v>
+      </c>
+      <c r="C105" s="8">
+        <v>1</v>
+      </c>
+      <c r="D105" s="9">
+        <v>10</v>
+      </c>
+      <c r="E105" s="10">
+        <v>2</v>
+      </c>
+      <c r="F105" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="3">
+        <f t="shared" si="2"/>
+        <v>20102102</v>
+      </c>
+      <c r="B106" s="8">
+        <v>201021</v>
+      </c>
+      <c r="C106" s="8">
+        <v>2</v>
+      </c>
+      <c r="D106" s="9">
+        <v>30</v>
+      </c>
+      <c r="E106" s="10">
+        <v>4</v>
+      </c>
+      <c r="F106" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="3">
+        <f t="shared" si="2"/>
+        <v>20102103</v>
+      </c>
+      <c r="B107" s="8">
+        <v>201021</v>
+      </c>
+      <c r="C107" s="8">
+        <v>3</v>
+      </c>
+      <c r="D107" s="9">
+        <v>60</v>
+      </c>
+      <c r="E107" s="10">
+        <v>6</v>
+      </c>
+      <c r="F107" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="3">
+        <f t="shared" si="2"/>
+        <v>20102104</v>
+      </c>
+      <c r="B108" s="8">
+        <v>201021</v>
+      </c>
+      <c r="C108" s="8">
+        <v>4</v>
+      </c>
+      <c r="D108" s="9">
+        <v>100</v>
+      </c>
+      <c r="E108" s="10">
+        <v>8</v>
+      </c>
+      <c r="F108" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="3">
+        <f t="shared" si="2"/>
+        <v>20102105</v>
+      </c>
+      <c r="B109" s="8">
+        <v>201021</v>
+      </c>
+      <c r="C109" s="8">
+        <v>5</v>
+      </c>
+      <c r="D109" s="8"/>
+      <c r="E109" s="10">
+        <v>10</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="3">
+        <f t="shared" si="2"/>
+        <v>20202201</v>
+      </c>
+      <c r="B110" s="8">
+        <v>202022</v>
+      </c>
+      <c r="C110" s="8">
+        <v>1</v>
+      </c>
+      <c r="D110" s="9">
+        <v>10</v>
+      </c>
+      <c r="E110" s="10">
+        <v>2</v>
+      </c>
+      <c r="F110" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="3">
+        <f t="shared" si="2"/>
+        <v>20202202</v>
+      </c>
+      <c r="B111" s="8">
+        <v>202022</v>
+      </c>
+      <c r="C111" s="8">
+        <v>2</v>
+      </c>
+      <c r="D111" s="9">
+        <v>30</v>
+      </c>
+      <c r="E111" s="10">
+        <v>4</v>
+      </c>
+      <c r="F111" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="3">
+        <f t="shared" ref="A112:A154" si="3">B112*100+C112</f>
+        <v>20202203</v>
+      </c>
+      <c r="B112" s="8">
+        <v>202022</v>
+      </c>
+      <c r="C112" s="8">
+        <v>3</v>
+      </c>
+      <c r="D112" s="9">
+        <v>60</v>
+      </c>
+      <c r="E112" s="10">
+        <v>6</v>
+      </c>
+      <c r="F112" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="3">
+        <f t="shared" si="3"/>
+        <v>20202204</v>
+      </c>
+      <c r="B113" s="8">
+        <v>202022</v>
+      </c>
+      <c r="C113" s="8">
+        <v>4</v>
+      </c>
+      <c r="D113" s="9">
+        <v>100</v>
+      </c>
+      <c r="E113" s="10">
+        <v>8</v>
+      </c>
+      <c r="F113" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="3">
+        <f t="shared" si="3"/>
+        <v>20202205</v>
+      </c>
+      <c r="B114" s="8">
+        <v>202022</v>
+      </c>
+      <c r="C114" s="8">
+        <v>5</v>
+      </c>
+      <c r="D114" s="8"/>
+      <c r="E114" s="10">
+        <v>10</v>
+      </c>
+      <c r="F114" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="3">
+        <f t="shared" si="3"/>
+        <v>20302301</v>
+      </c>
+      <c r="B115" s="8">
+        <v>203023</v>
+      </c>
+      <c r="C115" s="8">
+        <v>1</v>
+      </c>
+      <c r="D115" s="9">
+        <v>10</v>
+      </c>
+      <c r="E115" s="10">
+        <v>2</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="3">
+        <f t="shared" si="3"/>
+        <v>20302302</v>
+      </c>
+      <c r="B116" s="8">
+        <v>203023</v>
+      </c>
+      <c r="C116" s="8">
+        <v>2</v>
+      </c>
+      <c r="D116" s="9">
+        <v>30</v>
+      </c>
+      <c r="E116" s="10">
+        <v>4</v>
+      </c>
+      <c r="F116" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" s="3">
+        <f t="shared" si="3"/>
+        <v>20302303</v>
+      </c>
+      <c r="B117" s="8">
+        <v>203023</v>
+      </c>
+      <c r="C117" s="8">
+        <v>3</v>
+      </c>
+      <c r="D117" s="9">
+        <v>60</v>
+      </c>
+      <c r="E117" s="10">
+        <v>6</v>
+      </c>
+      <c r="F117" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="3">
+        <f t="shared" si="3"/>
+        <v>20302304</v>
+      </c>
+      <c r="B118" s="8">
+        <v>203023</v>
+      </c>
+      <c r="C118" s="8">
+        <v>4</v>
+      </c>
+      <c r="D118" s="9">
+        <v>100</v>
+      </c>
+      <c r="E118" s="10">
+        <v>8</v>
+      </c>
+      <c r="F118" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" s="3">
+        <f t="shared" si="3"/>
+        <v>20302305</v>
+      </c>
+      <c r="B119" s="8">
+        <v>203023</v>
+      </c>
+      <c r="C119" s="8">
+        <v>5</v>
+      </c>
+      <c r="D119" s="8"/>
+      <c r="E119" s="10">
+        <v>10</v>
+      </c>
+      <c r="F119" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" s="3">
+        <f t="shared" si="3"/>
+        <v>20402401</v>
+      </c>
+      <c r="B120" s="8">
+        <v>204024</v>
+      </c>
+      <c r="C120" s="8">
+        <v>1</v>
+      </c>
+      <c r="D120" s="9">
+        <v>10</v>
+      </c>
+      <c r="E120" s="10">
+        <v>2</v>
+      </c>
+      <c r="F120" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="3">
+        <f t="shared" si="3"/>
+        <v>20402402</v>
+      </c>
+      <c r="B121" s="8">
+        <v>204024</v>
+      </c>
+      <c r="C121" s="8">
+        <v>2</v>
+      </c>
+      <c r="D121" s="9">
+        <v>30</v>
+      </c>
+      <c r="E121" s="10">
+        <v>4</v>
+      </c>
+      <c r="F121" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" s="3">
+        <f t="shared" si="3"/>
+        <v>20402403</v>
+      </c>
+      <c r="B122" s="8">
+        <v>204024</v>
+      </c>
+      <c r="C122" s="8">
+        <v>3</v>
+      </c>
+      <c r="D122" s="9">
+        <v>60</v>
+      </c>
+      <c r="E122" s="10">
+        <v>6</v>
+      </c>
+      <c r="F122" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="3">
+        <f t="shared" si="3"/>
+        <v>20402404</v>
+      </c>
+      <c r="B123" s="8">
+        <v>204024</v>
+      </c>
+      <c r="C123" s="8">
+        <v>4</v>
+      </c>
+      <c r="D123" s="9">
+        <v>100</v>
+      </c>
+      <c r="E123" s="10">
+        <v>8</v>
+      </c>
+      <c r="F123" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="3">
+        <f t="shared" si="3"/>
+        <v>20402405</v>
+      </c>
+      <c r="B124" s="8">
+        <v>204024</v>
+      </c>
+      <c r="C124" s="8">
+        <v>5</v>
+      </c>
+      <c r="D124" s="8"/>
+      <c r="E124" s="10">
+        <v>10</v>
+      </c>
+      <c r="F124" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" s="3">
+        <f t="shared" si="3"/>
+        <v>20502501</v>
+      </c>
+      <c r="B125" s="8">
+        <v>205025</v>
+      </c>
+      <c r="C125" s="8">
+        <v>1</v>
+      </c>
+      <c r="D125" s="9">
+        <v>10</v>
+      </c>
+      <c r="E125" s="10">
+        <v>2</v>
+      </c>
+      <c r="F125" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" s="3">
+        <f t="shared" si="3"/>
+        <v>20502502</v>
+      </c>
+      <c r="B126" s="8">
+        <v>205025</v>
+      </c>
+      <c r="C126" s="8">
+        <v>2</v>
+      </c>
+      <c r="D126" s="9">
+        <v>30</v>
+      </c>
+      <c r="E126" s="10">
+        <v>4</v>
+      </c>
+      <c r="F126" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" s="3">
+        <f t="shared" si="3"/>
+        <v>20502503</v>
+      </c>
+      <c r="B127" s="8">
+        <v>205025</v>
+      </c>
+      <c r="C127" s="8">
+        <v>3</v>
+      </c>
+      <c r="D127" s="9">
+        <v>60</v>
+      </c>
+      <c r="E127" s="10">
+        <v>6</v>
+      </c>
+      <c r="F127" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" s="3">
+        <f t="shared" si="3"/>
+        <v>20502504</v>
+      </c>
+      <c r="B128" s="8">
+        <v>205025</v>
+      </c>
+      <c r="C128" s="8">
+        <v>4</v>
+      </c>
+      <c r="D128" s="9">
+        <v>100</v>
+      </c>
+      <c r="E128" s="10">
+        <v>8</v>
+      </c>
+      <c r="F128" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" s="3">
+        <f t="shared" si="3"/>
+        <v>20502505</v>
+      </c>
+      <c r="B129" s="8">
+        <v>205025</v>
+      </c>
+      <c r="C129" s="8">
+        <v>5</v>
+      </c>
+      <c r="D129" s="8"/>
+      <c r="E129" s="10">
+        <v>10</v>
+      </c>
+      <c r="F129" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" s="3">
+        <f t="shared" si="3"/>
+        <v>30102601</v>
+      </c>
+      <c r="B130" s="8">
+        <v>301026</v>
+      </c>
+      <c r="C130" s="8">
+        <v>1</v>
+      </c>
+      <c r="D130" s="9">
+        <v>10</v>
+      </c>
+      <c r="E130" s="10">
+        <v>2</v>
+      </c>
+      <c r="F130" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" s="3">
+        <f t="shared" si="3"/>
+        <v>30102602</v>
+      </c>
+      <c r="B131" s="8">
+        <v>301026</v>
+      </c>
+      <c r="C131" s="8">
+        <v>2</v>
+      </c>
+      <c r="D131" s="9">
+        <v>30</v>
+      </c>
+      <c r="E131" s="10">
+        <v>4</v>
+      </c>
+      <c r="F131" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" s="3">
+        <f t="shared" si="3"/>
+        <v>30102603</v>
+      </c>
+      <c r="B132" s="8">
+        <v>301026</v>
+      </c>
+      <c r="C132" s="8">
+        <v>3</v>
+      </c>
+      <c r="D132" s="9">
+        <v>60</v>
+      </c>
+      <c r="E132" s="10">
+        <v>6</v>
+      </c>
+      <c r="F132" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" s="3">
+        <f t="shared" si="3"/>
+        <v>30102604</v>
+      </c>
+      <c r="B133" s="8">
+        <v>301026</v>
+      </c>
+      <c r="C133" s="8">
+        <v>4</v>
+      </c>
+      <c r="D133" s="9">
+        <v>100</v>
+      </c>
+      <c r="E133" s="10">
+        <v>8</v>
+      </c>
+      <c r="F133" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" s="3">
+        <f t="shared" si="3"/>
+        <v>30102605</v>
+      </c>
+      <c r="B134" s="8">
+        <v>301026</v>
+      </c>
+      <c r="C134" s="8">
+        <v>5</v>
+      </c>
+      <c r="D134" s="8"/>
+      <c r="E134" s="10">
+        <v>10</v>
+      </c>
+      <c r="F134" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" s="3">
+        <f t="shared" si="3"/>
+        <v>30202701</v>
+      </c>
+      <c r="B135" s="8">
+        <v>302027</v>
+      </c>
+      <c r="C135" s="8">
+        <v>1</v>
+      </c>
+      <c r="D135" s="9">
+        <v>10</v>
+      </c>
+      <c r="E135" s="10">
+        <v>2</v>
+      </c>
+      <c r="F135" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" s="3">
+        <f t="shared" si="3"/>
+        <v>30202702</v>
+      </c>
+      <c r="B136" s="8">
+        <v>302027</v>
+      </c>
+      <c r="C136" s="8">
+        <v>2</v>
+      </c>
+      <c r="D136" s="9">
+        <v>30</v>
+      </c>
+      <c r="E136" s="10">
+        <v>4</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" s="3">
+        <f t="shared" si="3"/>
+        <v>30202703</v>
+      </c>
+      <c r="B137" s="8">
+        <v>302027</v>
+      </c>
+      <c r="C137" s="8">
+        <v>3</v>
+      </c>
+      <c r="D137" s="9">
+        <v>60</v>
+      </c>
+      <c r="E137" s="10">
+        <v>6</v>
+      </c>
+      <c r="F137" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" s="3">
+        <f t="shared" si="3"/>
+        <v>30202704</v>
+      </c>
+      <c r="B138" s="8">
+        <v>302027</v>
+      </c>
+      <c r="C138" s="8">
+        <v>4</v>
+      </c>
+      <c r="D138" s="9">
+        <v>100</v>
+      </c>
+      <c r="E138" s="10">
+        <v>8</v>
+      </c>
+      <c r="F138" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" s="3">
+        <f t="shared" si="3"/>
+        <v>30202705</v>
+      </c>
+      <c r="B139" s="8">
+        <v>302027</v>
+      </c>
+      <c r="C139" s="8">
+        <v>5</v>
+      </c>
+      <c r="D139" s="8"/>
+      <c r="E139" s="10">
+        <v>10</v>
+      </c>
+      <c r="F139" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" s="3">
+        <f t="shared" si="3"/>
+        <v>30302801</v>
+      </c>
+      <c r="B140" s="10">
+        <v>303028</v>
+      </c>
+      <c r="C140" s="8">
+        <v>1</v>
+      </c>
+      <c r="D140" s="9">
+        <v>10</v>
+      </c>
+      <c r="E140" s="10">
+        <v>2</v>
+      </c>
+      <c r="F140" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" s="3">
+        <f t="shared" si="3"/>
+        <v>30302802</v>
+      </c>
+      <c r="B141" s="10">
+        <v>303028</v>
+      </c>
+      <c r="C141" s="8">
+        <v>2</v>
+      </c>
+      <c r="D141" s="9">
+        <v>30</v>
+      </c>
+      <c r="E141" s="10">
+        <v>4</v>
+      </c>
+      <c r="F141" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" s="3">
+        <f t="shared" si="3"/>
+        <v>30302803</v>
+      </c>
+      <c r="B142" s="10">
+        <v>303028</v>
+      </c>
+      <c r="C142" s="8">
+        <v>3</v>
+      </c>
+      <c r="D142" s="9">
+        <v>60</v>
+      </c>
+      <c r="E142" s="10">
+        <v>6</v>
+      </c>
+      <c r="F142" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" s="3">
+        <f t="shared" si="3"/>
+        <v>30302804</v>
+      </c>
+      <c r="B143" s="10">
+        <v>303028</v>
+      </c>
+      <c r="C143" s="8">
+        <v>4</v>
+      </c>
+      <c r="D143" s="9">
+        <v>100</v>
+      </c>
+      <c r="E143" s="10">
+        <v>8</v>
+      </c>
+      <c r="F143" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" s="3">
+        <f t="shared" si="3"/>
+        <v>30302805</v>
+      </c>
+      <c r="B144" s="10">
+        <v>303028</v>
+      </c>
+      <c r="C144" s="8">
+        <v>5</v>
+      </c>
+      <c r="D144" s="8"/>
+      <c r="E144" s="10">
+        <v>10</v>
+      </c>
+      <c r="F144" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" s="3">
+        <f t="shared" si="3"/>
+        <v>30402901</v>
+      </c>
+      <c r="B145" s="8">
+        <v>304029</v>
+      </c>
+      <c r="C145" s="8">
+        <v>1</v>
+      </c>
+      <c r="D145" s="9">
+        <v>10</v>
+      </c>
+      <c r="E145" s="10">
+        <v>2</v>
+      </c>
+      <c r="F145" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" s="3">
+        <f t="shared" si="3"/>
+        <v>30402902</v>
+      </c>
+      <c r="B146" s="8">
+        <v>304029</v>
+      </c>
+      <c r="C146" s="8">
+        <v>2</v>
+      </c>
+      <c r="D146" s="9">
+        <v>30</v>
+      </c>
+      <c r="E146" s="10">
+        <v>4</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" s="3">
+        <f t="shared" si="3"/>
+        <v>30402903</v>
+      </c>
+      <c r="B147" s="8">
+        <v>304029</v>
+      </c>
+      <c r="C147" s="8">
+        <v>3</v>
+      </c>
+      <c r="D147" s="9">
+        <v>60</v>
+      </c>
+      <c r="E147" s="10">
+        <v>6</v>
+      </c>
+      <c r="F147" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" s="3">
+        <f t="shared" si="3"/>
+        <v>30402904</v>
+      </c>
+      <c r="B148" s="8">
+        <v>304029</v>
+      </c>
+      <c r="C148" s="8">
+        <v>4</v>
+      </c>
+      <c r="D148" s="9">
+        <v>100</v>
+      </c>
+      <c r="E148" s="10">
+        <v>8</v>
+      </c>
+      <c r="F148" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" s="3">
+        <f t="shared" si="3"/>
+        <v>30402905</v>
+      </c>
+      <c r="B149" s="8">
+        <v>304029</v>
+      </c>
+      <c r="C149" s="8">
+        <v>5</v>
+      </c>
+      <c r="D149" s="8"/>
+      <c r="E149" s="10">
+        <v>10</v>
+      </c>
+      <c r="F149" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="3">
+        <f t="shared" si="3"/>
+        <v>30503001</v>
+      </c>
+      <c r="B150" s="8">
+        <v>305030</v>
+      </c>
+      <c r="C150" s="8">
+        <v>1</v>
+      </c>
+      <c r="D150" s="9">
+        <v>10</v>
+      </c>
+      <c r="E150" s="10">
+        <v>2</v>
+      </c>
+      <c r="F150" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="3">
+        <f t="shared" si="3"/>
+        <v>30503002</v>
+      </c>
+      <c r="B151" s="8">
+        <v>305030</v>
+      </c>
+      <c r="C151" s="8">
+        <v>2</v>
+      </c>
+      <c r="D151" s="9">
+        <v>30</v>
+      </c>
+      <c r="E151" s="10">
+        <v>4</v>
+      </c>
+      <c r="F151" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="3">
+        <f t="shared" si="3"/>
+        <v>30503003</v>
+      </c>
+      <c r="B152" s="8">
+        <v>305030</v>
+      </c>
+      <c r="C152" s="8">
+        <v>3</v>
+      </c>
+      <c r="D152" s="9">
+        <v>60</v>
+      </c>
+      <c r="E152" s="10">
+        <v>6</v>
+      </c>
+      <c r="F152" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="3">
+        <f t="shared" si="3"/>
+        <v>30503004</v>
+      </c>
+      <c r="B153" s="8">
+        <v>305030</v>
+      </c>
+      <c r="C153" s="8">
+        <v>4</v>
+      </c>
+      <c r="D153" s="9">
+        <v>100</v>
+      </c>
+      <c r="E153" s="10">
+        <v>8</v>
+      </c>
+      <c r="F153" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="3">
+        <f t="shared" si="3"/>
+        <v>30503005</v>
+      </c>
+      <c r="B154" s="8">
+        <v>305030</v>
+      </c>
+      <c r="C154" s="8">
+        <v>5</v>
+      </c>
+      <c r="D154" s="8"/>
+      <c r="E154" s="10">
+        <v>10</v>
+      </c>
+      <c r="F154" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/EmployeeStar.xlsx
+++ b/hall/resources/sample/EmployeeStar.xlsx
@@ -1562,7 +1562,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E6" s="6">
         <v>4</v>
@@ -1583,7 +1583,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="5">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E7" s="6">
         <v>6</v>
@@ -1604,7 +1604,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="5">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E8" s="6">
         <v>8</v>
@@ -1644,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E10" s="10">
         <v>2</v>
@@ -1665,7 +1665,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E11" s="10">
         <v>4</v>
@@ -1686,7 +1686,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="9">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E12" s="10">
         <v>6</v>
@@ -1707,7 +1707,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="9">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E13" s="10">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E15" s="10">
         <v>2</v>
@@ -1789,7 +1789,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E17" s="10">
         <v>6</v>
@@ -1810,7 +1810,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E18" s="10">
         <v>8</v>
@@ -1850,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E20" s="10">
         <v>2</v>
@@ -1871,7 +1871,7 @@
         <v>2</v>
       </c>
       <c r="D21" s="9">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E21" s="10">
         <v>4</v>
@@ -1892,7 +1892,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="9">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E22" s="10">
         <v>6</v>
@@ -1913,7 +1913,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="9">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="E23" s="10">
         <v>8</v>
@@ -1953,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="9">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E25" s="10">
         <v>2</v>
@@ -1974,7 +1974,7 @@
         <v>2</v>
       </c>
       <c r="D26" s="9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E26" s="10">
         <v>4</v>
@@ -1995,7 +1995,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E27" s="10">
         <v>6</v>
@@ -2016,7 +2016,7 @@
         <v>4</v>
       </c>
       <c r="D28" s="9">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E28" s="10">
         <v>8</v>
@@ -2055,7 +2055,7 @@
       <c r="C30" s="8">
         <v>1</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="5">
         <v>10</v>
       </c>
       <c r="E30" s="10">
@@ -2076,8 +2076,8 @@
       <c r="C31" s="8">
         <v>2</v>
       </c>
-      <c r="D31" s="9">
-        <v>30</v>
+      <c r="D31" s="5">
+        <v>20</v>
       </c>
       <c r="E31" s="10">
         <v>4</v>
@@ -2097,8 +2097,8 @@
       <c r="C32" s="8">
         <v>3</v>
       </c>
-      <c r="D32" s="9">
-        <v>60</v>
+      <c r="D32" s="5">
+        <v>30</v>
       </c>
       <c r="E32" s="10">
         <v>6</v>
@@ -2118,8 +2118,8 @@
       <c r="C33" s="8">
         <v>4</v>
       </c>
-      <c r="D33" s="9">
-        <v>100</v>
+      <c r="D33" s="5">
+        <v>40</v>
       </c>
       <c r="E33" s="10">
         <v>8</v>
@@ -2139,7 +2139,7 @@
       <c r="C34" s="8">
         <v>5</v>
       </c>
-      <c r="D34" s="8"/>
+      <c r="D34" s="4"/>
       <c r="E34" s="10">
         <v>10</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E35" s="10">
         <v>2</v>
@@ -2180,7 +2180,7 @@
         <v>2</v>
       </c>
       <c r="D36" s="9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E36" s="10">
         <v>4</v>
@@ -2201,7 +2201,7 @@
         <v>3</v>
       </c>
       <c r="D37" s="9">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E37" s="10">
         <v>6</v>
@@ -2222,7 +2222,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="9">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E38" s="10">
         <v>8</v>
@@ -2262,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E40" s="10">
         <v>2</v>
@@ -2304,7 +2304,7 @@
         <v>3</v>
       </c>
       <c r="D42" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E42" s="10">
         <v>6</v>
@@ -2325,7 +2325,7 @@
         <v>4</v>
       </c>
       <c r="D43" s="9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E43" s="10">
         <v>8</v>
@@ -2365,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E45" s="10">
         <v>2</v>
@@ -2386,7 +2386,7 @@
         <v>2</v>
       </c>
       <c r="D46" s="9">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E46" s="10">
         <v>4</v>
@@ -2407,7 +2407,7 @@
         <v>3</v>
       </c>
       <c r="D47" s="9">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E47" s="10">
         <v>6</v>
@@ -2428,7 +2428,7 @@
         <v>4</v>
       </c>
       <c r="D48" s="9">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="E48" s="10">
         <v>8</v>
@@ -2468,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="9">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E50" s="10">
         <v>2</v>
@@ -2489,7 +2489,7 @@
         <v>2</v>
       </c>
       <c r="D51" s="9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E51" s="10">
         <v>4</v>
@@ -2510,7 +2510,7 @@
         <v>3</v>
       </c>
       <c r="D52" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E52" s="10">
         <v>6</v>
@@ -2531,7 +2531,7 @@
         <v>4</v>
       </c>
       <c r="D53" s="9">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E53" s="10">
         <v>8</v>
@@ -2570,7 +2570,7 @@
       <c r="C55" s="8">
         <v>1</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="5">
         <v>10</v>
       </c>
       <c r="E55" s="10">
@@ -2591,8 +2591,8 @@
       <c r="C56" s="8">
         <v>2</v>
       </c>
-      <c r="D56" s="9">
-        <v>30</v>
+      <c r="D56" s="5">
+        <v>20</v>
       </c>
       <c r="E56" s="10">
         <v>4</v>
@@ -2612,8 +2612,8 @@
       <c r="C57" s="8">
         <v>3</v>
       </c>
-      <c r="D57" s="9">
-        <v>60</v>
+      <c r="D57" s="5">
+        <v>30</v>
       </c>
       <c r="E57" s="10">
         <v>6</v>
@@ -2633,8 +2633,8 @@
       <c r="C58" s="8">
         <v>4</v>
       </c>
-      <c r="D58" s="9">
-        <v>100</v>
+      <c r="D58" s="5">
+        <v>40</v>
       </c>
       <c r="E58" s="10">
         <v>8</v>
@@ -2654,7 +2654,7 @@
       <c r="C59" s="8">
         <v>5</v>
       </c>
-      <c r="D59" s="8"/>
+      <c r="D59" s="4"/>
       <c r="E59" s="10">
         <v>10</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="D60" s="9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E60" s="10">
         <v>2</v>
@@ -2695,7 +2695,7 @@
         <v>2</v>
       </c>
       <c r="D61" s="9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E61" s="10">
         <v>4</v>
@@ -2716,7 +2716,7 @@
         <v>3</v>
       </c>
       <c r="D62" s="9">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E62" s="10">
         <v>6</v>
@@ -2737,7 +2737,7 @@
         <v>4</v>
       </c>
       <c r="D63" s="9">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E63" s="10">
         <v>8</v>
@@ -2777,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="D65" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E65" s="10">
         <v>2</v>
@@ -2819,7 +2819,7 @@
         <v>3</v>
       </c>
       <c r="D67" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E67" s="10">
         <v>6</v>
@@ -2840,7 +2840,7 @@
         <v>4</v>
       </c>
       <c r="D68" s="9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E68" s="10">
         <v>8</v>
@@ -2880,7 +2880,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E70" s="10">
         <v>2</v>
@@ -2901,7 +2901,7 @@
         <v>2</v>
       </c>
       <c r="D71" s="9">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E71" s="10">
         <v>4</v>
@@ -2922,7 +2922,7 @@
         <v>3</v>
       </c>
       <c r="D72" s="9">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E72" s="10">
         <v>6</v>
@@ -2943,7 +2943,7 @@
         <v>4</v>
       </c>
       <c r="D73" s="9">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="E73" s="10">
         <v>8</v>
@@ -2983,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="9">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E75" s="10">
         <v>2</v>
@@ -3004,7 +3004,7 @@
         <v>2</v>
       </c>
       <c r="D76" s="9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E76" s="10">
         <v>4</v>
@@ -3025,7 +3025,7 @@
         <v>3</v>
       </c>
       <c r="D77" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E77" s="10">
         <v>6</v>
@@ -3046,7 +3046,7 @@
         <v>4</v>
       </c>
       <c r="D78" s="9">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E78" s="10">
         <v>8</v>
@@ -3107,7 +3107,7 @@
         <v>2</v>
       </c>
       <c r="D81" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E81" s="6">
         <v>4</v>
@@ -3128,7 +3128,7 @@
         <v>3</v>
       </c>
       <c r="D82" s="5">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E82" s="6">
         <v>6</v>
@@ -3149,7 +3149,7 @@
         <v>4</v>
       </c>
       <c r="D83" s="5">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E83" s="6">
         <v>8</v>
@@ -3189,7 +3189,7 @@
         <v>1</v>
       </c>
       <c r="D85" s="9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E85" s="10">
         <v>2</v>
@@ -3210,7 +3210,7 @@
         <v>2</v>
       </c>
       <c r="D86" s="9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E86" s="10">
         <v>4</v>
@@ -3231,7 +3231,7 @@
         <v>3</v>
       </c>
       <c r="D87" s="9">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E87" s="10">
         <v>6</v>
@@ -3252,7 +3252,7 @@
         <v>4</v>
       </c>
       <c r="D88" s="9">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E88" s="10">
         <v>8</v>
@@ -3292,7 +3292,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E90" s="10">
         <v>2</v>
@@ -3334,7 +3334,7 @@
         <v>3</v>
       </c>
       <c r="D92" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E92" s="10">
         <v>6</v>
@@ -3355,7 +3355,7 @@
         <v>4</v>
       </c>
       <c r="D93" s="9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E93" s="10">
         <v>8</v>
@@ -3395,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="D95" s="9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E95" s="10">
         <v>2</v>
@@ -3416,7 +3416,7 @@
         <v>2</v>
       </c>
       <c r="D96" s="9">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E96" s="10">
         <v>4</v>
@@ -3437,7 +3437,7 @@
         <v>3</v>
       </c>
       <c r="D97" s="9">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E97" s="10">
         <v>6</v>
@@ -3458,7 +3458,7 @@
         <v>4</v>
       </c>
       <c r="D98" s="9">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="E98" s="10">
         <v>8</v>
@@ -3498,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="9">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E100" s="10">
         <v>2</v>
@@ -3519,7 +3519,7 @@
         <v>2</v>
       </c>
       <c r="D101" s="9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E101" s="10">
         <v>4</v>
@@ -3540,7 +3540,7 @@
         <v>3</v>
       </c>
       <c r="D102" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E102" s="10">
         <v>6</v>
@@ -3561,7 +3561,7 @@
         <v>4</v>
       </c>
       <c r="D103" s="9">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E103" s="10">
         <v>8</v>
@@ -3600,7 +3600,7 @@
       <c r="C105" s="8">
         <v>1</v>
       </c>
-      <c r="D105" s="9">
+      <c r="D105" s="5">
         <v>10</v>
       </c>
       <c r="E105" s="10">
@@ -3621,8 +3621,8 @@
       <c r="C106" s="8">
         <v>2</v>
       </c>
-      <c r="D106" s="9">
-        <v>30</v>
+      <c r="D106" s="5">
+        <v>20</v>
       </c>
       <c r="E106" s="10">
         <v>4</v>
@@ -3642,8 +3642,8 @@
       <c r="C107" s="8">
         <v>3</v>
       </c>
-      <c r="D107" s="9">
-        <v>60</v>
+      <c r="D107" s="5">
+        <v>30</v>
       </c>
       <c r="E107" s="10">
         <v>6</v>
@@ -3663,8 +3663,8 @@
       <c r="C108" s="8">
         <v>4</v>
       </c>
-      <c r="D108" s="9">
-        <v>100</v>
+      <c r="D108" s="5">
+        <v>40</v>
       </c>
       <c r="E108" s="10">
         <v>8</v>
@@ -3684,7 +3684,7 @@
       <c r="C109" s="8">
         <v>5</v>
       </c>
-      <c r="D109" s="8"/>
+      <c r="D109" s="4"/>
       <c r="E109" s="10">
         <v>10</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E110" s="10">
         <v>2</v>
@@ -3725,7 +3725,7 @@
         <v>2</v>
       </c>
       <c r="D111" s="9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E111" s="10">
         <v>4</v>
@@ -3746,7 +3746,7 @@
         <v>3</v>
       </c>
       <c r="D112" s="9">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E112" s="10">
         <v>6</v>
@@ -3767,7 +3767,7 @@
         <v>4</v>
       </c>
       <c r="D113" s="9">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E113" s="10">
         <v>8</v>
@@ -3807,7 +3807,7 @@
         <v>1</v>
       </c>
       <c r="D115" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E115" s="10">
         <v>2</v>
@@ -3849,7 +3849,7 @@
         <v>3</v>
       </c>
       <c r="D117" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E117" s="10">
         <v>6</v>
@@ -3870,7 +3870,7 @@
         <v>4</v>
       </c>
       <c r="D118" s="9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E118" s="10">
         <v>8</v>
@@ -3910,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E120" s="10">
         <v>2</v>
@@ -3931,7 +3931,7 @@
         <v>2</v>
       </c>
       <c r="D121" s="9">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E121" s="10">
         <v>4</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="D122" s="9">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E122" s="10">
         <v>6</v>
@@ -3973,7 +3973,7 @@
         <v>4</v>
       </c>
       <c r="D123" s="9">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="E123" s="10">
         <v>8</v>
@@ -4013,7 +4013,7 @@
         <v>1</v>
       </c>
       <c r="D125" s="9">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E125" s="10">
         <v>2</v>
@@ -4034,7 +4034,7 @@
         <v>2</v>
       </c>
       <c r="D126" s="9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E126" s="10">
         <v>4</v>
@@ -4055,7 +4055,7 @@
         <v>3</v>
       </c>
       <c r="D127" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E127" s="10">
         <v>6</v>
@@ -4076,7 +4076,7 @@
         <v>4</v>
       </c>
       <c r="D128" s="9">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E128" s="10">
         <v>8</v>
@@ -4115,7 +4115,7 @@
       <c r="C130" s="8">
         <v>1</v>
       </c>
-      <c r="D130" s="9">
+      <c r="D130" s="5">
         <v>10</v>
       </c>
       <c r="E130" s="10">
@@ -4136,8 +4136,8 @@
       <c r="C131" s="8">
         <v>2</v>
       </c>
-      <c r="D131" s="9">
-        <v>30</v>
+      <c r="D131" s="5">
+        <v>20</v>
       </c>
       <c r="E131" s="10">
         <v>4</v>
@@ -4157,8 +4157,8 @@
       <c r="C132" s="8">
         <v>3</v>
       </c>
-      <c r="D132" s="9">
-        <v>60</v>
+      <c r="D132" s="5">
+        <v>30</v>
       </c>
       <c r="E132" s="10">
         <v>6</v>
@@ -4178,8 +4178,8 @@
       <c r="C133" s="8">
         <v>4</v>
       </c>
-      <c r="D133" s="9">
-        <v>100</v>
+      <c r="D133" s="5">
+        <v>40</v>
       </c>
       <c r="E133" s="10">
         <v>8</v>
@@ -4199,7 +4199,7 @@
       <c r="C134" s="8">
         <v>5</v>
       </c>
-      <c r="D134" s="8"/>
+      <c r="D134" s="4"/>
       <c r="E134" s="10">
         <v>10</v>
       </c>
@@ -4219,7 +4219,7 @@
         <v>1</v>
       </c>
       <c r="D135" s="9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E135" s="10">
         <v>2</v>
@@ -4240,7 +4240,7 @@
         <v>2</v>
       </c>
       <c r="D136" s="9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E136" s="10">
         <v>4</v>
@@ -4261,7 +4261,7 @@
         <v>3</v>
       </c>
       <c r="D137" s="9">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E137" s="10">
         <v>6</v>
@@ -4282,7 +4282,7 @@
         <v>4</v>
       </c>
       <c r="D138" s="9">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E138" s="10">
         <v>8</v>
@@ -4322,7 +4322,7 @@
         <v>1</v>
       </c>
       <c r="D140" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E140" s="10">
         <v>2</v>
@@ -4364,7 +4364,7 @@
         <v>3</v>
       </c>
       <c r="D142" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E142" s="10">
         <v>6</v>
@@ -4385,7 +4385,7 @@
         <v>4</v>
       </c>
       <c r="D143" s="9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E143" s="10">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1</v>
       </c>
       <c r="D145" s="9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E145" s="10">
         <v>2</v>
@@ -4446,7 +4446,7 @@
         <v>2</v>
       </c>
       <c r="D146" s="9">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E146" s="10">
         <v>4</v>
@@ -4467,7 +4467,7 @@
         <v>3</v>
       </c>
       <c r="D147" s="9">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E147" s="10">
         <v>6</v>
@@ -4488,7 +4488,7 @@
         <v>4</v>
       </c>
       <c r="D148" s="9">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="E148" s="10">
         <v>8</v>
@@ -4528,7 +4528,7 @@
         <v>1</v>
       </c>
       <c r="D150" s="9">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E150" s="10">
         <v>2</v>
@@ -4549,7 +4549,7 @@
         <v>2</v>
       </c>
       <c r="D151" s="9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E151" s="10">
         <v>4</v>
@@ -4570,7 +4570,7 @@
         <v>3</v>
       </c>
       <c r="D152" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E152" s="10">
         <v>6</v>
@@ -4591,7 +4591,7 @@
         <v>4</v>
       </c>
       <c r="D153" s="9">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E153" s="10">
         <v>8</v>

--- a/hall/resources/sample/EmployeeStar.xlsx
+++ b/hall/resources/sample/EmployeeStar.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -44,15 +44,9 @@
     <t>等级上限</t>
   </si>
   <si>
-    <t>主管加成</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
-    <t>Map&lt;int{_}int&gt;{|}</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -68,175 +62,184 @@
     <t>LevelCap</t>
   </si>
   <si>
-    <t>SupervisorBonus</t>
+    <t>3_50</t>
+  </si>
+  <si>
+    <t>5_50</t>
+  </si>
+  <si>
+    <t>6_50</t>
+  </si>
+  <si>
+    <t>3_80</t>
+  </si>
+  <si>
+    <t>5_80</t>
+  </si>
+  <si>
+    <t>6_80</t>
+  </si>
+  <si>
+    <t>3_110</t>
+  </si>
+  <si>
+    <t>5_110</t>
+  </si>
+  <si>
+    <t>6_110</t>
+  </si>
+  <si>
+    <t>3_140</t>
+  </si>
+  <si>
+    <t>5_140</t>
+  </si>
+  <si>
+    <t>6_140</t>
+  </si>
+  <si>
+    <t>3_170</t>
+  </si>
+  <si>
+    <t>5_170</t>
+  </si>
+  <si>
+    <t>6_170</t>
+  </si>
+  <si>
+    <t>3_120</t>
+  </si>
+  <si>
+    <t>5_120</t>
+  </si>
+  <si>
+    <t>6_120</t>
+  </si>
+  <si>
+    <t>3_160</t>
+  </si>
+  <si>
+    <t>5_160</t>
+  </si>
+  <si>
+    <t>6_160</t>
   </si>
   <si>
     <t>3_200</t>
   </si>
   <si>
-    <t>3_400</t>
-  </si>
-  <si>
-    <t>3_600</t>
-  </si>
-  <si>
-    <t>3_800</t>
-  </si>
-  <si>
-    <t>3_1000</t>
+    <t>5_200</t>
+  </si>
+  <si>
+    <t>6_200</t>
+  </si>
+  <si>
+    <t>3_240</t>
+  </si>
+  <si>
+    <t>5_240</t>
+  </si>
+  <si>
+    <t>6_240</t>
+  </si>
+  <si>
+    <t>3_100</t>
+  </si>
+  <si>
+    <t>5_100</t>
+  </si>
+  <si>
+    <t>6_100</t>
+  </si>
+  <si>
+    <t>3_150</t>
+  </si>
+  <si>
+    <t>5_150</t>
+  </si>
+  <si>
+    <t>6_150</t>
+  </si>
+  <si>
+    <t>3_250</t>
+  </si>
+  <si>
+    <t>5_250</t>
+  </si>
+  <si>
+    <t>6_250</t>
   </si>
   <si>
     <t>3_300</t>
   </si>
   <si>
-    <t>3_900</t>
-  </si>
-  <si>
-    <t>3_1200</t>
-  </si>
-  <si>
-    <t>3_1500</t>
-  </si>
-  <si>
-    <t>3_1600</t>
-  </si>
-  <si>
-    <t>3_2000</t>
-  </si>
-  <si>
-    <t>3_500</t>
-  </si>
-  <si>
-    <t>3_2500</t>
-  </si>
-  <si>
-    <t>3_1800</t>
-  </si>
-  <si>
-    <t>3_2400</t>
-  </si>
-  <si>
-    <t>3_3000</t>
-  </si>
-  <si>
-    <t>5_100</t>
-  </si>
-  <si>
-    <t>5_150</t>
-  </si>
-  <si>
-    <t>5_200</t>
-  </si>
-  <si>
-    <t>5_250</t>
-  </si>
-  <si>
     <t>5_300</t>
   </si>
   <si>
-    <t>5_180</t>
-  </si>
-  <si>
-    <t>5_240</t>
-  </si>
-  <si>
-    <t>5_360</t>
-  </si>
-  <si>
-    <t>5_420</t>
-  </si>
-  <si>
-    <t>5_280</t>
+    <t>6_300</t>
+  </si>
+  <si>
+    <t>3_260</t>
+  </si>
+  <si>
+    <t>5_260</t>
+  </si>
+  <si>
+    <t>6_260</t>
+  </si>
+  <si>
+    <t>3_320</t>
+  </si>
+  <si>
+    <t>5_320</t>
+  </si>
+  <si>
+    <t>6_320</t>
+  </si>
+  <si>
+    <t>3_380</t>
+  </si>
+  <si>
+    <t>5_380</t>
+  </si>
+  <si>
+    <t>6_380</t>
+  </si>
+  <si>
+    <t>3_440</t>
   </si>
   <si>
     <t>5_440</t>
   </si>
   <si>
-    <t>5_520</t>
-  </si>
-  <si>
-    <t>5_400</t>
-  </si>
-  <si>
-    <t>5_500</t>
-  </si>
-  <si>
-    <t>5_600</t>
-  </si>
-  <si>
-    <t>5_700</t>
-  </si>
-  <si>
-    <t>5_650</t>
-  </si>
-  <si>
-    <t>5_800</t>
-  </si>
-  <si>
-    <t>5_950</t>
-  </si>
-  <si>
-    <t>5_1100</t>
-  </si>
-  <si>
-    <t>4_50</t>
-  </si>
-  <si>
-    <t>4_80</t>
-  </si>
-  <si>
-    <t>4_110</t>
-  </si>
-  <si>
-    <t>4_140</t>
-  </si>
-  <si>
-    <t>4_170</t>
-  </si>
-  <si>
-    <t>4_120</t>
-  </si>
-  <si>
-    <t>4_160</t>
-  </si>
-  <si>
-    <t>4_200</t>
-  </si>
-  <si>
-    <t>4_240</t>
-  </si>
-  <si>
-    <t>4_100</t>
-  </si>
-  <si>
-    <t>4_150</t>
-  </si>
-  <si>
-    <t>4_250</t>
-  </si>
-  <si>
-    <t>4_300</t>
-  </si>
-  <si>
-    <t>4_260</t>
-  </si>
-  <si>
-    <t>4_320</t>
-  </si>
-  <si>
-    <t>4_380</t>
-  </si>
-  <si>
-    <t>4_440</t>
-  </si>
-  <si>
-    <t>4_460</t>
-  </si>
-  <si>
-    <t>4_540</t>
-  </si>
-  <si>
-    <t>4_620</t>
+    <t>6_440</t>
+  </si>
+  <si>
+    <t>3_460</t>
+  </si>
+  <si>
+    <t>5_460</t>
+  </si>
+  <si>
+    <t>6_460</t>
+  </si>
+  <si>
+    <t>3_540</t>
+  </si>
+  <si>
+    <t>5_540</t>
+  </si>
+  <si>
+    <t>6_540</t>
+  </si>
+  <si>
+    <t>3_620</t>
+  </si>
+  <si>
+    <t>5_620</t>
+  </si>
+  <si>
+    <t>6_620</t>
   </si>
 </sst>
 </file>
@@ -402,7 +405,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,18 +415,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -761,7 +752,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -785,16 +776,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -803,89 +794,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -907,9 +898,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -919,10 +907,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1450,18 +1435,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F154"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:K154"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
     <col min="2" max="2" width="12.375" customWidth="1"/>
     <col min="3" max="3" width="11.25" customWidth="1"/>
     <col min="4" max="4" width="13.875" customWidth="1"/>
     <col min="5" max="5" width="10.75" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1477,59 +1461,49 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="3">
         <f>B5*100+C5</f>
         <v>10100101</v>
@@ -1546,11 +1520,8 @@
       <c r="E5" s="6">
         <v>2</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="3">
         <f t="shared" ref="A6:A37" si="0">B6*100+C6</f>
         <v>10100102</v>
@@ -1567,11 +1538,8 @@
       <c r="E6" s="6">
         <v>4</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>10100103</v>
@@ -1588,11 +1556,8 @@
       <c r="E7" s="6">
         <v>6</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>10100104</v>
@@ -1609,11 +1574,8 @@
       <c r="E8" s="6">
         <v>8</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>10100105</v>
@@ -1628,11 +1590,8 @@
       <c r="E9" s="6">
         <v>10</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>10200201</v>
@@ -1640,20 +1599,17 @@
       <c r="B10" s="1">
         <v>102002</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>1</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>15</v>
       </c>
-      <c r="E10" s="10">
-        <v>2</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="E10" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>10200202</v>
@@ -1661,20 +1617,17 @@
       <c r="B11" s="1">
         <v>102002</v>
       </c>
-      <c r="C11" s="8">
-        <v>2</v>
-      </c>
-      <c r="D11" s="9">
+      <c r="C11" s="7">
+        <v>2</v>
+      </c>
+      <c r="D11" s="8">
         <v>25</v>
       </c>
-      <c r="E11" s="10">
-        <v>4</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="E11" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>10200203</v>
@@ -1682,20 +1635,17 @@
       <c r="B12" s="1">
         <v>102002</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>3</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>35</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>6</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>10200204</v>
@@ -1703,20 +1653,17 @@
       <c r="B13" s="1">
         <v>102002</v>
       </c>
-      <c r="C13" s="8">
-        <v>4</v>
-      </c>
-      <c r="D13" s="9">
+      <c r="C13" s="7">
+        <v>4</v>
+      </c>
+      <c r="D13" s="8">
         <v>45</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <v>8</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>10200205</v>
@@ -1724,1357 +1671,1384 @@
       <c r="B14" s="1">
         <v>102002</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>5</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10">
+      <c r="D14" s="7"/>
+      <c r="E14" s="9">
         <v>10</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>10300301</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>103003</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>1</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>20</v>
       </c>
-      <c r="E15" s="10">
-        <v>2</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="E15" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>10300302</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>103003</v>
       </c>
-      <c r="C16" s="8">
-        <v>2</v>
-      </c>
-      <c r="D16" s="9">
+      <c r="C16" s="7">
+        <v>2</v>
+      </c>
+      <c r="D16" s="8">
         <v>30</v>
       </c>
-      <c r="E16" s="10">
-        <v>4</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="E16" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>10300303</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>103003</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>3</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>40</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>6</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>10300304</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>103003</v>
       </c>
-      <c r="C18" s="8">
-        <v>4</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="C18" s="7">
+        <v>4</v>
+      </c>
+      <c r="D18" s="8">
         <v>50</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>8</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>10300305</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <v>103003</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>5</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="10">
+      <c r="D19" s="7"/>
+      <c r="E19" s="9">
         <v>10</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>10400401</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="7">
         <v>104004</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <v>1</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>25</v>
       </c>
-      <c r="E20" s="10">
-        <v>2</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="E20" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>10400402</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="7">
         <v>104004</v>
       </c>
-      <c r="C21" s="8">
-        <v>2</v>
-      </c>
-      <c r="D21" s="9">
+      <c r="C21" s="7">
+        <v>2</v>
+      </c>
+      <c r="D21" s="8">
         <v>35</v>
       </c>
-      <c r="E21" s="10">
-        <v>4</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="E21" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>10400403</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="7">
         <v>104004</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="7">
         <v>3</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>45</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <v>6</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>10400404</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="7">
         <v>104004</v>
       </c>
-      <c r="C23" s="8">
-        <v>4</v>
-      </c>
-      <c r="D23" s="9">
+      <c r="C23" s="7">
+        <v>4</v>
+      </c>
+      <c r="D23" s="8">
         <v>55</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <v>8</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>10400405</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="7">
         <v>104004</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="7">
         <v>5</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="10">
+      <c r="D24" s="7"/>
+      <c r="E24" s="9">
         <v>10</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>10500501</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="7">
         <v>105005</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="7">
         <v>1</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="8">
         <v>30</v>
       </c>
-      <c r="E25" s="10">
-        <v>2</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="E25" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>10500502</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="7">
         <v>105005</v>
       </c>
-      <c r="C26" s="8">
-        <v>2</v>
-      </c>
-      <c r="D26" s="9">
+      <c r="C26" s="7">
+        <v>2</v>
+      </c>
+      <c r="D26" s="8">
         <v>40</v>
       </c>
-      <c r="E26" s="10">
-        <v>4</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="E26" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>10500503</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="7">
         <v>105005</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>3</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="8">
         <v>50</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="9">
         <v>6</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>10500504</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="7">
         <v>105005</v>
       </c>
-      <c r="C28" s="8">
-        <v>4</v>
-      </c>
-      <c r="D28" s="9">
+      <c r="C28" s="7">
+        <v>4</v>
+      </c>
+      <c r="D28" s="8">
         <v>60</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <v>8</v>
       </c>
-      <c r="F28" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>10500505</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <v>105005</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="7">
         <v>5</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="10">
+      <c r="D29" s="7"/>
+      <c r="E29" s="9">
         <v>10</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>20100601</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="7">
         <v>201006</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="7">
         <v>1</v>
       </c>
       <c r="D30" s="5">
         <v>10</v>
       </c>
-      <c r="E30" s="10">
-        <v>2</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="E30" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>20100602</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="7">
         <v>201006</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="7">
         <v>2</v>
       </c>
       <c r="D31" s="5">
         <v>20</v>
       </c>
-      <c r="E31" s="10">
-        <v>4</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="E31" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>20100603</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="7">
         <v>201006</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="7">
         <v>3</v>
       </c>
       <c r="D32" s="5">
         <v>30</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="9">
         <v>6</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>20100604</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="7">
         <v>201006</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="7">
         <v>4</v>
       </c>
       <c r="D33" s="5">
         <v>40</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="9">
         <v>8</v>
       </c>
-      <c r="F33" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>20100605</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="7">
         <v>201006</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="7">
         <v>5</v>
       </c>
       <c r="D34" s="4"/>
-      <c r="E34" s="10">
+      <c r="E34" s="9">
         <v>10</v>
       </c>
-      <c r="F34" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>20200701</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="7">
         <v>202007</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="7">
         <v>1</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="8">
         <v>15</v>
       </c>
-      <c r="E35" s="10">
-        <v>2</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="E35" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="3">
         <f t="shared" si="0"/>
         <v>20200702</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="7">
         <v>202007</v>
       </c>
-      <c r="C36" s="8">
-        <v>2</v>
-      </c>
-      <c r="D36" s="9">
+      <c r="C36" s="7">
+        <v>2</v>
+      </c>
+      <c r="D36" s="8">
         <v>25</v>
       </c>
-      <c r="E36" s="10">
-        <v>4</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="E36" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="3">
         <f t="shared" si="0"/>
         <v>20200703</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="7">
         <v>202007</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="7">
         <v>3</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="8">
         <v>35</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="9">
         <v>6</v>
       </c>
-      <c r="F37" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="3">
         <f t="shared" ref="A38:A79" si="1">B38*100+C38</f>
         <v>20200704</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="7">
         <v>202007</v>
       </c>
-      <c r="C38" s="8">
-        <v>4</v>
-      </c>
-      <c r="D38" s="9">
+      <c r="C38" s="7">
+        <v>4</v>
+      </c>
+      <c r="D38" s="8">
         <v>45</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="9">
         <v>8</v>
       </c>
-      <c r="F38" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="3">
         <f t="shared" si="1"/>
         <v>20200705</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="7">
         <v>202007</v>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="7">
         <v>5</v>
       </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="10">
+      <c r="D39" s="7"/>
+      <c r="E39" s="9">
         <v>10</v>
       </c>
-      <c r="F39" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>20300801</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="7">
         <v>203008</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="7">
         <v>1</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="8">
         <v>20</v>
       </c>
-      <c r="E40" s="10">
-        <v>2</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="E40" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="3">
         <f t="shared" si="1"/>
         <v>20300802</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="7">
         <v>203008</v>
       </c>
-      <c r="C41" s="8">
-        <v>2</v>
-      </c>
-      <c r="D41" s="9">
+      <c r="C41" s="7">
+        <v>2</v>
+      </c>
+      <c r="D41" s="8">
         <v>30</v>
       </c>
-      <c r="E41" s="10">
-        <v>4</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="E41" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" s="3">
         <f t="shared" si="1"/>
         <v>20300803</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="7">
         <v>203008</v>
       </c>
-      <c r="C42" s="8">
+      <c r="C42" s="7">
         <v>3</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="8">
         <v>40</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="9">
         <v>6</v>
       </c>
-      <c r="F42" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="3">
         <f t="shared" si="1"/>
         <v>20300804</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="7">
         <v>203008</v>
       </c>
-      <c r="C43" s="8">
-        <v>4</v>
-      </c>
-      <c r="D43" s="9">
+      <c r="C43" s="7">
+        <v>4</v>
+      </c>
+      <c r="D43" s="8">
         <v>50</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="9">
         <v>8</v>
       </c>
-      <c r="F43" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" s="3">
         <f t="shared" si="1"/>
         <v>20300805</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="7">
         <v>203008</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="7">
         <v>5</v>
       </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="10">
+      <c r="D44" s="7"/>
+      <c r="E44" s="9">
         <v>10</v>
       </c>
-      <c r="F44" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" s="3">
         <f t="shared" si="1"/>
         <v>20400901</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="7">
         <v>204009</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="7">
         <v>1</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="8">
         <v>25</v>
       </c>
-      <c r="E45" s="10">
-        <v>2</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="E45" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" s="3">
         <f t="shared" si="1"/>
         <v>20400902</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="7">
         <v>204009</v>
       </c>
-      <c r="C46" s="8">
-        <v>2</v>
-      </c>
-      <c r="D46" s="9">
+      <c r="C46" s="7">
+        <v>2</v>
+      </c>
+      <c r="D46" s="8">
         <v>35</v>
       </c>
-      <c r="E46" s="10">
-        <v>4</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="E46" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" s="3">
         <f t="shared" si="1"/>
         <v>20400903</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="7">
         <v>204009</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C47" s="7">
         <v>3</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="8">
         <v>45</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="9">
         <v>6</v>
       </c>
-      <c r="F47" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" s="3">
         <f t="shared" si="1"/>
         <v>20400904</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="7">
         <v>204009</v>
       </c>
-      <c r="C48" s="8">
-        <v>4</v>
-      </c>
-      <c r="D48" s="9">
+      <c r="C48" s="7">
+        <v>4</v>
+      </c>
+      <c r="D48" s="8">
         <v>55</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E48" s="9">
         <v>8</v>
       </c>
-      <c r="F48" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="3">
         <f t="shared" si="1"/>
         <v>20400905</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="7">
         <v>204009</v>
       </c>
-      <c r="C49" s="8">
+      <c r="C49" s="7">
         <v>5</v>
       </c>
-      <c r="D49" s="8"/>
-      <c r="E49" s="10">
+      <c r="D49" s="7"/>
+      <c r="E49" s="9">
         <v>10</v>
       </c>
-      <c r="F49" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="3">
         <f t="shared" si="1"/>
         <v>20501001</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="7">
         <v>205010</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="7">
         <v>1</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="8">
         <v>30</v>
       </c>
-      <c r="E50" s="10">
-        <v>2</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="E50" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="3">
         <f t="shared" si="1"/>
         <v>20501002</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="7">
         <v>205010</v>
       </c>
-      <c r="C51" s="8">
-        <v>2</v>
-      </c>
-      <c r="D51" s="9">
+      <c r="C51" s="7">
+        <v>2</v>
+      </c>
+      <c r="D51" s="8">
         <v>40</v>
       </c>
-      <c r="E51" s="10">
-        <v>4</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="E51" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" s="3">
         <f t="shared" si="1"/>
         <v>20501003</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="7">
         <v>205010</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="7">
         <v>3</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="8">
         <v>50</v>
       </c>
-      <c r="E52" s="10">
+      <c r="E52" s="9">
         <v>6</v>
       </c>
-      <c r="F52" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="3">
         <f t="shared" si="1"/>
         <v>20501004</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="7">
         <v>205010</v>
       </c>
-      <c r="C53" s="8">
-        <v>4</v>
-      </c>
-      <c r="D53" s="9">
+      <c r="C53" s="7">
+        <v>4</v>
+      </c>
+      <c r="D53" s="8">
         <v>60</v>
       </c>
-      <c r="E53" s="10">
+      <c r="E53" s="9">
         <v>8</v>
       </c>
-      <c r="F53" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" s="3">
         <f t="shared" si="1"/>
         <v>20501005</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="7">
         <v>205010</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C54" s="7">
         <v>5</v>
       </c>
-      <c r="D54" s="8"/>
-      <c r="E54" s="10">
+      <c r="D54" s="7"/>
+      <c r="E54" s="9">
         <v>10</v>
       </c>
-      <c r="F54" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" s="3">
         <f t="shared" si="1"/>
         <v>30101101</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="7">
         <v>301011</v>
       </c>
-      <c r="C55" s="8">
+      <c r="C55" s="7">
         <v>1</v>
       </c>
       <c r="D55" s="5">
         <v>10</v>
       </c>
-      <c r="E55" s="10">
-        <v>2</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="E55" s="9">
+        <v>2</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J55" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K55" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" s="3">
         <f t="shared" si="1"/>
         <v>30101102</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="7">
         <v>301011</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C56" s="7">
         <v>2</v>
       </c>
       <c r="D56" s="5">
         <v>20</v>
       </c>
-      <c r="E56" s="10">
-        <v>4</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="E56" s="9">
+        <v>4</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K56" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" s="3">
         <f t="shared" si="1"/>
         <v>30101103</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="7">
         <v>301011</v>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="7">
         <v>3</v>
       </c>
       <c r="D57" s="5">
         <v>30</v>
       </c>
-      <c r="E57" s="10">
+      <c r="E57" s="9">
         <v>6</v>
       </c>
-      <c r="F57" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="I57" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="3">
         <f t="shared" si="1"/>
         <v>30101104</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="7">
         <v>301011</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="7">
         <v>4</v>
       </c>
       <c r="D58" s="5">
         <v>40</v>
       </c>
-      <c r="E58" s="10">
+      <c r="E58" s="9">
         <v>8</v>
       </c>
-      <c r="F58" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="I58" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K58" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" s="3">
         <f t="shared" si="1"/>
         <v>30101105</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="7">
         <v>301011</v>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="7">
         <v>5</v>
       </c>
       <c r="D59" s="4"/>
-      <c r="E59" s="10">
+      <c r="E59" s="9">
         <v>10</v>
       </c>
-      <c r="F59" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="I59" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" s="3">
         <f t="shared" si="1"/>
         <v>30201201</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="7">
         <v>302012</v>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="7">
         <v>1</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="8">
         <v>15</v>
       </c>
-      <c r="E60" s="10">
-        <v>2</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="E60" s="9">
+        <v>2</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" s="3">
         <f t="shared" si="1"/>
         <v>30201202</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="7">
         <v>302012</v>
       </c>
-      <c r="C61" s="8">
-        <v>2</v>
-      </c>
-      <c r="D61" s="9">
+      <c r="C61" s="7">
+        <v>2</v>
+      </c>
+      <c r="D61" s="8">
         <v>25</v>
       </c>
-      <c r="E61" s="10">
-        <v>4</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="E61" s="9">
+        <v>4</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J61" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" s="3">
         <f t="shared" si="1"/>
         <v>30201203</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="7">
         <v>302012</v>
       </c>
-      <c r="C62" s="8">
+      <c r="C62" s="7">
         <v>3</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="8">
         <v>35</v>
       </c>
-      <c r="E62" s="10">
+      <c r="E62" s="9">
         <v>6</v>
       </c>
-      <c r="F62" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="I62" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J62" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K62" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" s="3">
         <f t="shared" si="1"/>
         <v>30201204</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="7">
         <v>302012</v>
       </c>
-      <c r="C63" s="8">
-        <v>4</v>
-      </c>
-      <c r="D63" s="9">
+      <c r="C63" s="7">
+        <v>4</v>
+      </c>
+      <c r="D63" s="8">
         <v>45</v>
       </c>
-      <c r="E63" s="10">
+      <c r="E63" s="9">
         <v>8</v>
       </c>
-      <c r="F63" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="I63" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J63" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" s="3">
         <f t="shared" si="1"/>
         <v>30201205</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B64" s="7">
         <v>302012</v>
       </c>
-      <c r="C64" s="8">
+      <c r="C64" s="7">
         <v>5</v>
       </c>
-      <c r="D64" s="8"/>
-      <c r="E64" s="10">
+      <c r="D64" s="7"/>
+      <c r="E64" s="9">
         <v>10</v>
       </c>
-      <c r="F64" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="I64" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J64" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K64" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65" s="3">
         <f t="shared" si="1"/>
         <v>30301301</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="9">
         <v>303013</v>
       </c>
-      <c r="C65" s="8">
+      <c r="C65" s="7">
         <v>1</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="8">
         <v>20</v>
       </c>
-      <c r="E65" s="10">
-        <v>2</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="E65" s="9">
+        <v>2</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J65" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" s="3">
         <f t="shared" si="1"/>
         <v>30301302</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="9">
         <v>303013</v>
       </c>
-      <c r="C66" s="8">
-        <v>2</v>
-      </c>
-      <c r="D66" s="9">
+      <c r="C66" s="7">
+        <v>2</v>
+      </c>
+      <c r="D66" s="8">
         <v>30</v>
       </c>
-      <c r="E66" s="10">
-        <v>4</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="E66" s="9">
+        <v>4</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J66" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="K66" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67" s="3">
         <f t="shared" si="1"/>
         <v>30301303</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="9">
         <v>303013</v>
       </c>
-      <c r="C67" s="8">
+      <c r="C67" s="7">
         <v>3</v>
       </c>
-      <c r="D67" s="9">
+      <c r="D67" s="8">
         <v>40</v>
       </c>
-      <c r="E67" s="10">
+      <c r="E67" s="9">
         <v>6</v>
       </c>
-      <c r="F67" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="I67" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J67" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K67" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" s="3">
         <f t="shared" si="1"/>
         <v>30301304</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="9">
         <v>303013</v>
       </c>
-      <c r="C68" s="8">
-        <v>4</v>
-      </c>
-      <c r="D68" s="9">
+      <c r="C68" s="7">
+        <v>4</v>
+      </c>
+      <c r="D68" s="8">
         <v>50</v>
       </c>
-      <c r="E68" s="10">
+      <c r="E68" s="9">
         <v>8</v>
       </c>
-      <c r="F68" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="I68" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K68" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" s="3">
         <f t="shared" si="1"/>
         <v>30301305</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="9">
         <v>303013</v>
       </c>
-      <c r="C69" s="8">
+      <c r="C69" s="7">
         <v>5</v>
       </c>
-      <c r="D69" s="8"/>
-      <c r="E69" s="10">
+      <c r="D69" s="7"/>
+      <c r="E69" s="9">
         <v>10</v>
       </c>
-      <c r="F69" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="I69" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J69" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K69" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" s="3">
         <f t="shared" si="1"/>
         <v>30401401</v>
       </c>
-      <c r="B70" s="8">
+      <c r="B70" s="7">
         <v>304014</v>
       </c>
-      <c r="C70" s="8">
+      <c r="C70" s="7">
         <v>1</v>
       </c>
-      <c r="D70" s="9">
+      <c r="D70" s="8">
         <v>25</v>
       </c>
-      <c r="E70" s="10">
-        <v>2</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="E70" s="9">
+        <v>2</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J70" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K70" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" s="3">
         <f t="shared" si="1"/>
         <v>30401402</v>
       </c>
-      <c r="B71" s="8">
+      <c r="B71" s="7">
         <v>304014</v>
       </c>
-      <c r="C71" s="8">
-        <v>2</v>
-      </c>
-      <c r="D71" s="9">
+      <c r="C71" s="7">
+        <v>2</v>
+      </c>
+      <c r="D71" s="8">
         <v>35</v>
       </c>
-      <c r="E71" s="10">
-        <v>4</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="E71" s="9">
+        <v>4</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J71" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="K71" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" s="3">
         <f t="shared" si="1"/>
         <v>30401403</v>
       </c>
-      <c r="B72" s="8">
+      <c r="B72" s="7">
         <v>304014</v>
       </c>
-      <c r="C72" s="8">
+      <c r="C72" s="7">
         <v>3</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="8">
         <v>45</v>
       </c>
-      <c r="E72" s="10">
+      <c r="E72" s="9">
         <v>6</v>
       </c>
-      <c r="F72" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="I72" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="K72" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" s="3">
         <f t="shared" si="1"/>
         <v>30401404</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="7">
         <v>304014</v>
       </c>
-      <c r="C73" s="8">
-        <v>4</v>
-      </c>
-      <c r="D73" s="9">
+      <c r="C73" s="7">
+        <v>4</v>
+      </c>
+      <c r="D73" s="8">
         <v>55</v>
       </c>
-      <c r="E73" s="10">
+      <c r="E73" s="9">
         <v>8</v>
       </c>
-      <c r="F73" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="I73" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J73" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" s="3">
         <f t="shared" si="1"/>
         <v>30401405</v>
       </c>
-      <c r="B74" s="8">
+      <c r="B74" s="7">
         <v>304014</v>
       </c>
-      <c r="C74" s="8">
+      <c r="C74" s="7">
         <v>5</v>
       </c>
-      <c r="D74" s="8"/>
-      <c r="E74" s="10">
+      <c r="D74" s="7"/>
+      <c r="E74" s="9">
         <v>10</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="I74" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J74" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="K74" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" s="3">
         <f t="shared" si="1"/>
         <v>30501501</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="7">
         <v>305015</v>
       </c>
-      <c r="C75" s="8">
+      <c r="C75" s="7">
         <v>1</v>
       </c>
-      <c r="D75" s="9">
+      <c r="D75" s="8">
         <v>30</v>
       </c>
-      <c r="E75" s="10">
-        <v>2</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="E75" s="9">
+        <v>2</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J75" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K75" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" s="3">
         <f t="shared" si="1"/>
         <v>30501502</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="7">
         <v>305015</v>
       </c>
-      <c r="C76" s="8">
-        <v>2</v>
-      </c>
-      <c r="D76" s="9">
+      <c r="C76" s="7">
+        <v>2</v>
+      </c>
+      <c r="D76" s="8">
         <v>40</v>
       </c>
-      <c r="E76" s="10">
-        <v>4</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="E76" s="9">
+        <v>4</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J76" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="K76" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" s="3">
         <f t="shared" si="1"/>
         <v>30501503</v>
       </c>
-      <c r="B77" s="8">
+      <c r="B77" s="7">
         <v>305015</v>
       </c>
-      <c r="C77" s="8">
+      <c r="C77" s="7">
         <v>3</v>
       </c>
-      <c r="D77" s="9">
+      <c r="D77" s="8">
         <v>50</v>
       </c>
-      <c r="E77" s="10">
+      <c r="E77" s="9">
         <v>6</v>
       </c>
-      <c r="F77" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="I77" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J77" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K77" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" s="3">
         <f t="shared" si="1"/>
         <v>30501504</v>
       </c>
-      <c r="B78" s="8">
+      <c r="B78" s="7">
         <v>305015</v>
       </c>
-      <c r="C78" s="8">
-        <v>4</v>
-      </c>
-      <c r="D78" s="9">
+      <c r="C78" s="7">
+        <v>4</v>
+      </c>
+      <c r="D78" s="8">
         <v>60</v>
       </c>
-      <c r="E78" s="10">
+      <c r="E78" s="9">
         <v>8</v>
       </c>
-      <c r="F78" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="I78" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J78" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K78" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="3">
         <f t="shared" si="1"/>
         <v>30501505</v>
       </c>
-      <c r="B79" s="8">
+      <c r="B79" s="7">
         <v>305015</v>
       </c>
-      <c r="C79" s="8">
+      <c r="C79" s="7">
         <v>5</v>
       </c>
-      <c r="D79" s="8"/>
-      <c r="E79" s="10">
+      <c r="D79" s="7"/>
+      <c r="E79" s="9">
         <v>10</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="I79" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J79" s="10" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="K79" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="3">
         <f t="shared" ref="A80:A111" si="2">B80*100+C80</f>
         <v>10101601</v>
@@ -3091,11 +3065,8 @@
       <c r="E80" s="6">
         <v>2</v>
       </c>
-      <c r="F80" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" s="3">
         <f t="shared" si="2"/>
         <v>10101602</v>
@@ -3112,11 +3083,8 @@
       <c r="E81" s="6">
         <v>4</v>
       </c>
-      <c r="F81" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" s="3">
         <f t="shared" si="2"/>
         <v>10101603</v>
@@ -3133,11 +3101,8 @@
       <c r="E82" s="6">
         <v>6</v>
       </c>
-      <c r="F82" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" s="3">
         <f t="shared" si="2"/>
         <v>10101604</v>
@@ -3154,11 +3119,8 @@
       <c r="E83" s="6">
         <v>8</v>
       </c>
-      <c r="F83" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" s="3">
         <f t="shared" si="2"/>
         <v>10101605</v>
@@ -3173,11 +3135,8 @@
       <c r="E84" s="6">
         <v>10</v>
       </c>
-      <c r="F84" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" s="3">
         <f t="shared" si="2"/>
         <v>10201701</v>
@@ -3185,20 +3144,17 @@
       <c r="B85" s="1">
         <v>102017</v>
       </c>
-      <c r="C85" s="8">
+      <c r="C85" s="7">
         <v>1</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="8">
         <v>15</v>
       </c>
-      <c r="E85" s="10">
-        <v>2</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+      <c r="E85" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" s="3">
         <f t="shared" si="2"/>
         <v>10201702</v>
@@ -3206,20 +3162,17 @@
       <c r="B86" s="1">
         <v>102017</v>
       </c>
-      <c r="C86" s="8">
-        <v>2</v>
-      </c>
-      <c r="D86" s="9">
+      <c r="C86" s="7">
+        <v>2</v>
+      </c>
+      <c r="D86" s="8">
         <v>25</v>
       </c>
-      <c r="E86" s="10">
-        <v>4</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="E86" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" s="3">
         <f t="shared" si="2"/>
         <v>10201703</v>
@@ -3227,20 +3180,17 @@
       <c r="B87" s="1">
         <v>102017</v>
       </c>
-      <c r="C87" s="8">
+      <c r="C87" s="7">
         <v>3</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D87" s="8">
         <v>35</v>
       </c>
-      <c r="E87" s="10">
+      <c r="E87" s="9">
         <v>6</v>
       </c>
-      <c r="F87" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" s="3">
         <f t="shared" si="2"/>
         <v>10201704</v>
@@ -3248,20 +3198,17 @@
       <c r="B88" s="1">
         <v>102017</v>
       </c>
-      <c r="C88" s="8">
-        <v>4</v>
-      </c>
-      <c r="D88" s="9">
+      <c r="C88" s="7">
+        <v>4</v>
+      </c>
+      <c r="D88" s="8">
         <v>45</v>
       </c>
-      <c r="E88" s="10">
+      <c r="E88" s="9">
         <v>8</v>
       </c>
-      <c r="F88" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" s="3">
         <f t="shared" si="2"/>
         <v>10201705</v>
@@ -3269,1354 +3216,1156 @@
       <c r="B89" s="1">
         <v>102017</v>
       </c>
-      <c r="C89" s="8">
+      <c r="C89" s="7">
         <v>5</v>
       </c>
-      <c r="D89" s="8"/>
-      <c r="E89" s="10">
+      <c r="D89" s="7"/>
+      <c r="E89" s="9">
         <v>10</v>
       </c>
-      <c r="F89" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" s="3">
         <f t="shared" si="2"/>
         <v>10301801</v>
       </c>
-      <c r="B90" s="8">
+      <c r="B90" s="7">
         <v>103018</v>
       </c>
-      <c r="C90" s="8">
+      <c r="C90" s="7">
         <v>1</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="8">
         <v>20</v>
       </c>
-      <c r="E90" s="10">
-        <v>2</v>
-      </c>
-      <c r="F90" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+      <c r="E90" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" s="3">
         <f t="shared" si="2"/>
         <v>10301802</v>
       </c>
-      <c r="B91" s="8">
+      <c r="B91" s="7">
         <v>103018</v>
       </c>
-      <c r="C91" s="8">
-        <v>2</v>
-      </c>
-      <c r="D91" s="9">
+      <c r="C91" s="7">
+        <v>2</v>
+      </c>
+      <c r="D91" s="8">
         <v>30</v>
       </c>
-      <c r="E91" s="10">
-        <v>4</v>
-      </c>
-      <c r="F91" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="E91" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" s="3">
         <f t="shared" si="2"/>
         <v>10301803</v>
       </c>
-      <c r="B92" s="8">
+      <c r="B92" s="7">
         <v>103018</v>
       </c>
-      <c r="C92" s="8">
+      <c r="C92" s="7">
         <v>3</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="8">
         <v>40</v>
       </c>
-      <c r="E92" s="10">
+      <c r="E92" s="9">
         <v>6</v>
       </c>
-      <c r="F92" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" s="3">
         <f t="shared" si="2"/>
         <v>10301804</v>
       </c>
-      <c r="B93" s="8">
+      <c r="B93" s="7">
         <v>103018</v>
       </c>
-      <c r="C93" s="8">
-        <v>4</v>
-      </c>
-      <c r="D93" s="9">
+      <c r="C93" s="7">
+        <v>4</v>
+      </c>
+      <c r="D93" s="8">
         <v>50</v>
       </c>
-      <c r="E93" s="10">
+      <c r="E93" s="9">
         <v>8</v>
       </c>
-      <c r="F93" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" s="3">
         <f t="shared" si="2"/>
         <v>10301805</v>
       </c>
-      <c r="B94" s="8">
+      <c r="B94" s="7">
         <v>103018</v>
       </c>
-      <c r="C94" s="8">
+      <c r="C94" s="7">
         <v>5</v>
       </c>
-      <c r="D94" s="8"/>
-      <c r="E94" s="10">
+      <c r="D94" s="7"/>
+      <c r="E94" s="9">
         <v>10</v>
       </c>
-      <c r="F94" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" s="3">
         <f t="shared" si="2"/>
         <v>10401901</v>
       </c>
-      <c r="B95" s="8">
+      <c r="B95" s="7">
         <v>104019</v>
       </c>
-      <c r="C95" s="8">
+      <c r="C95" s="7">
         <v>1</v>
       </c>
-      <c r="D95" s="9">
+      <c r="D95" s="8">
         <v>25</v>
       </c>
-      <c r="E95" s="10">
-        <v>2</v>
-      </c>
-      <c r="F95" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="E95" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" s="3">
         <f t="shared" si="2"/>
         <v>10401902</v>
       </c>
-      <c r="B96" s="8">
+      <c r="B96" s="7">
         <v>104019</v>
       </c>
-      <c r="C96" s="8">
-        <v>2</v>
-      </c>
-      <c r="D96" s="9">
+      <c r="C96" s="7">
+        <v>2</v>
+      </c>
+      <c r="D96" s="8">
         <v>35</v>
       </c>
-      <c r="E96" s="10">
-        <v>4</v>
-      </c>
-      <c r="F96" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="E96" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" s="3">
         <f t="shared" si="2"/>
         <v>10401903</v>
       </c>
-      <c r="B97" s="8">
+      <c r="B97" s="7">
         <v>104019</v>
       </c>
-      <c r="C97" s="8">
+      <c r="C97" s="7">
         <v>3</v>
       </c>
-      <c r="D97" s="9">
+      <c r="D97" s="8">
         <v>45</v>
       </c>
-      <c r="E97" s="10">
+      <c r="E97" s="9">
         <v>6</v>
       </c>
-      <c r="F97" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" s="3">
         <f t="shared" si="2"/>
         <v>10401904</v>
       </c>
-      <c r="B98" s="8">
+      <c r="B98" s="7">
         <v>104019</v>
       </c>
-      <c r="C98" s="8">
-        <v>4</v>
-      </c>
-      <c r="D98" s="9">
+      <c r="C98" s="7">
+        <v>4</v>
+      </c>
+      <c r="D98" s="8">
         <v>55</v>
       </c>
-      <c r="E98" s="10">
+      <c r="E98" s="9">
         <v>8</v>
       </c>
-      <c r="F98" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" s="3">
         <f t="shared" si="2"/>
         <v>10401905</v>
       </c>
-      <c r="B99" s="8">
+      <c r="B99" s="7">
         <v>104019</v>
       </c>
-      <c r="C99" s="8">
+      <c r="C99" s="7">
         <v>5</v>
       </c>
-      <c r="D99" s="8"/>
-      <c r="E99" s="10">
+      <c r="D99" s="7"/>
+      <c r="E99" s="9">
         <v>10</v>
       </c>
-      <c r="F99" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" s="3">
         <f t="shared" si="2"/>
         <v>10502001</v>
       </c>
-      <c r="B100" s="8">
+      <c r="B100" s="7">
         <v>105020</v>
       </c>
-      <c r="C100" s="8">
+      <c r="C100" s="7">
         <v>1</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="8">
         <v>30</v>
       </c>
-      <c r="E100" s="10">
-        <v>2</v>
-      </c>
-      <c r="F100" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+      <c r="E100" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101" s="3">
         <f t="shared" si="2"/>
         <v>10502002</v>
       </c>
-      <c r="B101" s="8">
+      <c r="B101" s="7">
         <v>105020</v>
       </c>
-      <c r="C101" s="8">
-        <v>2</v>
-      </c>
-      <c r="D101" s="9">
+      <c r="C101" s="7">
+        <v>2</v>
+      </c>
+      <c r="D101" s="8">
         <v>40</v>
       </c>
-      <c r="E101" s="10">
-        <v>4</v>
-      </c>
-      <c r="F101" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+      <c r="E101" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102" s="3">
         <f t="shared" si="2"/>
         <v>10502003</v>
       </c>
-      <c r="B102" s="8">
+      <c r="B102" s="7">
         <v>105020</v>
       </c>
-      <c r="C102" s="8">
+      <c r="C102" s="7">
         <v>3</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="8">
         <v>50</v>
       </c>
-      <c r="E102" s="10">
+      <c r="E102" s="9">
         <v>6</v>
       </c>
-      <c r="F102" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103" s="3">
         <f t="shared" si="2"/>
         <v>10502004</v>
       </c>
-      <c r="B103" s="8">
+      <c r="B103" s="7">
         <v>105020</v>
       </c>
-      <c r="C103" s="8">
-        <v>4</v>
-      </c>
-      <c r="D103" s="9">
+      <c r="C103" s="7">
+        <v>4</v>
+      </c>
+      <c r="D103" s="8">
         <v>60</v>
       </c>
-      <c r="E103" s="10">
+      <c r="E103" s="9">
         <v>8</v>
       </c>
-      <c r="F103" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104" s="3">
         <f t="shared" si="2"/>
         <v>10502005</v>
       </c>
-      <c r="B104" s="8">
+      <c r="B104" s="7">
         <v>105020</v>
       </c>
-      <c r="C104" s="8">
+      <c r="C104" s="7">
         <v>5</v>
       </c>
-      <c r="D104" s="8"/>
-      <c r="E104" s="10">
+      <c r="D104" s="7"/>
+      <c r="E104" s="9">
         <v>10</v>
       </c>
-      <c r="F104" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+    </row>
+    <row r="105" spans="1:5">
       <c r="A105" s="3">
         <f t="shared" si="2"/>
         <v>20102101</v>
       </c>
-      <c r="B105" s="8">
+      <c r="B105" s="7">
         <v>201021</v>
       </c>
-      <c r="C105" s="8">
+      <c r="C105" s="7">
         <v>1</v>
       </c>
       <c r="D105" s="5">
         <v>10</v>
       </c>
-      <c r="E105" s="10">
-        <v>2</v>
-      </c>
-      <c r="F105" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+      <c r="E105" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
       <c r="A106" s="3">
         <f t="shared" si="2"/>
         <v>20102102</v>
       </c>
-      <c r="B106" s="8">
+      <c r="B106" s="7">
         <v>201021</v>
       </c>
-      <c r="C106" s="8">
+      <c r="C106" s="7">
         <v>2</v>
       </c>
       <c r="D106" s="5">
         <v>20</v>
       </c>
-      <c r="E106" s="10">
-        <v>4</v>
-      </c>
-      <c r="F106" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
+      <c r="E106" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107" s="3">
         <f t="shared" si="2"/>
         <v>20102103</v>
       </c>
-      <c r="B107" s="8">
+      <c r="B107" s="7">
         <v>201021</v>
       </c>
-      <c r="C107" s="8">
+      <c r="C107" s="7">
         <v>3</v>
       </c>
       <c r="D107" s="5">
         <v>30</v>
       </c>
-      <c r="E107" s="10">
+      <c r="E107" s="9">
         <v>6</v>
       </c>
-      <c r="F107" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108" s="3">
         <f t="shared" si="2"/>
         <v>20102104</v>
       </c>
-      <c r="B108" s="8">
+      <c r="B108" s="7">
         <v>201021</v>
       </c>
-      <c r="C108" s="8">
+      <c r="C108" s="7">
         <v>4</v>
       </c>
       <c r="D108" s="5">
         <v>40</v>
       </c>
-      <c r="E108" s="10">
+      <c r="E108" s="9">
         <v>8</v>
       </c>
-      <c r="F108" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109" s="3">
         <f t="shared" si="2"/>
         <v>20102105</v>
       </c>
-      <c r="B109" s="8">
+      <c r="B109" s="7">
         <v>201021</v>
       </c>
-      <c r="C109" s="8">
+      <c r="C109" s="7">
         <v>5</v>
       </c>
       <c r="D109" s="4"/>
-      <c r="E109" s="10">
+      <c r="E109" s="9">
         <v>10</v>
       </c>
-      <c r="F109" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
+    </row>
+    <row r="110" spans="1:5">
       <c r="A110" s="3">
         <f t="shared" si="2"/>
         <v>20202201</v>
       </c>
-      <c r="B110" s="8">
+      <c r="B110" s="7">
         <v>202022</v>
       </c>
-      <c r="C110" s="8">
+      <c r="C110" s="7">
         <v>1</v>
       </c>
-      <c r="D110" s="9">
+      <c r="D110" s="8">
         <v>15</v>
       </c>
-      <c r="E110" s="10">
-        <v>2</v>
-      </c>
-      <c r="F110" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+      <c r="E110" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
       <c r="A111" s="3">
         <f t="shared" si="2"/>
         <v>20202202</v>
       </c>
-      <c r="B111" s="8">
+      <c r="B111" s="7">
         <v>202022</v>
       </c>
-      <c r="C111" s="8">
-        <v>2</v>
-      </c>
-      <c r="D111" s="9">
+      <c r="C111" s="7">
+        <v>2</v>
+      </c>
+      <c r="D111" s="8">
         <v>25</v>
       </c>
-      <c r="E111" s="10">
-        <v>4</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
+      <c r="E111" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112" s="3">
         <f t="shared" ref="A112:A154" si="3">B112*100+C112</f>
         <v>20202203</v>
       </c>
-      <c r="B112" s="8">
+      <c r="B112" s="7">
         <v>202022</v>
       </c>
-      <c r="C112" s="8">
+      <c r="C112" s="7">
         <v>3</v>
       </c>
-      <c r="D112" s="9">
+      <c r="D112" s="8">
         <v>35</v>
       </c>
-      <c r="E112" s="10">
+      <c r="E112" s="9">
         <v>6</v>
       </c>
-      <c r="F112" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
+    </row>
+    <row r="113" spans="1:5">
       <c r="A113" s="3">
         <f t="shared" si="3"/>
         <v>20202204</v>
       </c>
-      <c r="B113" s="8">
+      <c r="B113" s="7">
         <v>202022</v>
       </c>
-      <c r="C113" s="8">
-        <v>4</v>
-      </c>
-      <c r="D113" s="9">
+      <c r="C113" s="7">
+        <v>4</v>
+      </c>
+      <c r="D113" s="8">
         <v>45</v>
       </c>
-      <c r="E113" s="10">
+      <c r="E113" s="9">
         <v>8</v>
       </c>
-      <c r="F113" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+    </row>
+    <row r="114" spans="1:5">
       <c r="A114" s="3">
         <f t="shared" si="3"/>
         <v>20202205</v>
       </c>
-      <c r="B114" s="8">
+      <c r="B114" s="7">
         <v>202022</v>
       </c>
-      <c r="C114" s="8">
+      <c r="C114" s="7">
         <v>5</v>
       </c>
-      <c r="D114" s="8"/>
-      <c r="E114" s="10">
+      <c r="D114" s="7"/>
+      <c r="E114" s="9">
         <v>10</v>
       </c>
-      <c r="F114" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115" s="3">
         <f t="shared" si="3"/>
         <v>20302301</v>
       </c>
-      <c r="B115" s="8">
+      <c r="B115" s="7">
         <v>203023</v>
       </c>
-      <c r="C115" s="8">
+      <c r="C115" s="7">
         <v>1</v>
       </c>
-      <c r="D115" s="9">
+      <c r="D115" s="8">
         <v>20</v>
       </c>
-      <c r="E115" s="10">
-        <v>2</v>
-      </c>
-      <c r="F115" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
+      <c r="E115" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116" s="3">
         <f t="shared" si="3"/>
         <v>20302302</v>
       </c>
-      <c r="B116" s="8">
+      <c r="B116" s="7">
         <v>203023</v>
       </c>
-      <c r="C116" s="8">
-        <v>2</v>
-      </c>
-      <c r="D116" s="9">
+      <c r="C116" s="7">
+        <v>2</v>
+      </c>
+      <c r="D116" s="8">
         <v>30</v>
       </c>
-      <c r="E116" s="10">
-        <v>4</v>
-      </c>
-      <c r="F116" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="E116" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
       <c r="A117" s="3">
         <f t="shared" si="3"/>
         <v>20302303</v>
       </c>
-      <c r="B117" s="8">
+      <c r="B117" s="7">
         <v>203023</v>
       </c>
-      <c r="C117" s="8">
+      <c r="C117" s="7">
         <v>3</v>
       </c>
-      <c r="D117" s="9">
+      <c r="D117" s="8">
         <v>40</v>
       </c>
-      <c r="E117" s="10">
+      <c r="E117" s="9">
         <v>6</v>
       </c>
-      <c r="F117" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
+    </row>
+    <row r="118" spans="1:5">
       <c r="A118" s="3">
         <f t="shared" si="3"/>
         <v>20302304</v>
       </c>
-      <c r="B118" s="8">
+      <c r="B118" s="7">
         <v>203023</v>
       </c>
-      <c r="C118" s="8">
-        <v>4</v>
-      </c>
-      <c r="D118" s="9">
+      <c r="C118" s="7">
+        <v>4</v>
+      </c>
+      <c r="D118" s="8">
         <v>50</v>
       </c>
-      <c r="E118" s="10">
+      <c r="E118" s="9">
         <v>8</v>
       </c>
-      <c r="F118" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+    </row>
+    <row r="119" spans="1:5">
       <c r="A119" s="3">
         <f t="shared" si="3"/>
         <v>20302305</v>
       </c>
-      <c r="B119" s="8">
+      <c r="B119" s="7">
         <v>203023</v>
       </c>
-      <c r="C119" s="8">
+      <c r="C119" s="7">
         <v>5</v>
       </c>
-      <c r="D119" s="8"/>
-      <c r="E119" s="10">
+      <c r="D119" s="7"/>
+      <c r="E119" s="9">
         <v>10</v>
       </c>
-      <c r="F119" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
+    </row>
+    <row r="120" spans="1:5">
       <c r="A120" s="3">
         <f t="shared" si="3"/>
         <v>20402401</v>
       </c>
-      <c r="B120" s="8">
+      <c r="B120" s="7">
         <v>204024</v>
       </c>
-      <c r="C120" s="8">
+      <c r="C120" s="7">
         <v>1</v>
       </c>
-      <c r="D120" s="9">
+      <c r="D120" s="8">
         <v>25</v>
       </c>
-      <c r="E120" s="10">
-        <v>2</v>
-      </c>
-      <c r="F120" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="E120" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
       <c r="A121" s="3">
         <f t="shared" si="3"/>
         <v>20402402</v>
       </c>
-      <c r="B121" s="8">
+      <c r="B121" s="7">
         <v>204024</v>
       </c>
-      <c r="C121" s="8">
-        <v>2</v>
-      </c>
-      <c r="D121" s="9">
+      <c r="C121" s="7">
+        <v>2</v>
+      </c>
+      <c r="D121" s="8">
         <v>35</v>
       </c>
-      <c r="E121" s="10">
-        <v>4</v>
-      </c>
-      <c r="F121" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="E121" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
       <c r="A122" s="3">
         <f t="shared" si="3"/>
         <v>20402403</v>
       </c>
-      <c r="B122" s="8">
+      <c r="B122" s="7">
         <v>204024</v>
       </c>
-      <c r="C122" s="8">
+      <c r="C122" s="7">
         <v>3</v>
       </c>
-      <c r="D122" s="9">
+      <c r="D122" s="8">
         <v>45</v>
       </c>
-      <c r="E122" s="10">
+      <c r="E122" s="9">
         <v>6</v>
       </c>
-      <c r="F122" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+    </row>
+    <row r="123" spans="1:5">
       <c r="A123" s="3">
         <f t="shared" si="3"/>
         <v>20402404</v>
       </c>
-      <c r="B123" s="8">
+      <c r="B123" s="7">
         <v>204024</v>
       </c>
-      <c r="C123" s="8">
-        <v>4</v>
-      </c>
-      <c r="D123" s="9">
+      <c r="C123" s="7">
+        <v>4</v>
+      </c>
+      <c r="D123" s="8">
         <v>55</v>
       </c>
-      <c r="E123" s="10">
+      <c r="E123" s="9">
         <v>8</v>
       </c>
-      <c r="F123" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+    </row>
+    <row r="124" spans="1:5">
       <c r="A124" s="3">
         <f t="shared" si="3"/>
         <v>20402405</v>
       </c>
-      <c r="B124" s="8">
+      <c r="B124" s="7">
         <v>204024</v>
       </c>
-      <c r="C124" s="8">
+      <c r="C124" s="7">
         <v>5</v>
       </c>
-      <c r="D124" s="8"/>
-      <c r="E124" s="10">
+      <c r="D124" s="7"/>
+      <c r="E124" s="9">
         <v>10</v>
       </c>
-      <c r="F124" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+    </row>
+    <row r="125" spans="1:5">
       <c r="A125" s="3">
         <f t="shared" si="3"/>
         <v>20502501</v>
       </c>
-      <c r="B125" s="8">
+      <c r="B125" s="7">
         <v>205025</v>
       </c>
-      <c r="C125" s="8">
+      <c r="C125" s="7">
         <v>1</v>
       </c>
-      <c r="D125" s="9">
+      <c r="D125" s="8">
         <v>30</v>
       </c>
-      <c r="E125" s="10">
-        <v>2</v>
-      </c>
-      <c r="F125" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="E125" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
       <c r="A126" s="3">
         <f t="shared" si="3"/>
         <v>20502502</v>
       </c>
-      <c r="B126" s="8">
+      <c r="B126" s="7">
         <v>205025</v>
       </c>
-      <c r="C126" s="8">
-        <v>2</v>
-      </c>
-      <c r="D126" s="9">
+      <c r="C126" s="7">
+        <v>2</v>
+      </c>
+      <c r="D126" s="8">
         <v>40</v>
       </c>
-      <c r="E126" s="10">
-        <v>4</v>
-      </c>
-      <c r="F126" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="E126" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
       <c r="A127" s="3">
         <f t="shared" si="3"/>
         <v>20502503</v>
       </c>
-      <c r="B127" s="8">
+      <c r="B127" s="7">
         <v>205025</v>
       </c>
-      <c r="C127" s="8">
+      <c r="C127" s="7">
         <v>3</v>
       </c>
-      <c r="D127" s="9">
+      <c r="D127" s="8">
         <v>50</v>
       </c>
-      <c r="E127" s="10">
+      <c r="E127" s="9">
         <v>6</v>
       </c>
-      <c r="F127" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+    </row>
+    <row r="128" spans="1:5">
       <c r="A128" s="3">
         <f t="shared" si="3"/>
         <v>20502504</v>
       </c>
-      <c r="B128" s="8">
+      <c r="B128" s="7">
         <v>205025</v>
       </c>
-      <c r="C128" s="8">
-        <v>4</v>
-      </c>
-      <c r="D128" s="9">
+      <c r="C128" s="7">
+        <v>4</v>
+      </c>
+      <c r="D128" s="8">
         <v>60</v>
       </c>
-      <c r="E128" s="10">
+      <c r="E128" s="9">
         <v>8</v>
       </c>
-      <c r="F128" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
+    </row>
+    <row r="129" spans="1:5">
       <c r="A129" s="3">
         <f t="shared" si="3"/>
         <v>20502505</v>
       </c>
-      <c r="B129" s="8">
+      <c r="B129" s="7">
         <v>205025</v>
       </c>
-      <c r="C129" s="8">
+      <c r="C129" s="7">
         <v>5</v>
       </c>
-      <c r="D129" s="8"/>
-      <c r="E129" s="10">
+      <c r="D129" s="7"/>
+      <c r="E129" s="9">
         <v>10</v>
       </c>
-      <c r="F129" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
+    </row>
+    <row r="130" spans="1:5">
       <c r="A130" s="3">
         <f t="shared" si="3"/>
         <v>30102601</v>
       </c>
-      <c r="B130" s="8">
+      <c r="B130" s="7">
         <v>301026</v>
       </c>
-      <c r="C130" s="8">
+      <c r="C130" s="7">
         <v>1</v>
       </c>
       <c r="D130" s="5">
         <v>10</v>
       </c>
-      <c r="E130" s="10">
-        <v>2</v>
-      </c>
-      <c r="F130" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+      <c r="E130" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
       <c r="A131" s="3">
         <f t="shared" si="3"/>
         <v>30102602</v>
       </c>
-      <c r="B131" s="8">
+      <c r="B131" s="7">
         <v>301026</v>
       </c>
-      <c r="C131" s="8">
+      <c r="C131" s="7">
         <v>2</v>
       </c>
       <c r="D131" s="5">
         <v>20</v>
       </c>
-      <c r="E131" s="10">
-        <v>4</v>
-      </c>
-      <c r="F131" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
+      <c r="E131" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
       <c r="A132" s="3">
         <f t="shared" si="3"/>
         <v>30102603</v>
       </c>
-      <c r="B132" s="8">
+      <c r="B132" s="7">
         <v>301026</v>
       </c>
-      <c r="C132" s="8">
+      <c r="C132" s="7">
         <v>3</v>
       </c>
       <c r="D132" s="5">
         <v>30</v>
       </c>
-      <c r="E132" s="10">
+      <c r="E132" s="9">
         <v>6</v>
       </c>
-      <c r="F132" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+    </row>
+    <row r="133" spans="1:5">
       <c r="A133" s="3">
         <f t="shared" si="3"/>
         <v>30102604</v>
       </c>
-      <c r="B133" s="8">
+      <c r="B133" s="7">
         <v>301026</v>
       </c>
-      <c r="C133" s="8">
+      <c r="C133" s="7">
         <v>4</v>
       </c>
       <c r="D133" s="5">
         <v>40</v>
       </c>
-      <c r="E133" s="10">
+      <c r="E133" s="9">
         <v>8</v>
       </c>
-      <c r="F133" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
+    </row>
+    <row r="134" spans="1:5">
       <c r="A134" s="3">
         <f t="shared" si="3"/>
         <v>30102605</v>
       </c>
-      <c r="B134" s="8">
+      <c r="B134" s="7">
         <v>301026</v>
       </c>
-      <c r="C134" s="8">
+      <c r="C134" s="7">
         <v>5</v>
       </c>
       <c r="D134" s="4"/>
-      <c r="E134" s="10">
+      <c r="E134" s="9">
         <v>10</v>
       </c>
-      <c r="F134" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135" s="3">
         <f t="shared" si="3"/>
         <v>30202701</v>
       </c>
-      <c r="B135" s="8">
+      <c r="B135" s="7">
         <v>302027</v>
       </c>
-      <c r="C135" s="8">
+      <c r="C135" s="7">
         <v>1</v>
       </c>
-      <c r="D135" s="9">
+      <c r="D135" s="8">
         <v>15</v>
       </c>
-      <c r="E135" s="10">
-        <v>2</v>
-      </c>
-      <c r="F135" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+      <c r="E135" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
       <c r="A136" s="3">
         <f t="shared" si="3"/>
         <v>30202702</v>
       </c>
-      <c r="B136" s="8">
+      <c r="B136" s="7">
         <v>302027</v>
       </c>
-      <c r="C136" s="8">
-        <v>2</v>
-      </c>
-      <c r="D136" s="9">
+      <c r="C136" s="7">
+        <v>2</v>
+      </c>
+      <c r="D136" s="8">
         <v>25</v>
       </c>
-      <c r="E136" s="10">
-        <v>4</v>
-      </c>
-      <c r="F136" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+      <c r="E136" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
       <c r="A137" s="3">
         <f t="shared" si="3"/>
         <v>30202703</v>
       </c>
-      <c r="B137" s="8">
+      <c r="B137" s="7">
         <v>302027</v>
       </c>
-      <c r="C137" s="8">
+      <c r="C137" s="7">
         <v>3</v>
       </c>
-      <c r="D137" s="9">
+      <c r="D137" s="8">
         <v>35</v>
       </c>
-      <c r="E137" s="10">
+      <c r="E137" s="9">
         <v>6</v>
       </c>
-      <c r="F137" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+    </row>
+    <row r="138" spans="1:5">
       <c r="A138" s="3">
         <f t="shared" si="3"/>
         <v>30202704</v>
       </c>
-      <c r="B138" s="8">
+      <c r="B138" s="7">
         <v>302027</v>
       </c>
-      <c r="C138" s="8">
-        <v>4</v>
-      </c>
-      <c r="D138" s="9">
+      <c r="C138" s="7">
+        <v>4</v>
+      </c>
+      <c r="D138" s="8">
         <v>45</v>
       </c>
-      <c r="E138" s="10">
+      <c r="E138" s="9">
         <v>8</v>
       </c>
-      <c r="F138" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+    </row>
+    <row r="139" spans="1:5">
       <c r="A139" s="3">
         <f t="shared" si="3"/>
         <v>30202705</v>
       </c>
-      <c r="B139" s="8">
+      <c r="B139" s="7">
         <v>302027</v>
       </c>
-      <c r="C139" s="8">
+      <c r="C139" s="7">
         <v>5</v>
       </c>
-      <c r="D139" s="8"/>
-      <c r="E139" s="10">
+      <c r="D139" s="7"/>
+      <c r="E139" s="9">
         <v>10</v>
       </c>
-      <c r="F139" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
+    </row>
+    <row r="140" spans="1:5">
       <c r="A140" s="3">
         <f t="shared" si="3"/>
         <v>30302801</v>
       </c>
-      <c r="B140" s="10">
+      <c r="B140" s="9">
         <v>303028</v>
       </c>
-      <c r="C140" s="8">
+      <c r="C140" s="7">
         <v>1</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D140" s="8">
         <v>20</v>
       </c>
-      <c r="E140" s="10">
-        <v>2</v>
-      </c>
-      <c r="F140" s="12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
+      <c r="E140" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
       <c r="A141" s="3">
         <f t="shared" si="3"/>
         <v>30302802</v>
       </c>
-      <c r="B141" s="10">
+      <c r="B141" s="9">
         <v>303028</v>
       </c>
-      <c r="C141" s="8">
-        <v>2</v>
-      </c>
-      <c r="D141" s="9">
+      <c r="C141" s="7">
+        <v>2</v>
+      </c>
+      <c r="D141" s="8">
         <v>30</v>
       </c>
-      <c r="E141" s="10">
-        <v>4</v>
-      </c>
-      <c r="F141" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
+      <c r="E141" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
       <c r="A142" s="3">
         <f t="shared" si="3"/>
         <v>30302803</v>
       </c>
-      <c r="B142" s="10">
+      <c r="B142" s="9">
         <v>303028</v>
       </c>
-      <c r="C142" s="8">
+      <c r="C142" s="7">
         <v>3</v>
       </c>
-      <c r="D142" s="9">
+      <c r="D142" s="8">
         <v>40</v>
       </c>
-      <c r="E142" s="10">
+      <c r="E142" s="9">
         <v>6</v>
       </c>
-      <c r="F142" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+    </row>
+    <row r="143" spans="1:5">
       <c r="A143" s="3">
         <f t="shared" si="3"/>
         <v>30302804</v>
       </c>
-      <c r="B143" s="10">
+      <c r="B143" s="9">
         <v>303028</v>
       </c>
-      <c r="C143" s="8">
-        <v>4</v>
-      </c>
-      <c r="D143" s="9">
+      <c r="C143" s="7">
+        <v>4</v>
+      </c>
+      <c r="D143" s="8">
         <v>50</v>
       </c>
-      <c r="E143" s="10">
+      <c r="E143" s="9">
         <v>8</v>
       </c>
-      <c r="F143" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
+    </row>
+    <row r="144" spans="1:5">
       <c r="A144" s="3">
         <f t="shared" si="3"/>
         <v>30302805</v>
       </c>
-      <c r="B144" s="10">
+      <c r="B144" s="9">
         <v>303028</v>
       </c>
-      <c r="C144" s="8">
+      <c r="C144" s="7">
         <v>5</v>
       </c>
-      <c r="D144" s="8"/>
-      <c r="E144" s="10">
+      <c r="D144" s="7"/>
+      <c r="E144" s="9">
         <v>10</v>
       </c>
-      <c r="F144" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
+    </row>
+    <row r="145" spans="1:5">
       <c r="A145" s="3">
         <f t="shared" si="3"/>
         <v>30402901</v>
       </c>
-      <c r="B145" s="8">
+      <c r="B145" s="7">
         <v>304029</v>
       </c>
-      <c r="C145" s="8">
+      <c r="C145" s="7">
         <v>1</v>
       </c>
-      <c r="D145" s="9">
+      <c r="D145" s="8">
         <v>25</v>
       </c>
-      <c r="E145" s="10">
-        <v>2</v>
-      </c>
-      <c r="F145" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
+      <c r="E145" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
       <c r="A146" s="3">
         <f t="shared" si="3"/>
         <v>30402902</v>
       </c>
-      <c r="B146" s="8">
+      <c r="B146" s="7">
         <v>304029</v>
       </c>
-      <c r="C146" s="8">
-        <v>2</v>
-      </c>
-      <c r="D146" s="9">
+      <c r="C146" s="7">
+        <v>2</v>
+      </c>
+      <c r="D146" s="8">
         <v>35</v>
       </c>
-      <c r="E146" s="10">
-        <v>4</v>
-      </c>
-      <c r="F146" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+      <c r="E146" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
       <c r="A147" s="3">
         <f t="shared" si="3"/>
         <v>30402903</v>
       </c>
-      <c r="B147" s="8">
+      <c r="B147" s="7">
         <v>304029</v>
       </c>
-      <c r="C147" s="8">
+      <c r="C147" s="7">
         <v>3</v>
       </c>
-      <c r="D147" s="9">
+      <c r="D147" s="8">
         <v>45</v>
       </c>
-      <c r="E147" s="10">
+      <c r="E147" s="9">
         <v>6</v>
       </c>
-      <c r="F147" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
+    </row>
+    <row r="148" spans="1:5">
       <c r="A148" s="3">
         <f t="shared" si="3"/>
         <v>30402904</v>
       </c>
-      <c r="B148" s="8">
+      <c r="B148" s="7">
         <v>304029</v>
       </c>
-      <c r="C148" s="8">
-        <v>4</v>
-      </c>
-      <c r="D148" s="9">
+      <c r="C148" s="7">
+        <v>4</v>
+      </c>
+      <c r="D148" s="8">
         <v>55</v>
       </c>
-      <c r="E148" s="10">
+      <c r="E148" s="9">
         <v>8</v>
       </c>
-      <c r="F148" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
+    </row>
+    <row r="149" spans="1:5">
       <c r="A149" s="3">
         <f t="shared" si="3"/>
         <v>30402905</v>
       </c>
-      <c r="B149" s="8">
+      <c r="B149" s="7">
         <v>304029</v>
       </c>
-      <c r="C149" s="8">
+      <c r="C149" s="7">
         <v>5</v>
       </c>
-      <c r="D149" s="8"/>
-      <c r="E149" s="10">
+      <c r="D149" s="7"/>
+      <c r="E149" s="9">
         <v>10</v>
       </c>
-      <c r="F149" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
+    </row>
+    <row r="150" spans="1:5">
       <c r="A150" s="3">
         <f t="shared" si="3"/>
         <v>30503001</v>
       </c>
-      <c r="B150" s="8">
+      <c r="B150" s="7">
         <v>305030</v>
       </c>
-      <c r="C150" s="8">
+      <c r="C150" s="7">
         <v>1</v>
       </c>
-      <c r="D150" s="9">
+      <c r="D150" s="8">
         <v>30</v>
       </c>
-      <c r="E150" s="10">
-        <v>2</v>
-      </c>
-      <c r="F150" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="E150" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
       <c r="A151" s="3">
         <f t="shared" si="3"/>
         <v>30503002</v>
       </c>
-      <c r="B151" s="8">
+      <c r="B151" s="7">
         <v>305030</v>
       </c>
-      <c r="C151" s="8">
-        <v>2</v>
-      </c>
-      <c r="D151" s="9">
+      <c r="C151" s="7">
+        <v>2</v>
+      </c>
+      <c r="D151" s="8">
         <v>40</v>
       </c>
-      <c r="E151" s="10">
-        <v>4</v>
-      </c>
-      <c r="F151" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
+      <c r="E151" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
       <c r="A152" s="3">
         <f t="shared" si="3"/>
         <v>30503003</v>
       </c>
-      <c r="B152" s="8">
+      <c r="B152" s="7">
         <v>305030</v>
       </c>
-      <c r="C152" s="8">
+      <c r="C152" s="7">
         <v>3</v>
       </c>
-      <c r="D152" s="9">
+      <c r="D152" s="8">
         <v>50</v>
       </c>
-      <c r="E152" s="10">
+      <c r="E152" s="9">
         <v>6</v>
       </c>
-      <c r="F152" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
+    </row>
+    <row r="153" spans="1:5">
       <c r="A153" s="3">
         <f t="shared" si="3"/>
         <v>30503004</v>
       </c>
-      <c r="B153" s="8">
+      <c r="B153" s="7">
         <v>305030</v>
       </c>
-      <c r="C153" s="8">
-        <v>4</v>
-      </c>
-      <c r="D153" s="9">
+      <c r="C153" s="7">
+        <v>4</v>
+      </c>
+      <c r="D153" s="8">
         <v>60</v>
       </c>
-      <c r="E153" s="10">
+      <c r="E153" s="9">
         <v>8</v>
       </c>
-      <c r="F153" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
+    </row>
+    <row r="154" spans="1:5">
       <c r="A154" s="3">
         <f t="shared" si="3"/>
         <v>30503005</v>
       </c>
-      <c r="B154" s="8">
+      <c r="B154" s="7">
         <v>305030</v>
       </c>
-      <c r="C154" s="8">
+      <c r="C154" s="7">
         <v>5</v>
       </c>
-      <c r="D154" s="8"/>
-      <c r="E154" s="10">
+      <c r="D154" s="7"/>
+      <c r="E154" s="9">
         <v>10</v>
-      </c>
-      <c r="F154" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/EmployeeStar.xlsx
+++ b/hall/resources/sample/EmployeeStar.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="17">
   <si>
     <t>ID</t>
   </si>
@@ -44,7 +44,13 @@
     <t>等级上限</t>
   </si>
   <si>
+    <t>主管加成</t>
+  </si>
+  <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>Map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -62,184 +68,16 @@
     <t>LevelCap</t>
   </si>
   <si>
-    <t>3_50</t>
+    <t>SupervisorBonus</t>
   </si>
   <si>
-    <t>5_50</t>
+    <t>1_200</t>
   </si>
   <si>
-    <t>6_50</t>
+    <t>2_200</t>
   </si>
   <si>
-    <t>3_80</t>
-  </si>
-  <si>
-    <t>5_80</t>
-  </si>
-  <si>
-    <t>6_80</t>
-  </si>
-  <si>
-    <t>3_110</t>
-  </si>
-  <si>
-    <t>5_110</t>
-  </si>
-  <si>
-    <t>6_110</t>
-  </si>
-  <si>
-    <t>3_140</t>
-  </si>
-  <si>
-    <t>5_140</t>
-  </si>
-  <si>
-    <t>6_140</t>
-  </si>
-  <si>
-    <t>3_170</t>
-  </si>
-  <si>
-    <t>5_170</t>
-  </si>
-  <si>
-    <t>6_170</t>
-  </si>
-  <si>
-    <t>3_120</t>
-  </si>
-  <si>
-    <t>5_120</t>
-  </si>
-  <si>
-    <t>6_120</t>
-  </si>
-  <si>
-    <t>3_160</t>
-  </si>
-  <si>
-    <t>5_160</t>
-  </si>
-  <si>
-    <t>6_160</t>
-  </si>
-  <si>
-    <t>3_200</t>
-  </si>
-  <si>
-    <t>5_200</t>
-  </si>
-  <si>
-    <t>6_200</t>
-  </si>
-  <si>
-    <t>3_240</t>
-  </si>
-  <si>
-    <t>5_240</t>
-  </si>
-  <si>
-    <t>6_240</t>
-  </si>
-  <si>
-    <t>3_100</t>
-  </si>
-  <si>
-    <t>5_100</t>
-  </si>
-  <si>
-    <t>6_100</t>
-  </si>
-  <si>
-    <t>3_150</t>
-  </si>
-  <si>
-    <t>5_150</t>
-  </si>
-  <si>
-    <t>6_150</t>
-  </si>
-  <si>
-    <t>3_250</t>
-  </si>
-  <si>
-    <t>5_250</t>
-  </si>
-  <si>
-    <t>6_250</t>
-  </si>
-  <si>
-    <t>3_300</t>
-  </si>
-  <si>
-    <t>5_300</t>
-  </si>
-  <si>
-    <t>6_300</t>
-  </si>
-  <si>
-    <t>3_260</t>
-  </si>
-  <si>
-    <t>5_260</t>
-  </si>
-  <si>
-    <t>6_260</t>
-  </si>
-  <si>
-    <t>3_320</t>
-  </si>
-  <si>
-    <t>5_320</t>
-  </si>
-  <si>
-    <t>6_320</t>
-  </si>
-  <si>
-    <t>3_380</t>
-  </si>
-  <si>
-    <t>5_380</t>
-  </si>
-  <si>
-    <t>6_380</t>
-  </si>
-  <si>
-    <t>3_440</t>
-  </si>
-  <si>
-    <t>5_440</t>
-  </si>
-  <si>
-    <t>6_440</t>
-  </si>
-  <si>
-    <t>3_460</t>
-  </si>
-  <si>
-    <t>5_460</t>
-  </si>
-  <si>
-    <t>6_460</t>
-  </si>
-  <si>
-    <t>3_540</t>
-  </si>
-  <si>
-    <t>5_540</t>
-  </si>
-  <si>
-    <t>6_540</t>
-  </si>
-  <si>
-    <t>3_620</t>
-  </si>
-  <si>
-    <t>5_620</t>
-  </si>
-  <si>
-    <t>6_620</t>
+    <t>11_300</t>
   </si>
 </sst>
 </file>
@@ -876,7 +714,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -898,6 +736,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -907,7 +748,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1435,17 +1276,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K154"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:F154"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
     <col min="2" max="2" width="12.375" customWidth="1"/>
     <col min="3" max="3" width="11.25" customWidth="1"/>
     <col min="4" max="4" width="13.875" customWidth="1"/>
     <col min="5" max="5" width="10.75" customWidth="1"/>
+    <col min="6" max="6" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1461,49 +1303,59 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="3">
         <f>B5*100+C5</f>
         <v>10100101</v>
@@ -1520,8 +1372,11 @@
       <c r="E5" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="3">
         <f t="shared" ref="A6:A37" si="0">B6*100+C6</f>
         <v>10100102</v>
@@ -1538,8 +1393,11 @@
       <c r="E6" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>10100103</v>
@@ -1556,8 +1414,11 @@
       <c r="E7" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>10100104</v>
@@ -1574,8 +1435,11 @@
       <c r="E8" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>10100105</v>
@@ -1590,8 +1454,11 @@
       <c r="E9" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>10200201</v>
@@ -1599,17 +1466,20 @@
       <c r="B10" s="1">
         <v>102002</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>1</v>
       </c>
-      <c r="D10" s="8">
-        <v>15</v>
-      </c>
-      <c r="E10" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="D10" s="9">
+        <v>15</v>
+      </c>
+      <c r="E10" s="10">
+        <v>2</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>10200202</v>
@@ -1617,17 +1487,20 @@
       <c r="B11" s="1">
         <v>102002</v>
       </c>
-      <c r="C11" s="7">
-        <v>2</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="C11" s="8">
+        <v>2</v>
+      </c>
+      <c r="D11" s="9">
         <v>25</v>
       </c>
-      <c r="E11" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="E11" s="10">
+        <v>4</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>10200203</v>
@@ -1635,17 +1508,20 @@
       <c r="B12" s="1">
         <v>102002</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>3</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="9">
         <v>35</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>10200204</v>
@@ -1653,17 +1529,20 @@
       <c r="B13" s="1">
         <v>102002</v>
       </c>
-      <c r="C13" s="7">
-        <v>4</v>
-      </c>
-      <c r="D13" s="8">
+      <c r="C13" s="8">
+        <v>4</v>
+      </c>
+      <c r="D13" s="9">
         <v>45</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>10200205</v>
@@ -1671,1384 +1550,1357 @@
       <c r="B14" s="1">
         <v>102002</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <v>5</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9">
+      <c r="D14" s="8"/>
+      <c r="E14" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>10300301</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <v>103003</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <v>1</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <v>20</v>
       </c>
-      <c r="E15" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="E15" s="10">
+        <v>2</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>10300302</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <v>103003</v>
       </c>
-      <c r="C16" s="7">
-        <v>2</v>
-      </c>
-      <c r="D16" s="8">
+      <c r="C16" s="8">
+        <v>2</v>
+      </c>
+      <c r="D16" s="9">
         <v>30</v>
       </c>
-      <c r="E16" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="E16" s="10">
+        <v>4</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>10300303</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <v>103003</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <v>3</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="9">
         <v>40</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>10300304</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="8">
         <v>103003</v>
       </c>
-      <c r="C18" s="7">
-        <v>4</v>
-      </c>
-      <c r="D18" s="8">
+      <c r="C18" s="8">
+        <v>4</v>
+      </c>
+      <c r="D18" s="9">
         <v>50</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>10300305</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <v>103003</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>5</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="9">
+      <c r="D19" s="8"/>
+      <c r="E19" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>10400401</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="8">
         <v>104004</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>1</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="9">
         <v>25</v>
       </c>
-      <c r="E20" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="E20" s="10">
+        <v>2</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>10400402</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="8">
         <v>104004</v>
       </c>
-      <c r="C21" s="7">
-        <v>2</v>
-      </c>
-      <c r="D21" s="8">
+      <c r="C21" s="8">
+        <v>2</v>
+      </c>
+      <c r="D21" s="9">
         <v>35</v>
       </c>
-      <c r="E21" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="E21" s="10">
+        <v>4</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>10400403</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="8">
         <v>104004</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <v>3</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="9">
         <v>45</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>10400404</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="8">
         <v>104004</v>
       </c>
-      <c r="C23" s="7">
-        <v>4</v>
-      </c>
-      <c r="D23" s="8">
+      <c r="C23" s="8">
+        <v>4</v>
+      </c>
+      <c r="D23" s="9">
         <v>55</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>10400405</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="8">
         <v>104004</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="8">
         <v>5</v>
       </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="9">
+      <c r="D24" s="8"/>
+      <c r="E24" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>10500501</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="8">
         <v>105005</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="8">
         <v>1</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="9">
         <v>30</v>
       </c>
-      <c r="E25" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="E25" s="10">
+        <v>2</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>10500502</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="8">
         <v>105005</v>
       </c>
-      <c r="C26" s="7">
-        <v>2</v>
-      </c>
-      <c r="D26" s="8">
+      <c r="C26" s="8">
+        <v>2</v>
+      </c>
+      <c r="D26" s="9">
         <v>40</v>
       </c>
-      <c r="E26" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="E26" s="10">
+        <v>4</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>10500503</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="8">
         <v>105005</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <v>3</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="9">
         <v>50</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>10500504</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="8">
         <v>105005</v>
       </c>
-      <c r="C28" s="7">
-        <v>4</v>
-      </c>
-      <c r="D28" s="8">
+      <c r="C28" s="8">
+        <v>4</v>
+      </c>
+      <c r="D28" s="9">
         <v>60</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>10500505</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="8">
         <v>105005</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="8">
         <v>5</v>
       </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="9">
+      <c r="D29" s="8"/>
+      <c r="E29" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>20100601</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="8">
         <v>201006</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="8">
         <v>1</v>
       </c>
       <c r="D30" s="5">
         <v>10</v>
       </c>
-      <c r="E30" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="E30" s="10">
+        <v>2</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>20100602</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="8">
         <v>201006</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="8">
         <v>2</v>
       </c>
       <c r="D31" s="5">
         <v>20</v>
       </c>
-      <c r="E31" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="E31" s="10">
+        <v>4</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>20100603</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="8">
         <v>201006</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="8">
         <v>3</v>
       </c>
       <c r="D32" s="5">
         <v>30</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>20100604</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="8">
         <v>201006</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="8">
         <v>4</v>
       </c>
       <c r="D33" s="5">
         <v>40</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>20100605</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="8">
         <v>201006</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="8">
         <v>5</v>
       </c>
       <c r="D34" s="4"/>
-      <c r="E34" s="9">
+      <c r="E34" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>20200701</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="8">
         <v>202007</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="8">
         <v>1</v>
       </c>
-      <c r="D35" s="8">
-        <v>15</v>
-      </c>
-      <c r="E35" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="D35" s="9">
+        <v>15</v>
+      </c>
+      <c r="E35" s="10">
+        <v>2</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="3">
         <f t="shared" si="0"/>
         <v>20200702</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="8">
         <v>202007</v>
       </c>
-      <c r="C36" s="7">
-        <v>2</v>
-      </c>
-      <c r="D36" s="8">
+      <c r="C36" s="8">
+        <v>2</v>
+      </c>
+      <c r="D36" s="9">
         <v>25</v>
       </c>
-      <c r="E36" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="E36" s="10">
+        <v>4</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="3">
         <f t="shared" si="0"/>
         <v>20200703</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="8">
         <v>202007</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="8">
         <v>3</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="9">
         <v>35</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="3">
         <f t="shared" ref="A38:A79" si="1">B38*100+C38</f>
         <v>20200704</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="8">
         <v>202007</v>
       </c>
-      <c r="C38" s="7">
-        <v>4</v>
-      </c>
-      <c r="D38" s="8">
+      <c r="C38" s="8">
+        <v>4</v>
+      </c>
+      <c r="D38" s="9">
         <v>45</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="3">
         <f t="shared" si="1"/>
         <v>20200705</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="8">
         <v>202007</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="8">
         <v>5</v>
       </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="9">
+      <c r="D39" s="8"/>
+      <c r="E39" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>20300801</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="8">
         <v>203008</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="8">
         <v>1</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="9">
         <v>20</v>
       </c>
-      <c r="E40" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="E40" s="10">
+        <v>2</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="3">
         <f t="shared" si="1"/>
         <v>20300802</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="8">
         <v>203008</v>
       </c>
-      <c r="C41" s="7">
-        <v>2</v>
-      </c>
-      <c r="D41" s="8">
+      <c r="C41" s="8">
+        <v>2</v>
+      </c>
+      <c r="D41" s="9">
         <v>30</v>
       </c>
-      <c r="E41" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="E41" s="10">
+        <v>4</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="3">
         <f t="shared" si="1"/>
         <v>20300803</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="8">
         <v>203008</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="8">
         <v>3</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="9">
         <v>40</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="F42" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="3">
         <f t="shared" si="1"/>
         <v>20300804</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="8">
         <v>203008</v>
       </c>
-      <c r="C43" s="7">
-        <v>4</v>
-      </c>
-      <c r="D43" s="8">
+      <c r="C43" s="8">
+        <v>4</v>
+      </c>
+      <c r="D43" s="9">
         <v>50</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="F43" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="3">
         <f t="shared" si="1"/>
         <v>20300805</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="8">
         <v>203008</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="8">
         <v>5</v>
       </c>
-      <c r="D44" s="7"/>
-      <c r="E44" s="9">
+      <c r="D44" s="8"/>
+      <c r="E44" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="F44" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" s="3">
         <f t="shared" si="1"/>
         <v>20400901</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="8">
         <v>204009</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="8">
         <v>1</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="9">
         <v>25</v>
       </c>
-      <c r="E45" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="E45" s="10">
+        <v>2</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="3">
         <f t="shared" si="1"/>
         <v>20400902</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="8">
         <v>204009</v>
       </c>
-      <c r="C46" s="7">
-        <v>2</v>
-      </c>
-      <c r="D46" s="8">
+      <c r="C46" s="8">
+        <v>2</v>
+      </c>
+      <c r="D46" s="9">
         <v>35</v>
       </c>
-      <c r="E46" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="E46" s="10">
+        <v>4</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="3">
         <f t="shared" si="1"/>
         <v>20400903</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="8">
         <v>204009</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="8">
         <v>3</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="9">
         <v>45</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="F47" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="3">
         <f t="shared" si="1"/>
         <v>20400904</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="8">
         <v>204009</v>
       </c>
-      <c r="C48" s="7">
-        <v>4</v>
-      </c>
-      <c r="D48" s="8">
+      <c r="C48" s="8">
+        <v>4</v>
+      </c>
+      <c r="D48" s="9">
         <v>55</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="F48" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="3">
         <f t="shared" si="1"/>
         <v>20400905</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="8">
         <v>204009</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="8">
         <v>5</v>
       </c>
-      <c r="D49" s="7"/>
-      <c r="E49" s="9">
+      <c r="D49" s="8"/>
+      <c r="E49" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="F49" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="3">
         <f t="shared" si="1"/>
         <v>20501001</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="8">
         <v>205010</v>
       </c>
-      <c r="C50" s="7">
+      <c r="C50" s="8">
         <v>1</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="9">
         <v>30</v>
       </c>
-      <c r="E50" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+      <c r="E50" s="10">
+        <v>2</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="3">
         <f t="shared" si="1"/>
         <v>20501002</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="8">
         <v>205010</v>
       </c>
-      <c r="C51" s="7">
-        <v>2</v>
-      </c>
-      <c r="D51" s="8">
+      <c r="C51" s="8">
+        <v>2</v>
+      </c>
+      <c r="D51" s="9">
         <v>40</v>
       </c>
-      <c r="E51" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="E51" s="10">
+        <v>4</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="3">
         <f t="shared" si="1"/>
         <v>20501003</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="8">
         <v>205010</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="8">
         <v>3</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="9">
         <v>50</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="F52" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="3">
         <f t="shared" si="1"/>
         <v>20501004</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="8">
         <v>205010</v>
       </c>
-      <c r="C53" s="7">
-        <v>4</v>
-      </c>
-      <c r="D53" s="8">
+      <c r="C53" s="8">
+        <v>4</v>
+      </c>
+      <c r="D53" s="9">
         <v>60</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="54" spans="1:11">
+      <c r="F53" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="3">
         <f t="shared" si="1"/>
         <v>20501005</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="8">
         <v>205010</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C54" s="8">
         <v>5</v>
       </c>
-      <c r="D54" s="7"/>
-      <c r="E54" s="9">
+      <c r="D54" s="8"/>
+      <c r="E54" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="F54" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="3">
         <f t="shared" si="1"/>
         <v>30101101</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="8">
         <v>301011</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C55" s="8">
         <v>1</v>
       </c>
       <c r="D55" s="5">
         <v>10</v>
       </c>
-      <c r="E55" s="9">
-        <v>2</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J55" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K55" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="E55" s="10">
+        <v>2</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="3">
         <f t="shared" si="1"/>
         <v>30101102</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="8">
         <v>301011</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="8">
         <v>2</v>
       </c>
       <c r="D56" s="5">
         <v>20</v>
       </c>
-      <c r="E56" s="9">
-        <v>4</v>
-      </c>
-      <c r="I56" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K56" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="E56" s="10">
+        <v>4</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="3">
         <f t="shared" si="1"/>
         <v>30101103</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="8">
         <v>301011</v>
       </c>
-      <c r="C57" s="7">
+      <c r="C57" s="8">
         <v>3</v>
       </c>
       <c r="D57" s="5">
         <v>30</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="10">
         <v>6</v>
       </c>
-      <c r="I57" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K57" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+      <c r="F57" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="3">
         <f t="shared" si="1"/>
         <v>30101104</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="8">
         <v>301011</v>
       </c>
-      <c r="C58" s="7">
+      <c r="C58" s="8">
         <v>4</v>
       </c>
       <c r="D58" s="5">
         <v>40</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="10">
         <v>8</v>
       </c>
-      <c r="I58" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J58" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K58" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+      <c r="F58" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="3">
         <f t="shared" si="1"/>
         <v>30101105</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="8">
         <v>301011</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C59" s="8">
         <v>5</v>
       </c>
       <c r="D59" s="4"/>
-      <c r="E59" s="9">
+      <c r="E59" s="10">
         <v>10</v>
       </c>
-      <c r="I59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K59" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="F59" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="3">
         <f t="shared" si="1"/>
         <v>30201201</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="8">
         <v>302012</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="8">
         <v>1</v>
       </c>
-      <c r="D60" s="8">
-        <v>15</v>
-      </c>
-      <c r="E60" s="9">
-        <v>2</v>
-      </c>
-      <c r="I60" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J60" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K60" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+      <c r="D60" s="9">
+        <v>15</v>
+      </c>
+      <c r="E60" s="10">
+        <v>2</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="3">
         <f t="shared" si="1"/>
         <v>30201202</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="8">
         <v>302012</v>
       </c>
-      <c r="C61" s="7">
-        <v>2</v>
-      </c>
-      <c r="D61" s="8">
+      <c r="C61" s="8">
+        <v>2</v>
+      </c>
+      <c r="D61" s="9">
         <v>25</v>
       </c>
-      <c r="E61" s="9">
-        <v>4</v>
-      </c>
-      <c r="I61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K61" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+      <c r="E61" s="10">
+        <v>4</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="3">
         <f t="shared" si="1"/>
         <v>30201203</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="8">
         <v>302012</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="8">
         <v>3</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="9">
         <v>35</v>
       </c>
-      <c r="E62" s="9">
+      <c r="E62" s="10">
         <v>6</v>
       </c>
-      <c r="I62" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J62" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K62" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+      <c r="F62" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" s="3">
         <f t="shared" si="1"/>
         <v>30201204</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="8">
         <v>302012</v>
       </c>
-      <c r="C63" s="7">
-        <v>4</v>
-      </c>
-      <c r="D63" s="8">
+      <c r="C63" s="8">
+        <v>4</v>
+      </c>
+      <c r="D63" s="9">
         <v>45</v>
       </c>
-      <c r="E63" s="9">
+      <c r="E63" s="10">
         <v>8</v>
       </c>
-      <c r="I63" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J63" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K63" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+      <c r="F63" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" s="3">
         <f t="shared" si="1"/>
         <v>30201205</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="8">
         <v>302012</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C64" s="8">
         <v>5</v>
       </c>
-      <c r="D64" s="7"/>
-      <c r="E64" s="9">
+      <c r="D64" s="8"/>
+      <c r="E64" s="10">
         <v>10</v>
       </c>
-      <c r="I64" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J64" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="K64" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+      <c r="F64" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" s="3">
         <f t="shared" si="1"/>
         <v>30301301</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="10">
         <v>303013</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="8">
         <v>1</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="9">
         <v>20</v>
       </c>
-      <c r="E65" s="9">
-        <v>2</v>
-      </c>
-      <c r="I65" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J65" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="K65" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+      <c r="E65" s="10">
+        <v>2</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" s="3">
         <f t="shared" si="1"/>
         <v>30301302</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="10">
         <v>303013</v>
       </c>
-      <c r="C66" s="7">
-        <v>2</v>
-      </c>
-      <c r="D66" s="8">
+      <c r="C66" s="8">
+        <v>2</v>
+      </c>
+      <c r="D66" s="9">
         <v>30</v>
       </c>
-      <c r="E66" s="9">
-        <v>4</v>
-      </c>
-      <c r="I66" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J66" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K66" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
+      <c r="E66" s="10">
+        <v>4</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" s="3">
         <f t="shared" si="1"/>
         <v>30301303</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="10">
         <v>303013</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C67" s="8">
         <v>3</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="9">
         <v>40</v>
       </c>
-      <c r="E67" s="9">
+      <c r="E67" s="10">
         <v>6</v>
       </c>
-      <c r="I67" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J67" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K67" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
+      <c r="F67" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" s="3">
         <f t="shared" si="1"/>
         <v>30301304</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="10">
         <v>303013</v>
       </c>
-      <c r="C68" s="7">
-        <v>4</v>
-      </c>
-      <c r="D68" s="8">
+      <c r="C68" s="8">
+        <v>4</v>
+      </c>
+      <c r="D68" s="9">
         <v>50</v>
       </c>
-      <c r="E68" s="9">
+      <c r="E68" s="10">
         <v>8</v>
       </c>
-      <c r="I68" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J68" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="K68" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
+      <c r="F68" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="3">
         <f t="shared" si="1"/>
         <v>30301305</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="10">
         <v>303013</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="8">
         <v>5</v>
       </c>
-      <c r="D69" s="7"/>
-      <c r="E69" s="9">
+      <c r="D69" s="8"/>
+      <c r="E69" s="10">
         <v>10</v>
       </c>
-      <c r="I69" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J69" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="K69" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
+      <c r="F69" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="3">
         <f t="shared" si="1"/>
         <v>30401401</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="8">
         <v>304014</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="8">
         <v>1</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="9">
         <v>25</v>
       </c>
-      <c r="E70" s="9">
-        <v>2</v>
-      </c>
-      <c r="I70" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J70" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K70" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+      <c r="E70" s="10">
+        <v>2</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="3">
         <f t="shared" si="1"/>
         <v>30401402</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="8">
         <v>304014</v>
       </c>
-      <c r="C71" s="7">
-        <v>2</v>
-      </c>
-      <c r="D71" s="8">
+      <c r="C71" s="8">
+        <v>2</v>
+      </c>
+      <c r="D71" s="9">
         <v>35</v>
       </c>
-      <c r="E71" s="9">
-        <v>4</v>
-      </c>
-      <c r="I71" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="J71" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K71" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="E71" s="10">
+        <v>4</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="3">
         <f t="shared" si="1"/>
         <v>30401403</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="8">
         <v>304014</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C72" s="8">
         <v>3</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="9">
         <v>45</v>
       </c>
-      <c r="E72" s="9">
+      <c r="E72" s="10">
         <v>6</v>
       </c>
-      <c r="I72" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="J72" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="K72" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
+      <c r="F72" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" s="3">
         <f t="shared" si="1"/>
         <v>30401404</v>
       </c>
-      <c r="B73" s="7">
+      <c r="B73" s="8">
         <v>304014</v>
       </c>
-      <c r="C73" s="7">
-        <v>4</v>
-      </c>
-      <c r="D73" s="8">
+      <c r="C73" s="8">
+        <v>4</v>
+      </c>
+      <c r="D73" s="9">
         <v>55</v>
       </c>
-      <c r="E73" s="9">
+      <c r="E73" s="10">
         <v>8</v>
       </c>
-      <c r="I73" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="J73" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="K73" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
+      <c r="F73" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="3">
         <f t="shared" si="1"/>
         <v>30401405</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="8">
         <v>304014</v>
       </c>
-      <c r="C74" s="7">
+      <c r="C74" s="8">
         <v>5</v>
       </c>
-      <c r="D74" s="7"/>
-      <c r="E74" s="9">
+      <c r="D74" s="8"/>
+      <c r="E74" s="10">
         <v>10</v>
       </c>
-      <c r="I74" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="J74" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="K74" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
+      <c r="F74" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" s="3">
         <f t="shared" si="1"/>
         <v>30501501</v>
       </c>
-      <c r="B75" s="7">
+      <c r="B75" s="8">
         <v>305015</v>
       </c>
-      <c r="C75" s="7">
+      <c r="C75" s="8">
         <v>1</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="9">
         <v>30</v>
       </c>
-      <c r="E75" s="9">
-        <v>2</v>
-      </c>
-      <c r="I75" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J75" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="K75" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
+      <c r="E75" s="10">
+        <v>2</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" s="3">
         <f t="shared" si="1"/>
         <v>30501502</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="8">
         <v>305015</v>
       </c>
-      <c r="C76" s="7">
-        <v>2</v>
-      </c>
-      <c r="D76" s="8">
+      <c r="C76" s="8">
+        <v>2</v>
+      </c>
+      <c r="D76" s="9">
         <v>40</v>
       </c>
-      <c r="E76" s="9">
-        <v>4</v>
-      </c>
-      <c r="I76" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="K76" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
+      <c r="E76" s="10">
+        <v>4</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" s="3">
         <f t="shared" si="1"/>
         <v>30501503</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77" s="8">
         <v>305015</v>
       </c>
-      <c r="C77" s="7">
+      <c r="C77" s="8">
         <v>3</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="9">
         <v>50</v>
       </c>
-      <c r="E77" s="9">
+      <c r="E77" s="10">
         <v>6</v>
       </c>
-      <c r="I77" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J77" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K77" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
+      <c r="F77" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="3">
         <f t="shared" si="1"/>
         <v>30501504</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78" s="8">
         <v>305015</v>
       </c>
-      <c r="C78" s="7">
-        <v>4</v>
-      </c>
-      <c r="D78" s="8">
+      <c r="C78" s="8">
+        <v>4</v>
+      </c>
+      <c r="D78" s="9">
         <v>60</v>
       </c>
-      <c r="E78" s="9">
+      <c r="E78" s="10">
         <v>8</v>
       </c>
-      <c r="I78" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="J78" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K78" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
+      <c r="F78" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" s="3">
         <f t="shared" si="1"/>
         <v>30501505</v>
       </c>
-      <c r="B79" s="7">
+      <c r="B79" s="8">
         <v>305015</v>
       </c>
-      <c r="C79" s="7">
+      <c r="C79" s="8">
         <v>5</v>
       </c>
-      <c r="D79" s="7"/>
-      <c r="E79" s="9">
+      <c r="D79" s="8"/>
+      <c r="E79" s="10">
         <v>10</v>
       </c>
-      <c r="I79" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="J79" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="K79" s="10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
+      <c r="F79" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="3">
         <f t="shared" ref="A80:A111" si="2">B80*100+C80</f>
         <v>10101601</v>
@@ -3065,8 +2917,11 @@
       <c r="E80" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="81" spans="1:5">
+      <c r="F80" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" s="3">
         <f t="shared" si="2"/>
         <v>10101602</v>
@@ -3083,8 +2938,11 @@
       <c r="E81" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
+      <c r="F81" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" s="3">
         <f t="shared" si="2"/>
         <v>10101603</v>
@@ -3101,8 +2959,11 @@
       <c r="E82" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
+      <c r="F82" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" s="3">
         <f t="shared" si="2"/>
         <v>10101604</v>
@@ -3119,8 +2980,11 @@
       <c r="E83" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="1:5">
+      <c r="F83" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" s="3">
         <f t="shared" si="2"/>
         <v>10101605</v>
@@ -3135,8 +2999,11 @@
       <c r="E84" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="85" spans="1:5">
+      <c r="F84" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" s="3">
         <f t="shared" si="2"/>
         <v>10201701</v>
@@ -3144,17 +3011,20 @@
       <c r="B85" s="1">
         <v>102017</v>
       </c>
-      <c r="C85" s="7">
+      <c r="C85" s="8">
         <v>1</v>
       </c>
-      <c r="D85" s="8">
-        <v>15</v>
-      </c>
-      <c r="E85" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+      <c r="D85" s="9">
+        <v>15</v>
+      </c>
+      <c r="E85" s="10">
+        <v>2</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" s="3">
         <f t="shared" si="2"/>
         <v>10201702</v>
@@ -3162,17 +3032,20 @@
       <c r="B86" s="1">
         <v>102017</v>
       </c>
-      <c r="C86" s="7">
-        <v>2</v>
-      </c>
-      <c r="D86" s="8">
+      <c r="C86" s="8">
+        <v>2</v>
+      </c>
+      <c r="D86" s="9">
         <v>25</v>
       </c>
-      <c r="E86" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+      <c r="E86" s="10">
+        <v>4</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" s="3">
         <f t="shared" si="2"/>
         <v>10201703</v>
@@ -3180,17 +3053,20 @@
       <c r="B87" s="1">
         <v>102017</v>
       </c>
-      <c r="C87" s="7">
+      <c r="C87" s="8">
         <v>3</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="9">
         <v>35</v>
       </c>
-      <c r="E87" s="9">
+      <c r="E87" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="88" spans="1:5">
+      <c r="F87" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" s="3">
         <f t="shared" si="2"/>
         <v>10201704</v>
@@ -3198,17 +3074,20 @@
       <c r="B88" s="1">
         <v>102017</v>
       </c>
-      <c r="C88" s="7">
-        <v>4</v>
-      </c>
-      <c r="D88" s="8">
+      <c r="C88" s="8">
+        <v>4</v>
+      </c>
+      <c r="D88" s="9">
         <v>45</v>
       </c>
-      <c r="E88" s="9">
+      <c r="E88" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="89" spans="1:5">
+      <c r="F88" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" s="3">
         <f t="shared" si="2"/>
         <v>10201705</v>
@@ -3216,1156 +3095,1354 @@
       <c r="B89" s="1">
         <v>102017</v>
       </c>
-      <c r="C89" s="7">
+      <c r="C89" s="8">
         <v>5</v>
       </c>
-      <c r="D89" s="7"/>
-      <c r="E89" s="9">
+      <c r="D89" s="8"/>
+      <c r="E89" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="1:5">
+      <c r="F89" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" s="3">
         <f t="shared" si="2"/>
         <v>10301801</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90" s="8">
         <v>103018</v>
       </c>
-      <c r="C90" s="7">
+      <c r="C90" s="8">
         <v>1</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="9">
         <v>20</v>
       </c>
-      <c r="E90" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+      <c r="E90" s="10">
+        <v>2</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" s="3">
         <f t="shared" si="2"/>
         <v>10301802</v>
       </c>
-      <c r="B91" s="7">
+      <c r="B91" s="8">
         <v>103018</v>
       </c>
-      <c r="C91" s="7">
-        <v>2</v>
-      </c>
-      <c r="D91" s="8">
+      <c r="C91" s="8">
+        <v>2</v>
+      </c>
+      <c r="D91" s="9">
         <v>30</v>
       </c>
-      <c r="E91" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+      <c r="E91" s="10">
+        <v>4</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" s="3">
         <f t="shared" si="2"/>
         <v>10301803</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92" s="8">
         <v>103018</v>
       </c>
-      <c r="C92" s="7">
+      <c r="C92" s="8">
         <v>3</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="9">
         <v>40</v>
       </c>
-      <c r="E92" s="9">
+      <c r="E92" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="93" spans="1:5">
+      <c r="F92" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" s="3">
         <f t="shared" si="2"/>
         <v>10301804</v>
       </c>
-      <c r="B93" s="7">
+      <c r="B93" s="8">
         <v>103018</v>
       </c>
-      <c r="C93" s="7">
-        <v>4</v>
-      </c>
-      <c r="D93" s="8">
+      <c r="C93" s="8">
+        <v>4</v>
+      </c>
+      <c r="D93" s="9">
         <v>50</v>
       </c>
-      <c r="E93" s="9">
+      <c r="E93" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="94" spans="1:5">
+      <c r="F93" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" s="3">
         <f t="shared" si="2"/>
         <v>10301805</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="8">
         <v>103018</v>
       </c>
-      <c r="C94" s="7">
+      <c r="C94" s="8">
         <v>5</v>
       </c>
-      <c r="D94" s="7"/>
-      <c r="E94" s="9">
+      <c r="D94" s="8"/>
+      <c r="E94" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="1:5">
+      <c r="F94" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" s="3">
         <f t="shared" si="2"/>
         <v>10401901</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95" s="8">
         <v>104019</v>
       </c>
-      <c r="C95" s="7">
+      <c r="C95" s="8">
         <v>1</v>
       </c>
-      <c r="D95" s="8">
+      <c r="D95" s="9">
         <v>25</v>
       </c>
-      <c r="E95" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+      <c r="E95" s="10">
+        <v>2</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" s="3">
         <f t="shared" si="2"/>
         <v>10401902</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="8">
         <v>104019</v>
       </c>
-      <c r="C96" s="7">
-        <v>2</v>
-      </c>
-      <c r="D96" s="8">
+      <c r="C96" s="8">
+        <v>2</v>
+      </c>
+      <c r="D96" s="9">
         <v>35</v>
       </c>
-      <c r="E96" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+      <c r="E96" s="10">
+        <v>4</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="3">
         <f t="shared" si="2"/>
         <v>10401903</v>
       </c>
-      <c r="B97" s="7">
+      <c r="B97" s="8">
         <v>104019</v>
       </c>
-      <c r="C97" s="7">
+      <c r="C97" s="8">
         <v>3</v>
       </c>
-      <c r="D97" s="8">
+      <c r="D97" s="9">
         <v>45</v>
       </c>
-      <c r="E97" s="9">
+      <c r="E97" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="F97" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="3">
         <f t="shared" si="2"/>
         <v>10401904</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="8">
         <v>104019</v>
       </c>
-      <c r="C98" s="7">
-        <v>4</v>
-      </c>
-      <c r="D98" s="8">
+      <c r="C98" s="8">
+        <v>4</v>
+      </c>
+      <c r="D98" s="9">
         <v>55</v>
       </c>
-      <c r="E98" s="9">
+      <c r="E98" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="F98" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="3">
         <f t="shared" si="2"/>
         <v>10401905</v>
       </c>
-      <c r="B99" s="7">
+      <c r="B99" s="8">
         <v>104019</v>
       </c>
-      <c r="C99" s="7">
+      <c r="C99" s="8">
         <v>5</v>
       </c>
-      <c r="D99" s="7"/>
-      <c r="E99" s="9">
+      <c r="D99" s="8"/>
+      <c r="E99" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="F99" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" s="3">
         <f t="shared" si="2"/>
         <v>10502001</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100" s="8">
         <v>105020</v>
       </c>
-      <c r="C100" s="7">
+      <c r="C100" s="8">
         <v>1</v>
       </c>
-      <c r="D100" s="8">
+      <c r="D100" s="9">
         <v>30</v>
       </c>
-      <c r="E100" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+      <c r="E100" s="10">
+        <v>2</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" s="3">
         <f t="shared" si="2"/>
         <v>10502002</v>
       </c>
-      <c r="B101" s="7">
+      <c r="B101" s="8">
         <v>105020</v>
       </c>
-      <c r="C101" s="7">
-        <v>2</v>
-      </c>
-      <c r="D101" s="8">
+      <c r="C101" s="8">
+        <v>2</v>
+      </c>
+      <c r="D101" s="9">
         <v>40</v>
       </c>
-      <c r="E101" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+      <c r="E101" s="10">
+        <v>4</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" s="3">
         <f t="shared" si="2"/>
         <v>10502003</v>
       </c>
-      <c r="B102" s="7">
+      <c r="B102" s="8">
         <v>105020</v>
       </c>
-      <c r="C102" s="7">
+      <c r="C102" s="8">
         <v>3</v>
       </c>
-      <c r="D102" s="8">
+      <c r="D102" s="9">
         <v>50</v>
       </c>
-      <c r="E102" s="9">
+      <c r="E102" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="103" spans="1:5">
+      <c r="F102" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" s="3">
         <f t="shared" si="2"/>
         <v>10502004</v>
       </c>
-      <c r="B103" s="7">
+      <c r="B103" s="8">
         <v>105020</v>
       </c>
-      <c r="C103" s="7">
-        <v>4</v>
-      </c>
-      <c r="D103" s="8">
+      <c r="C103" s="8">
+        <v>4</v>
+      </c>
+      <c r="D103" s="9">
         <v>60</v>
       </c>
-      <c r="E103" s="9">
+      <c r="E103" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="104" spans="1:5">
+      <c r="F103" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" s="3">
         <f t="shared" si="2"/>
         <v>10502005</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="8">
         <v>105020</v>
       </c>
-      <c r="C104" s="7">
+      <c r="C104" s="8">
         <v>5</v>
       </c>
-      <c r="D104" s="7"/>
-      <c r="E104" s="9">
+      <c r="D104" s="8"/>
+      <c r="E104" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="105" spans="1:5">
+      <c r="F104" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" s="3">
         <f t="shared" si="2"/>
         <v>20102101</v>
       </c>
-      <c r="B105" s="7">
+      <c r="B105" s="8">
         <v>201021</v>
       </c>
-      <c r="C105" s="7">
+      <c r="C105" s="8">
         <v>1</v>
       </c>
       <c r="D105" s="5">
         <v>10</v>
       </c>
-      <c r="E105" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+      <c r="E105" s="10">
+        <v>2</v>
+      </c>
+      <c r="F105" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" s="3">
         <f t="shared" si="2"/>
         <v>20102102</v>
       </c>
-      <c r="B106" s="7">
+      <c r="B106" s="8">
         <v>201021</v>
       </c>
-      <c r="C106" s="7">
+      <c r="C106" s="8">
         <v>2</v>
       </c>
       <c r="D106" s="5">
         <v>20</v>
       </c>
-      <c r="E106" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+      <c r="E106" s="10">
+        <v>4</v>
+      </c>
+      <c r="F106" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" s="3">
         <f t="shared" si="2"/>
         <v>20102103</v>
       </c>
-      <c r="B107" s="7">
+      <c r="B107" s="8">
         <v>201021</v>
       </c>
-      <c r="C107" s="7">
+      <c r="C107" s="8">
         <v>3</v>
       </c>
       <c r="D107" s="5">
         <v>30</v>
       </c>
-      <c r="E107" s="9">
+      <c r="E107" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="108" spans="1:5">
+      <c r="F107" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="3">
         <f t="shared" si="2"/>
         <v>20102104</v>
       </c>
-      <c r="B108" s="7">
+      <c r="B108" s="8">
         <v>201021</v>
       </c>
-      <c r="C108" s="7">
+      <c r="C108" s="8">
         <v>4</v>
       </c>
       <c r="D108" s="5">
         <v>40</v>
       </c>
-      <c r="E108" s="9">
+      <c r="E108" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="109" spans="1:5">
+      <c r="F108" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="3">
         <f t="shared" si="2"/>
         <v>20102105</v>
       </c>
-      <c r="B109" s="7">
+      <c r="B109" s="8">
         <v>201021</v>
       </c>
-      <c r="C109" s="7">
+      <c r="C109" s="8">
         <v>5</v>
       </c>
       <c r="D109" s="4"/>
-      <c r="E109" s="9">
+      <c r="E109" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="110" spans="1:5">
+      <c r="F109" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" s="3">
         <f t="shared" si="2"/>
         <v>20202201</v>
       </c>
-      <c r="B110" s="7">
+      <c r="B110" s="8">
         <v>202022</v>
       </c>
-      <c r="C110" s="7">
+      <c r="C110" s="8">
         <v>1</v>
       </c>
-      <c r="D110" s="8">
-        <v>15</v>
-      </c>
-      <c r="E110" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+      <c r="D110" s="9">
+        <v>15</v>
+      </c>
+      <c r="E110" s="10">
+        <v>2</v>
+      </c>
+      <c r="F110" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" s="3">
         <f t="shared" si="2"/>
         <v>20202202</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="8">
         <v>202022</v>
       </c>
-      <c r="C111" s="7">
-        <v>2</v>
-      </c>
-      <c r="D111" s="8">
+      <c r="C111" s="8">
+        <v>2</v>
+      </c>
+      <c r="D111" s="9">
         <v>25</v>
       </c>
-      <c r="E111" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+      <c r="E111" s="10">
+        <v>4</v>
+      </c>
+      <c r="F111" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" s="3">
         <f t="shared" ref="A112:A154" si="3">B112*100+C112</f>
         <v>20202203</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="8">
         <v>202022</v>
       </c>
-      <c r="C112" s="7">
+      <c r="C112" s="8">
         <v>3</v>
       </c>
-      <c r="D112" s="8">
+      <c r="D112" s="9">
         <v>35</v>
       </c>
-      <c r="E112" s="9">
+      <c r="E112" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="113" spans="1:5">
+      <c r="F112" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" s="3">
         <f t="shared" si="3"/>
         <v>20202204</v>
       </c>
-      <c r="B113" s="7">
+      <c r="B113" s="8">
         <v>202022</v>
       </c>
-      <c r="C113" s="7">
-        <v>4</v>
-      </c>
-      <c r="D113" s="8">
+      <c r="C113" s="8">
+        <v>4</v>
+      </c>
+      <c r="D113" s="9">
         <v>45</v>
       </c>
-      <c r="E113" s="9">
+      <c r="E113" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="114" spans="1:5">
+      <c r="F113" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" s="3">
         <f t="shared" si="3"/>
         <v>20202205</v>
       </c>
-      <c r="B114" s="7">
+      <c r="B114" s="8">
         <v>202022</v>
       </c>
-      <c r="C114" s="7">
+      <c r="C114" s="8">
         <v>5</v>
       </c>
-      <c r="D114" s="7"/>
-      <c r="E114" s="9">
+      <c r="D114" s="8"/>
+      <c r="E114" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="115" spans="1:5">
+      <c r="F114" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="3">
         <f t="shared" si="3"/>
         <v>20302301</v>
       </c>
-      <c r="B115" s="7">
+      <c r="B115" s="8">
         <v>203023</v>
       </c>
-      <c r="C115" s="7">
+      <c r="C115" s="8">
         <v>1</v>
       </c>
-      <c r="D115" s="8">
+      <c r="D115" s="9">
         <v>20</v>
       </c>
-      <c r="E115" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+      <c r="E115" s="10">
+        <v>2</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" s="3">
         <f t="shared" si="3"/>
         <v>20302302</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="8">
         <v>203023</v>
       </c>
-      <c r="C116" s="7">
-        <v>2</v>
-      </c>
-      <c r="D116" s="8">
+      <c r="C116" s="8">
+        <v>2</v>
+      </c>
+      <c r="D116" s="9">
         <v>30</v>
       </c>
-      <c r="E116" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+      <c r="E116" s="10">
+        <v>4</v>
+      </c>
+      <c r="F116" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" s="3">
         <f t="shared" si="3"/>
         <v>20302303</v>
       </c>
-      <c r="B117" s="7">
+      <c r="B117" s="8">
         <v>203023</v>
       </c>
-      <c r="C117" s="7">
+      <c r="C117" s="8">
         <v>3</v>
       </c>
-      <c r="D117" s="8">
+      <c r="D117" s="9">
         <v>40</v>
       </c>
-      <c r="E117" s="9">
+      <c r="E117" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="118" spans="1:5">
+      <c r="F117" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" s="3">
         <f t="shared" si="3"/>
         <v>20302304</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="8">
         <v>203023</v>
       </c>
-      <c r="C118" s="7">
-        <v>4</v>
-      </c>
-      <c r="D118" s="8">
+      <c r="C118" s="8">
+        <v>4</v>
+      </c>
+      <c r="D118" s="9">
         <v>50</v>
       </c>
-      <c r="E118" s="9">
+      <c r="E118" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="119" spans="1:5">
+      <c r="F118" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" s="3">
         <f t="shared" si="3"/>
         <v>20302305</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="8">
         <v>203023</v>
       </c>
-      <c r="C119" s="7">
+      <c r="C119" s="8">
         <v>5</v>
       </c>
-      <c r="D119" s="7"/>
-      <c r="E119" s="9">
+      <c r="D119" s="8"/>
+      <c r="E119" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="120" spans="1:5">
+      <c r="F119" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" s="3">
         <f t="shared" si="3"/>
         <v>20402401</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="8">
         <v>204024</v>
       </c>
-      <c r="C120" s="7">
+      <c r="C120" s="8">
         <v>1</v>
       </c>
-      <c r="D120" s="8">
+      <c r="D120" s="9">
         <v>25</v>
       </c>
-      <c r="E120" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
+      <c r="E120" s="10">
+        <v>2</v>
+      </c>
+      <c r="F120" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" s="3">
         <f t="shared" si="3"/>
         <v>20402402</v>
       </c>
-      <c r="B121" s="7">
+      <c r="B121" s="8">
         <v>204024</v>
       </c>
-      <c r="C121" s="7">
-        <v>2</v>
-      </c>
-      <c r="D121" s="8">
+      <c r="C121" s="8">
+        <v>2</v>
+      </c>
+      <c r="D121" s="9">
         <v>35</v>
       </c>
-      <c r="E121" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
+      <c r="E121" s="10">
+        <v>4</v>
+      </c>
+      <c r="F121" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" s="3">
         <f t="shared" si="3"/>
         <v>20402403</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="8">
         <v>204024</v>
       </c>
-      <c r="C122" s="7">
+      <c r="C122" s="8">
         <v>3</v>
       </c>
-      <c r="D122" s="8">
+      <c r="D122" s="9">
         <v>45</v>
       </c>
-      <c r="E122" s="9">
+      <c r="E122" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="123" spans="1:5">
+      <c r="F122" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" s="3">
         <f t="shared" si="3"/>
         <v>20402404</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="8">
         <v>204024</v>
       </c>
-      <c r="C123" s="7">
-        <v>4</v>
-      </c>
-      <c r="D123" s="8">
+      <c r="C123" s="8">
+        <v>4</v>
+      </c>
+      <c r="D123" s="9">
         <v>55</v>
       </c>
-      <c r="E123" s="9">
+      <c r="E123" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="124" spans="1:5">
+      <c r="F123" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" s="3">
         <f t="shared" si="3"/>
         <v>20402405</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="8">
         <v>204024</v>
       </c>
-      <c r="C124" s="7">
+      <c r="C124" s="8">
         <v>5</v>
       </c>
-      <c r="D124" s="7"/>
-      <c r="E124" s="9">
+      <c r="D124" s="8"/>
+      <c r="E124" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="125" spans="1:5">
+      <c r="F124" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" s="3">
         <f t="shared" si="3"/>
         <v>20502501</v>
       </c>
-      <c r="B125" s="7">
+      <c r="B125" s="8">
         <v>205025</v>
       </c>
-      <c r="C125" s="7">
+      <c r="C125" s="8">
         <v>1</v>
       </c>
-      <c r="D125" s="8">
+      <c r="D125" s="9">
         <v>30</v>
       </c>
-      <c r="E125" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+      <c r="E125" s="10">
+        <v>2</v>
+      </c>
+      <c r="F125" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" s="3">
         <f t="shared" si="3"/>
         <v>20502502</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="8">
         <v>205025</v>
       </c>
-      <c r="C126" s="7">
-        <v>2</v>
-      </c>
-      <c r="D126" s="8">
+      <c r="C126" s="8">
+        <v>2</v>
+      </c>
+      <c r="D126" s="9">
         <v>40</v>
       </c>
-      <c r="E126" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+      <c r="E126" s="10">
+        <v>4</v>
+      </c>
+      <c r="F126" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" s="3">
         <f t="shared" si="3"/>
         <v>20502503</v>
       </c>
-      <c r="B127" s="7">
+      <c r="B127" s="8">
         <v>205025</v>
       </c>
-      <c r="C127" s="7">
+      <c r="C127" s="8">
         <v>3</v>
       </c>
-      <c r="D127" s="8">
+      <c r="D127" s="9">
         <v>50</v>
       </c>
-      <c r="E127" s="9">
+      <c r="E127" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="128" spans="1:5">
+      <c r="F127" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" s="3">
         <f t="shared" si="3"/>
         <v>20502504</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="8">
         <v>205025</v>
       </c>
-      <c r="C128" s="7">
-        <v>4</v>
-      </c>
-      <c r="D128" s="8">
+      <c r="C128" s="8">
+        <v>4</v>
+      </c>
+      <c r="D128" s="9">
         <v>60</v>
       </c>
-      <c r="E128" s="9">
+      <c r="E128" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="129" spans="1:5">
+      <c r="F128" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" s="3">
         <f t="shared" si="3"/>
         <v>20502505</v>
       </c>
-      <c r="B129" s="7">
+      <c r="B129" s="8">
         <v>205025</v>
       </c>
-      <c r="C129" s="7">
+      <c r="C129" s="8">
         <v>5</v>
       </c>
-      <c r="D129" s="7"/>
-      <c r="E129" s="9">
+      <c r="D129" s="8"/>
+      <c r="E129" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="130" spans="1:5">
+      <c r="F129" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" s="3">
         <f t="shared" si="3"/>
         <v>30102601</v>
       </c>
-      <c r="B130" s="7">
+      <c r="B130" s="8">
         <v>301026</v>
       </c>
-      <c r="C130" s="7">
+      <c r="C130" s="8">
         <v>1</v>
       </c>
       <c r="D130" s="5">
         <v>10</v>
       </c>
-      <c r="E130" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+      <c r="E130" s="10">
+        <v>2</v>
+      </c>
+      <c r="F130" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" s="3">
         <f t="shared" si="3"/>
         <v>30102602</v>
       </c>
-      <c r="B131" s="7">
+      <c r="B131" s="8">
         <v>301026</v>
       </c>
-      <c r="C131" s="7">
+      <c r="C131" s="8">
         <v>2</v>
       </c>
       <c r="D131" s="5">
         <v>20</v>
       </c>
-      <c r="E131" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
+      <c r="E131" s="10">
+        <v>4</v>
+      </c>
+      <c r="F131" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" s="3">
         <f t="shared" si="3"/>
         <v>30102603</v>
       </c>
-      <c r="B132" s="7">
+      <c r="B132" s="8">
         <v>301026</v>
       </c>
-      <c r="C132" s="7">
+      <c r="C132" s="8">
         <v>3</v>
       </c>
       <c r="D132" s="5">
         <v>30</v>
       </c>
-      <c r="E132" s="9">
+      <c r="E132" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="133" spans="1:5">
+      <c r="F132" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" s="3">
         <f t="shared" si="3"/>
         <v>30102604</v>
       </c>
-      <c r="B133" s="7">
+      <c r="B133" s="8">
         <v>301026</v>
       </c>
-      <c r="C133" s="7">
+      <c r="C133" s="8">
         <v>4</v>
       </c>
       <c r="D133" s="5">
         <v>40</v>
       </c>
-      <c r="E133" s="9">
+      <c r="E133" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="134" spans="1:5">
+      <c r="F133" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" s="3">
         <f t="shared" si="3"/>
         <v>30102605</v>
       </c>
-      <c r="B134" s="7">
+      <c r="B134" s="8">
         <v>301026</v>
       </c>
-      <c r="C134" s="7">
+      <c r="C134" s="8">
         <v>5</v>
       </c>
       <c r="D134" s="4"/>
-      <c r="E134" s="9">
+      <c r="E134" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="135" spans="1:5">
+      <c r="F134" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" s="3">
         <f t="shared" si="3"/>
         <v>30202701</v>
       </c>
-      <c r="B135" s="7">
+      <c r="B135" s="8">
         <v>302027</v>
       </c>
-      <c r="C135" s="7">
+      <c r="C135" s="8">
         <v>1</v>
       </c>
-      <c r="D135" s="8">
-        <v>15</v>
-      </c>
-      <c r="E135" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+      <c r="D135" s="9">
+        <v>15</v>
+      </c>
+      <c r="E135" s="10">
+        <v>2</v>
+      </c>
+      <c r="F135" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" s="3">
         <f t="shared" si="3"/>
         <v>30202702</v>
       </c>
-      <c r="B136" s="7">
+      <c r="B136" s="8">
         <v>302027</v>
       </c>
-      <c r="C136" s="7">
-        <v>2</v>
-      </c>
-      <c r="D136" s="8">
+      <c r="C136" s="8">
+        <v>2</v>
+      </c>
+      <c r="D136" s="9">
         <v>25</v>
       </c>
-      <c r="E136" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+      <c r="E136" s="10">
+        <v>4</v>
+      </c>
+      <c r="F136" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137" s="3">
         <f t="shared" si="3"/>
         <v>30202703</v>
       </c>
-      <c r="B137" s="7">
+      <c r="B137" s="8">
         <v>302027</v>
       </c>
-      <c r="C137" s="7">
+      <c r="C137" s="8">
         <v>3</v>
       </c>
-      <c r="D137" s="8">
+      <c r="D137" s="9">
         <v>35</v>
       </c>
-      <c r="E137" s="9">
+      <c r="E137" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="138" spans="1:5">
+      <c r="F137" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" s="3">
         <f t="shared" si="3"/>
         <v>30202704</v>
       </c>
-      <c r="B138" s="7">
+      <c r="B138" s="8">
         <v>302027</v>
       </c>
-      <c r="C138" s="7">
-        <v>4</v>
-      </c>
-      <c r="D138" s="8">
+      <c r="C138" s="8">
+        <v>4</v>
+      </c>
+      <c r="D138" s="9">
         <v>45</v>
       </c>
-      <c r="E138" s="9">
+      <c r="E138" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="139" spans="1:5">
+      <c r="F138" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" s="3">
         <f t="shared" si="3"/>
         <v>30202705</v>
       </c>
-      <c r="B139" s="7">
+      <c r="B139" s="8">
         <v>302027</v>
       </c>
-      <c r="C139" s="7">
+      <c r="C139" s="8">
         <v>5</v>
       </c>
-      <c r="D139" s="7"/>
-      <c r="E139" s="9">
+      <c r="D139" s="8"/>
+      <c r="E139" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="140" spans="1:5">
+      <c r="F139" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" s="3">
         <f t="shared" si="3"/>
         <v>30302801</v>
       </c>
-      <c r="B140" s="9">
+      <c r="B140" s="10">
         <v>303028</v>
       </c>
-      <c r="C140" s="7">
+      <c r="C140" s="8">
         <v>1</v>
       </c>
-      <c r="D140" s="8">
+      <c r="D140" s="9">
         <v>20</v>
       </c>
-      <c r="E140" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
+      <c r="E140" s="10">
+        <v>2</v>
+      </c>
+      <c r="F140" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" s="3">
         <f t="shared" si="3"/>
         <v>30302802</v>
       </c>
-      <c r="B141" s="9">
+      <c r="B141" s="10">
         <v>303028</v>
       </c>
-      <c r="C141" s="7">
-        <v>2</v>
-      </c>
-      <c r="D141" s="8">
+      <c r="C141" s="8">
+        <v>2</v>
+      </c>
+      <c r="D141" s="9">
         <v>30</v>
       </c>
-      <c r="E141" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+      <c r="E141" s="10">
+        <v>4</v>
+      </c>
+      <c r="F141" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" s="3">
         <f t="shared" si="3"/>
         <v>30302803</v>
       </c>
-      <c r="B142" s="9">
+      <c r="B142" s="10">
         <v>303028</v>
       </c>
-      <c r="C142" s="7">
+      <c r="C142" s="8">
         <v>3</v>
       </c>
-      <c r="D142" s="8">
+      <c r="D142" s="9">
         <v>40</v>
       </c>
-      <c r="E142" s="9">
+      <c r="E142" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="143" spans="1:5">
+      <c r="F142" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" s="3">
         <f t="shared" si="3"/>
         <v>30302804</v>
       </c>
-      <c r="B143" s="9">
+      <c r="B143" s="10">
         <v>303028</v>
       </c>
-      <c r="C143" s="7">
-        <v>4</v>
-      </c>
-      <c r="D143" s="8">
+      <c r="C143" s="8">
+        <v>4</v>
+      </c>
+      <c r="D143" s="9">
         <v>50</v>
       </c>
-      <c r="E143" s="9">
+      <c r="E143" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="144" spans="1:5">
+      <c r="F143" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" s="3">
         <f t="shared" si="3"/>
         <v>30302805</v>
       </c>
-      <c r="B144" s="9">
+      <c r="B144" s="10">
         <v>303028</v>
       </c>
-      <c r="C144" s="7">
+      <c r="C144" s="8">
         <v>5</v>
       </c>
-      <c r="D144" s="7"/>
-      <c r="E144" s="9">
+      <c r="D144" s="8"/>
+      <c r="E144" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="145" spans="1:5">
+      <c r="F144" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" s="3">
         <f t="shared" si="3"/>
         <v>30402901</v>
       </c>
-      <c r="B145" s="7">
+      <c r="B145" s="8">
         <v>304029</v>
       </c>
-      <c r="C145" s="7">
+      <c r="C145" s="8">
         <v>1</v>
       </c>
-      <c r="D145" s="8">
+      <c r="D145" s="9">
         <v>25</v>
       </c>
-      <c r="E145" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+      <c r="E145" s="10">
+        <v>2</v>
+      </c>
+      <c r="F145" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" s="3">
         <f t="shared" si="3"/>
         <v>30402902</v>
       </c>
-      <c r="B146" s="7">
+      <c r="B146" s="8">
         <v>304029</v>
       </c>
-      <c r="C146" s="7">
-        <v>2</v>
-      </c>
-      <c r="D146" s="8">
+      <c r="C146" s="8">
+        <v>2</v>
+      </c>
+      <c r="D146" s="9">
         <v>35</v>
       </c>
-      <c r="E146" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+      <c r="E146" s="10">
+        <v>4</v>
+      </c>
+      <c r="F146" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" s="3">
         <f t="shared" si="3"/>
         <v>30402903</v>
       </c>
-      <c r="B147" s="7">
+      <c r="B147" s="8">
         <v>304029</v>
       </c>
-      <c r="C147" s="7">
+      <c r="C147" s="8">
         <v>3</v>
       </c>
-      <c r="D147" s="8">
+      <c r="D147" s="9">
         <v>45</v>
       </c>
-      <c r="E147" s="9">
+      <c r="E147" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="148" spans="1:5">
+      <c r="F147" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" s="3">
         <f t="shared" si="3"/>
         <v>30402904</v>
       </c>
-      <c r="B148" s="7">
+      <c r="B148" s="8">
         <v>304029</v>
       </c>
-      <c r="C148" s="7">
-        <v>4</v>
-      </c>
-      <c r="D148" s="8">
+      <c r="C148" s="8">
+        <v>4</v>
+      </c>
+      <c r="D148" s="9">
         <v>55</v>
       </c>
-      <c r="E148" s="9">
+      <c r="E148" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="149" spans="1:5">
+      <c r="F148" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" s="3">
         <f t="shared" si="3"/>
         <v>30402905</v>
       </c>
-      <c r="B149" s="7">
+      <c r="B149" s="8">
         <v>304029</v>
       </c>
-      <c r="C149" s="7">
+      <c r="C149" s="8">
         <v>5</v>
       </c>
-      <c r="D149" s="7"/>
-      <c r="E149" s="9">
+      <c r="D149" s="8"/>
+      <c r="E149" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="150" spans="1:5">
+      <c r="F149" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" s="3">
         <f t="shared" si="3"/>
         <v>30503001</v>
       </c>
-      <c r="B150" s="7">
+      <c r="B150" s="8">
         <v>305030</v>
       </c>
-      <c r="C150" s="7">
+      <c r="C150" s="8">
         <v>1</v>
       </c>
-      <c r="D150" s="8">
+      <c r="D150" s="9">
         <v>30</v>
       </c>
-      <c r="E150" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
+      <c r="E150" s="10">
+        <v>2</v>
+      </c>
+      <c r="F150" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" s="3">
         <f t="shared" si="3"/>
         <v>30503002</v>
       </c>
-      <c r="B151" s="7">
+      <c r="B151" s="8">
         <v>305030</v>
       </c>
-      <c r="C151" s="7">
-        <v>2</v>
-      </c>
-      <c r="D151" s="8">
+      <c r="C151" s="8">
+        <v>2</v>
+      </c>
+      <c r="D151" s="9">
         <v>40</v>
       </c>
-      <c r="E151" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
+      <c r="E151" s="10">
+        <v>4</v>
+      </c>
+      <c r="F151" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" s="3">
         <f t="shared" si="3"/>
         <v>30503003</v>
       </c>
-      <c r="B152" s="7">
+      <c r="B152" s="8">
         <v>305030</v>
       </c>
-      <c r="C152" s="7">
+      <c r="C152" s="8">
         <v>3</v>
       </c>
-      <c r="D152" s="8">
+      <c r="D152" s="9">
         <v>50</v>
       </c>
-      <c r="E152" s="9">
+      <c r="E152" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="153" spans="1:5">
+      <c r="F152" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" s="3">
         <f t="shared" si="3"/>
         <v>30503004</v>
       </c>
-      <c r="B153" s="7">
+      <c r="B153" s="8">
         <v>305030</v>
       </c>
-      <c r="C153" s="7">
-        <v>4</v>
-      </c>
-      <c r="D153" s="8">
+      <c r="C153" s="8">
+        <v>4</v>
+      </c>
+      <c r="D153" s="9">
         <v>60</v>
       </c>
-      <c r="E153" s="9">
+      <c r="E153" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="154" spans="1:5">
+      <c r="F153" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" s="3">
         <f t="shared" si="3"/>
         <v>30503005</v>
       </c>
-      <c r="B154" s="7">
+      <c r="B154" s="8">
         <v>305030</v>
       </c>
-      <c r="C154" s="7">
+      <c r="C154" s="8">
         <v>5</v>
       </c>
-      <c r="D154" s="7"/>
-      <c r="E154" s="9">
+      <c r="D154" s="8"/>
+      <c r="E154" s="10">
         <v>10</v>
+      </c>
+      <c r="F154" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/EmployeeStar.xlsx
+++ b/hall/resources/sample/EmployeeStar.xlsx
@@ -714,7 +714,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -730,25 +730,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1367,12 +1361,12 @@
         <v>1</v>
       </c>
       <c r="D5" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E5" s="6">
-        <v>2</v>
-      </c>
-      <c r="F5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1388,12 +1382,12 @@
         <v>2</v>
       </c>
       <c r="D6" s="5">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E6" s="6">
-        <v>4</v>
-      </c>
-      <c r="F6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1409,12 +1403,12 @@
         <v>3</v>
       </c>
       <c r="D7" s="5">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="E7" s="6">
-        <v>6</v>
-      </c>
-      <c r="F7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1430,12 +1424,12 @@
         <v>4</v>
       </c>
       <c r="D8" s="5">
-        <v>40</v>
+        <v>540</v>
       </c>
       <c r="E8" s="6">
-        <v>8</v>
-      </c>
-      <c r="F8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1450,11 +1444,13 @@
       <c r="C9" s="4">
         <v>5</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="5">
+        <v>999999</v>
+      </c>
       <c r="E9" s="6">
-        <v>10</v>
-      </c>
-      <c r="F9" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1466,16 +1462,16 @@
       <c r="B10" s="1">
         <v>102002</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>1</v>
       </c>
-      <c r="D10" s="9">
-        <v>15</v>
-      </c>
-      <c r="E10" s="10">
-        <v>2</v>
-      </c>
-      <c r="F10" s="7" t="s">
+      <c r="D10" s="5">
+        <v>20</v>
+      </c>
+      <c r="E10" s="6">
+        <v>12</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1487,16 +1483,16 @@
       <c r="B11" s="1">
         <v>102002</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>2</v>
       </c>
-      <c r="D11" s="9">
-        <v>25</v>
-      </c>
-      <c r="E11" s="10">
-        <v>4</v>
-      </c>
-      <c r="F11" s="7" t="s">
+      <c r="D11" s="5">
+        <v>60</v>
+      </c>
+      <c r="E11" s="6">
+        <v>24</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1508,16 +1504,16 @@
       <c r="B12" s="1">
         <v>102002</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>3</v>
       </c>
-      <c r="D12" s="9">
-        <v>35</v>
-      </c>
-      <c r="E12" s="10">
-        <v>6</v>
-      </c>
-      <c r="F12" s="7" t="s">
+      <c r="D12" s="5">
+        <v>180</v>
+      </c>
+      <c r="E12" s="6">
+        <v>36</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1529,16 +1525,16 @@
       <c r="B13" s="1">
         <v>102002</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>4</v>
       </c>
-      <c r="D13" s="9">
-        <v>45</v>
-      </c>
-      <c r="E13" s="10">
-        <v>8</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="D13" s="5">
+        <v>540</v>
+      </c>
+      <c r="E13" s="6">
+        <v>48</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1550,14 +1546,16 @@
       <c r="B14" s="1">
         <v>102002</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>5</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10">
-        <v>10</v>
-      </c>
-      <c r="F14" s="7" t="s">
+      <c r="D14" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E14" s="6">
+        <v>60</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1566,19 +1564,19 @@
         <f t="shared" si="0"/>
         <v>10300301</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>103003</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>1</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="5">
         <v>20</v>
       </c>
-      <c r="E15" s="10">
-        <v>2</v>
-      </c>
-      <c r="F15" s="7" t="s">
+      <c r="E15" s="6">
+        <v>12</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1587,19 +1585,19 @@
         <f t="shared" si="0"/>
         <v>10300302</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>103003</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>2</v>
       </c>
-      <c r="D16" s="9">
-        <v>30</v>
-      </c>
-      <c r="E16" s="10">
-        <v>4</v>
-      </c>
-      <c r="F16" s="7" t="s">
+      <c r="D16" s="5">
+        <v>60</v>
+      </c>
+      <c r="E16" s="6">
+        <v>24</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1608,19 +1606,19 @@
         <f t="shared" si="0"/>
         <v>10300303</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>103003</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>3</v>
       </c>
-      <c r="D17" s="9">
-        <v>40</v>
-      </c>
-      <c r="E17" s="10">
-        <v>6</v>
-      </c>
-      <c r="F17" s="7" t="s">
+      <c r="D17" s="5">
+        <v>180</v>
+      </c>
+      <c r="E17" s="6">
+        <v>36</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1629,19 +1627,19 @@
         <f t="shared" si="0"/>
         <v>10300304</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>103003</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>4</v>
       </c>
-      <c r="D18" s="9">
-        <v>50</v>
-      </c>
-      <c r="E18" s="10">
-        <v>8</v>
-      </c>
-      <c r="F18" s="7" t="s">
+      <c r="D18" s="5">
+        <v>540</v>
+      </c>
+      <c r="E18" s="6">
+        <v>48</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1650,17 +1648,19 @@
         <f t="shared" si="0"/>
         <v>10300305</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <v>103003</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>5</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="10">
-        <v>10</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="D19" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E19" s="6">
+        <v>60</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1669,19 +1669,19 @@
         <f t="shared" si="0"/>
         <v>10400401</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="7">
         <v>104004</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <v>1</v>
       </c>
-      <c r="D20" s="9">
-        <v>25</v>
-      </c>
-      <c r="E20" s="10">
-        <v>2</v>
-      </c>
-      <c r="F20" s="7" t="s">
+      <c r="D20" s="5">
+        <v>20</v>
+      </c>
+      <c r="E20" s="6">
+        <v>12</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1690,19 +1690,19 @@
         <f t="shared" si="0"/>
         <v>10400402</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="7">
         <v>104004</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="7">
         <v>2</v>
       </c>
-      <c r="D21" s="9">
-        <v>35</v>
-      </c>
-      <c r="E21" s="10">
-        <v>4</v>
-      </c>
-      <c r="F21" s="7" t="s">
+      <c r="D21" s="5">
+        <v>60</v>
+      </c>
+      <c r="E21" s="6">
+        <v>24</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1711,19 +1711,19 @@
         <f t="shared" si="0"/>
         <v>10400403</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="7">
         <v>104004</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="7">
         <v>3</v>
       </c>
-      <c r="D22" s="9">
-        <v>45</v>
-      </c>
-      <c r="E22" s="10">
-        <v>6</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="D22" s="5">
+        <v>180</v>
+      </c>
+      <c r="E22" s="6">
+        <v>36</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1732,19 +1732,19 @@
         <f t="shared" si="0"/>
         <v>10400404</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="7">
         <v>104004</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="7">
         <v>4</v>
       </c>
-      <c r="D23" s="9">
-        <v>55</v>
-      </c>
-      <c r="E23" s="10">
-        <v>8</v>
-      </c>
-      <c r="F23" s="7" t="s">
+      <c r="D23" s="5">
+        <v>540</v>
+      </c>
+      <c r="E23" s="6">
+        <v>48</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1753,17 +1753,19 @@
         <f t="shared" si="0"/>
         <v>10400405</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="7">
         <v>104004</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="7">
         <v>5</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="10">
-        <v>10</v>
-      </c>
-      <c r="F24" s="7" t="s">
+      <c r="D24" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E24" s="6">
+        <v>60</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1772,19 +1774,19 @@
         <f t="shared" si="0"/>
         <v>10500501</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="7">
         <v>105005</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="7">
         <v>1</v>
       </c>
-      <c r="D25" s="9">
-        <v>30</v>
-      </c>
-      <c r="E25" s="10">
-        <v>2</v>
-      </c>
-      <c r="F25" s="7" t="s">
+      <c r="D25" s="5">
+        <v>20</v>
+      </c>
+      <c r="E25" s="6">
+        <v>12</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1793,19 +1795,19 @@
         <f t="shared" si="0"/>
         <v>10500502</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="7">
         <v>105005</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="7">
         <v>2</v>
       </c>
-      <c r="D26" s="9">
-        <v>40</v>
-      </c>
-      <c r="E26" s="10">
-        <v>4</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="D26" s="5">
+        <v>60</v>
+      </c>
+      <c r="E26" s="6">
+        <v>24</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1814,19 +1816,19 @@
         <f t="shared" si="0"/>
         <v>10500503</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="7">
         <v>105005</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>3</v>
       </c>
-      <c r="D27" s="9">
-        <v>50</v>
-      </c>
-      <c r="E27" s="10">
-        <v>6</v>
-      </c>
-      <c r="F27" s="7" t="s">
+      <c r="D27" s="5">
+        <v>180</v>
+      </c>
+      <c r="E27" s="6">
+        <v>36</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1835,19 +1837,19 @@
         <f t="shared" si="0"/>
         <v>10500504</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="7">
         <v>105005</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="7">
         <v>4</v>
       </c>
-      <c r="D28" s="9">
-        <v>60</v>
-      </c>
-      <c r="E28" s="10">
-        <v>8</v>
-      </c>
-      <c r="F28" s="7" t="s">
+      <c r="D28" s="5">
+        <v>540</v>
+      </c>
+      <c r="E28" s="6">
+        <v>48</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1856,17 +1858,19 @@
         <f t="shared" si="0"/>
         <v>10500505</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <v>105005</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="7">
         <v>5</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="10">
-        <v>10</v>
-      </c>
-      <c r="F29" s="7" t="s">
+      <c r="D29" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E29" s="6">
+        <v>60</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1875,19 +1879,19 @@
         <f t="shared" si="0"/>
         <v>20100601</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="7">
         <v>201006</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="7">
         <v>1</v>
       </c>
       <c r="D30" s="5">
-        <v>10</v>
-      </c>
-      <c r="E30" s="10">
-        <v>2</v>
-      </c>
-      <c r="F30" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="6">
+        <v>12</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1896,19 +1900,19 @@
         <f t="shared" si="0"/>
         <v>20100602</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="7">
         <v>201006</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="7">
         <v>2</v>
       </c>
       <c r="D31" s="5">
-        <v>20</v>
-      </c>
-      <c r="E31" s="10">
-        <v>4</v>
-      </c>
-      <c r="F31" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="6">
+        <v>24</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1917,19 +1921,19 @@
         <f t="shared" si="0"/>
         <v>20100603</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="7">
         <v>201006</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="7">
         <v>3</v>
       </c>
       <c r="D32" s="5">
-        <v>30</v>
-      </c>
-      <c r="E32" s="10">
-        <v>6</v>
-      </c>
-      <c r="F32" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E32" s="6">
+        <v>36</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1938,19 +1942,19 @@
         <f t="shared" si="0"/>
         <v>20100604</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="7">
         <v>201006</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="7">
         <v>4</v>
       </c>
       <c r="D33" s="5">
-        <v>40</v>
-      </c>
-      <c r="E33" s="10">
-        <v>8</v>
-      </c>
-      <c r="F33" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="E33" s="6">
+        <v>48</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1959,17 +1963,19 @@
         <f t="shared" si="0"/>
         <v>20100605</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="7">
         <v>201006</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="7">
         <v>5</v>
       </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="10">
-        <v>10</v>
-      </c>
-      <c r="F34" s="11" t="s">
+      <c r="D34" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E34" s="6">
+        <v>60</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1978,19 +1984,19 @@
         <f t="shared" si="0"/>
         <v>20200701</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="7">
         <v>202007</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="7">
         <v>1</v>
       </c>
-      <c r="D35" s="9">
-        <v>15</v>
-      </c>
-      <c r="E35" s="10">
-        <v>2</v>
-      </c>
-      <c r="F35" s="11" t="s">
+      <c r="D35" s="5">
+        <v>20</v>
+      </c>
+      <c r="E35" s="6">
+        <v>12</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1999,19 +2005,19 @@
         <f t="shared" si="0"/>
         <v>20200702</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="7">
         <v>202007</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="7">
         <v>2</v>
       </c>
-      <c r="D36" s="9">
-        <v>25</v>
-      </c>
-      <c r="E36" s="10">
-        <v>4</v>
-      </c>
-      <c r="F36" s="11" t="s">
+      <c r="D36" s="5">
+        <v>60</v>
+      </c>
+      <c r="E36" s="6">
+        <v>24</v>
+      </c>
+      <c r="F36" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2020,19 +2026,19 @@
         <f t="shared" si="0"/>
         <v>20200703</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="7">
         <v>202007</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="7">
         <v>3</v>
       </c>
-      <c r="D37" s="9">
-        <v>35</v>
-      </c>
-      <c r="E37" s="10">
-        <v>6</v>
-      </c>
-      <c r="F37" s="11" t="s">
+      <c r="D37" s="5">
+        <v>180</v>
+      </c>
+      <c r="E37" s="6">
+        <v>36</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2041,19 +2047,19 @@
         <f t="shared" ref="A38:A79" si="1">B38*100+C38</f>
         <v>20200704</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="7">
         <v>202007</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="7">
         <v>4</v>
       </c>
-      <c r="D38" s="9">
-        <v>45</v>
-      </c>
-      <c r="E38" s="10">
-        <v>8</v>
-      </c>
-      <c r="F38" s="11" t="s">
+      <c r="D38" s="5">
+        <v>540</v>
+      </c>
+      <c r="E38" s="6">
+        <v>48</v>
+      </c>
+      <c r="F38" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2062,17 +2068,19 @@
         <f t="shared" si="1"/>
         <v>20200705</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="7">
         <v>202007</v>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="7">
         <v>5</v>
       </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="10">
-        <v>10</v>
-      </c>
-      <c r="F39" s="11" t="s">
+      <c r="D39" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E39" s="6">
+        <v>60</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2081,19 +2089,19 @@
         <f t="shared" si="1"/>
         <v>20300801</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="7">
         <v>203008</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="7">
         <v>1</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="5">
         <v>20</v>
       </c>
-      <c r="E40" s="10">
-        <v>2</v>
-      </c>
-      <c r="F40" s="11" t="s">
+      <c r="E40" s="6">
+        <v>12</v>
+      </c>
+      <c r="F40" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2102,19 +2110,19 @@
         <f t="shared" si="1"/>
         <v>20300802</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="7">
         <v>203008</v>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="7">
         <v>2</v>
       </c>
-      <c r="D41" s="9">
-        <v>30</v>
-      </c>
-      <c r="E41" s="10">
-        <v>4</v>
-      </c>
-      <c r="F41" s="11" t="s">
+      <c r="D41" s="5">
+        <v>60</v>
+      </c>
+      <c r="E41" s="6">
+        <v>24</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2123,19 +2131,19 @@
         <f t="shared" si="1"/>
         <v>20300803</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="7">
         <v>203008</v>
       </c>
-      <c r="C42" s="8">
+      <c r="C42" s="7">
         <v>3</v>
       </c>
-      <c r="D42" s="9">
-        <v>40</v>
-      </c>
-      <c r="E42" s="10">
-        <v>6</v>
-      </c>
-      <c r="F42" s="11" t="s">
+      <c r="D42" s="5">
+        <v>180</v>
+      </c>
+      <c r="E42" s="6">
+        <v>36</v>
+      </c>
+      <c r="F42" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2144,19 +2152,19 @@
         <f t="shared" si="1"/>
         <v>20300804</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="7">
         <v>203008</v>
       </c>
-      <c r="C43" s="8">
+      <c r="C43" s="7">
         <v>4</v>
       </c>
-      <c r="D43" s="9">
-        <v>50</v>
-      </c>
-      <c r="E43" s="10">
-        <v>8</v>
-      </c>
-      <c r="F43" s="11" t="s">
+      <c r="D43" s="5">
+        <v>540</v>
+      </c>
+      <c r="E43" s="6">
+        <v>48</v>
+      </c>
+      <c r="F43" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2165,17 +2173,19 @@
         <f t="shared" si="1"/>
         <v>20300805</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="7">
         <v>203008</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="7">
         <v>5</v>
       </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="10">
-        <v>10</v>
-      </c>
-      <c r="F44" s="11" t="s">
+      <c r="D44" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E44" s="6">
+        <v>60</v>
+      </c>
+      <c r="F44" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2184,19 +2194,19 @@
         <f t="shared" si="1"/>
         <v>20400901</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="7">
         <v>204009</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="7">
         <v>1</v>
       </c>
-      <c r="D45" s="9">
-        <v>25</v>
-      </c>
-      <c r="E45" s="10">
-        <v>2</v>
-      </c>
-      <c r="F45" s="11" t="s">
+      <c r="D45" s="5">
+        <v>20</v>
+      </c>
+      <c r="E45" s="6">
+        <v>12</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2205,19 +2215,19 @@
         <f t="shared" si="1"/>
         <v>20400902</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="7">
         <v>204009</v>
       </c>
-      <c r="C46" s="8">
+      <c r="C46" s="7">
         <v>2</v>
       </c>
-      <c r="D46" s="9">
-        <v>35</v>
-      </c>
-      <c r="E46" s="10">
-        <v>4</v>
-      </c>
-      <c r="F46" s="11" t="s">
+      <c r="D46" s="5">
+        <v>60</v>
+      </c>
+      <c r="E46" s="6">
+        <v>24</v>
+      </c>
+      <c r="F46" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2226,19 +2236,19 @@
         <f t="shared" si="1"/>
         <v>20400903</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="7">
         <v>204009</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C47" s="7">
         <v>3</v>
       </c>
-      <c r="D47" s="9">
-        <v>45</v>
-      </c>
-      <c r="E47" s="10">
-        <v>6</v>
-      </c>
-      <c r="F47" s="11" t="s">
+      <c r="D47" s="5">
+        <v>180</v>
+      </c>
+      <c r="E47" s="6">
+        <v>36</v>
+      </c>
+      <c r="F47" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2247,19 +2257,19 @@
         <f t="shared" si="1"/>
         <v>20400904</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="7">
         <v>204009</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="7">
         <v>4</v>
       </c>
-      <c r="D48" s="9">
-        <v>55</v>
-      </c>
-      <c r="E48" s="10">
-        <v>8</v>
-      </c>
-      <c r="F48" s="11" t="s">
+      <c r="D48" s="5">
+        <v>540</v>
+      </c>
+      <c r="E48" s="6">
+        <v>48</v>
+      </c>
+      <c r="F48" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2268,17 +2278,19 @@
         <f t="shared" si="1"/>
         <v>20400905</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="7">
         <v>204009</v>
       </c>
-      <c r="C49" s="8">
+      <c r="C49" s="7">
         <v>5</v>
       </c>
-      <c r="D49" s="8"/>
-      <c r="E49" s="10">
-        <v>10</v>
-      </c>
-      <c r="F49" s="11" t="s">
+      <c r="D49" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E49" s="6">
+        <v>60</v>
+      </c>
+      <c r="F49" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2287,19 +2299,19 @@
         <f t="shared" si="1"/>
         <v>20501001</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="7">
         <v>205010</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="7">
         <v>1</v>
       </c>
-      <c r="D50" s="9">
-        <v>30</v>
-      </c>
-      <c r="E50" s="10">
-        <v>2</v>
-      </c>
-      <c r="F50" s="11" t="s">
+      <c r="D50" s="5">
+        <v>20</v>
+      </c>
+      <c r="E50" s="6">
+        <v>12</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2308,19 +2320,19 @@
         <f t="shared" si="1"/>
         <v>20501002</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="7">
         <v>205010</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="7">
         <v>2</v>
       </c>
-      <c r="D51" s="9">
-        <v>40</v>
-      </c>
-      <c r="E51" s="10">
-        <v>4</v>
-      </c>
-      <c r="F51" s="11" t="s">
+      <c r="D51" s="5">
+        <v>60</v>
+      </c>
+      <c r="E51" s="6">
+        <v>24</v>
+      </c>
+      <c r="F51" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2329,19 +2341,19 @@
         <f t="shared" si="1"/>
         <v>20501003</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="7">
         <v>205010</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="7">
         <v>3</v>
       </c>
-      <c r="D52" s="9">
-        <v>50</v>
-      </c>
-      <c r="E52" s="10">
-        <v>6</v>
-      </c>
-      <c r="F52" s="11" t="s">
+      <c r="D52" s="5">
+        <v>180</v>
+      </c>
+      <c r="E52" s="6">
+        <v>36</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2350,19 +2362,19 @@
         <f t="shared" si="1"/>
         <v>20501004</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="7">
         <v>205010</v>
       </c>
-      <c r="C53" s="8">
+      <c r="C53" s="7">
         <v>4</v>
       </c>
-      <c r="D53" s="9">
-        <v>60</v>
-      </c>
-      <c r="E53" s="10">
-        <v>8</v>
-      </c>
-      <c r="F53" s="11" t="s">
+      <c r="D53" s="5">
+        <v>540</v>
+      </c>
+      <c r="E53" s="6">
+        <v>48</v>
+      </c>
+      <c r="F53" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2371,17 +2383,19 @@
         <f t="shared" si="1"/>
         <v>20501005</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="7">
         <v>205010</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C54" s="7">
         <v>5</v>
       </c>
-      <c r="D54" s="8"/>
-      <c r="E54" s="10">
-        <v>10</v>
-      </c>
-      <c r="F54" s="11" t="s">
+      <c r="D54" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E54" s="6">
+        <v>60</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2390,19 +2404,19 @@
         <f t="shared" si="1"/>
         <v>30101101</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="7">
         <v>301011</v>
       </c>
-      <c r="C55" s="8">
+      <c r="C55" s="7">
         <v>1</v>
       </c>
       <c r="D55" s="5">
-        <v>10</v>
-      </c>
-      <c r="E55" s="10">
-        <v>2</v>
-      </c>
-      <c r="F55" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="6">
+        <v>12</v>
+      </c>
+      <c r="F55" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2411,19 +2425,19 @@
         <f t="shared" si="1"/>
         <v>30101102</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="7">
         <v>301011</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C56" s="7">
         <v>2</v>
       </c>
       <c r="D56" s="5">
-        <v>20</v>
-      </c>
-      <c r="E56" s="10">
-        <v>4</v>
-      </c>
-      <c r="F56" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E56" s="6">
+        <v>24</v>
+      </c>
+      <c r="F56" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2432,19 +2446,19 @@
         <f t="shared" si="1"/>
         <v>30101103</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="7">
         <v>301011</v>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="7">
         <v>3</v>
       </c>
       <c r="D57" s="5">
-        <v>30</v>
-      </c>
-      <c r="E57" s="10">
-        <v>6</v>
-      </c>
-      <c r="F57" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E57" s="6">
+        <v>36</v>
+      </c>
+      <c r="F57" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2453,19 +2467,19 @@
         <f t="shared" si="1"/>
         <v>30101104</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="7">
         <v>301011</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="7">
         <v>4</v>
       </c>
       <c r="D58" s="5">
-        <v>40</v>
-      </c>
-      <c r="E58" s="10">
-        <v>8</v>
-      </c>
-      <c r="F58" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="E58" s="6">
+        <v>48</v>
+      </c>
+      <c r="F58" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2474,17 +2488,19 @@
         <f t="shared" si="1"/>
         <v>30101105</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="7">
         <v>301011</v>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="7">
         <v>5</v>
       </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="10">
-        <v>10</v>
-      </c>
-      <c r="F59" s="11" t="s">
+      <c r="D59" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E59" s="6">
+        <v>60</v>
+      </c>
+      <c r="F59" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2493,19 +2509,19 @@
         <f t="shared" si="1"/>
         <v>30201201</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="7">
         <v>302012</v>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="7">
         <v>1</v>
       </c>
-      <c r="D60" s="9">
-        <v>15</v>
-      </c>
-      <c r="E60" s="10">
-        <v>2</v>
-      </c>
-      <c r="F60" s="11" t="s">
+      <c r="D60" s="5">
+        <v>20</v>
+      </c>
+      <c r="E60" s="6">
+        <v>12</v>
+      </c>
+      <c r="F60" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2514,19 +2530,19 @@
         <f t="shared" si="1"/>
         <v>30201202</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="7">
         <v>302012</v>
       </c>
-      <c r="C61" s="8">
+      <c r="C61" s="7">
         <v>2</v>
       </c>
-      <c r="D61" s="9">
-        <v>25</v>
-      </c>
-      <c r="E61" s="10">
-        <v>4</v>
-      </c>
-      <c r="F61" s="11" t="s">
+      <c r="D61" s="5">
+        <v>60</v>
+      </c>
+      <c r="E61" s="6">
+        <v>24</v>
+      </c>
+      <c r="F61" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2535,19 +2551,19 @@
         <f t="shared" si="1"/>
         <v>30201203</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="7">
         <v>302012</v>
       </c>
-      <c r="C62" s="8">
+      <c r="C62" s="7">
         <v>3</v>
       </c>
-      <c r="D62" s="9">
-        <v>35</v>
-      </c>
-      <c r="E62" s="10">
-        <v>6</v>
-      </c>
-      <c r="F62" s="11" t="s">
+      <c r="D62" s="5">
+        <v>180</v>
+      </c>
+      <c r="E62" s="6">
+        <v>36</v>
+      </c>
+      <c r="F62" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2556,19 +2572,19 @@
         <f t="shared" si="1"/>
         <v>30201204</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="7">
         <v>302012</v>
       </c>
-      <c r="C63" s="8">
+      <c r="C63" s="7">
         <v>4</v>
       </c>
-      <c r="D63" s="9">
-        <v>45</v>
-      </c>
-      <c r="E63" s="10">
-        <v>8</v>
-      </c>
-      <c r="F63" s="11" t="s">
+      <c r="D63" s="5">
+        <v>540</v>
+      </c>
+      <c r="E63" s="6">
+        <v>48</v>
+      </c>
+      <c r="F63" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2577,17 +2593,19 @@
         <f t="shared" si="1"/>
         <v>30201205</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B64" s="7">
         <v>302012</v>
       </c>
-      <c r="C64" s="8">
+      <c r="C64" s="7">
         <v>5</v>
       </c>
-      <c r="D64" s="8"/>
-      <c r="E64" s="10">
-        <v>10</v>
-      </c>
-      <c r="F64" s="11" t="s">
+      <c r="D64" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E64" s="6">
+        <v>60</v>
+      </c>
+      <c r="F64" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2596,19 +2614,19 @@
         <f t="shared" si="1"/>
         <v>30301301</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="9">
         <v>303013</v>
       </c>
-      <c r="C65" s="8">
+      <c r="C65" s="7">
         <v>1</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="5">
         <v>20</v>
       </c>
-      <c r="E65" s="10">
-        <v>2</v>
-      </c>
-      <c r="F65" s="11" t="s">
+      <c r="E65" s="6">
+        <v>12</v>
+      </c>
+      <c r="F65" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2617,19 +2635,19 @@
         <f t="shared" si="1"/>
         <v>30301302</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="9">
         <v>303013</v>
       </c>
-      <c r="C66" s="8">
+      <c r="C66" s="7">
         <v>2</v>
       </c>
-      <c r="D66" s="9">
-        <v>30</v>
-      </c>
-      <c r="E66" s="10">
-        <v>4</v>
-      </c>
-      <c r="F66" s="11" t="s">
+      <c r="D66" s="5">
+        <v>60</v>
+      </c>
+      <c r="E66" s="6">
+        <v>24</v>
+      </c>
+      <c r="F66" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2638,19 +2656,19 @@
         <f t="shared" si="1"/>
         <v>30301303</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="9">
         <v>303013</v>
       </c>
-      <c r="C67" s="8">
+      <c r="C67" s="7">
         <v>3</v>
       </c>
-      <c r="D67" s="9">
-        <v>40</v>
-      </c>
-      <c r="E67" s="10">
-        <v>6</v>
-      </c>
-      <c r="F67" s="11" t="s">
+      <c r="D67" s="5">
+        <v>180</v>
+      </c>
+      <c r="E67" s="6">
+        <v>36</v>
+      </c>
+      <c r="F67" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2659,19 +2677,19 @@
         <f t="shared" si="1"/>
         <v>30301304</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="9">
         <v>303013</v>
       </c>
-      <c r="C68" s="8">
+      <c r="C68" s="7">
         <v>4</v>
       </c>
-      <c r="D68" s="9">
-        <v>50</v>
-      </c>
-      <c r="E68" s="10">
-        <v>8</v>
-      </c>
-      <c r="F68" s="11" t="s">
+      <c r="D68" s="5">
+        <v>540</v>
+      </c>
+      <c r="E68" s="6">
+        <v>48</v>
+      </c>
+      <c r="F68" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2680,17 +2698,19 @@
         <f t="shared" si="1"/>
         <v>30301305</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="9">
         <v>303013</v>
       </c>
-      <c r="C69" s="8">
+      <c r="C69" s="7">
         <v>5</v>
       </c>
-      <c r="D69" s="8"/>
-      <c r="E69" s="10">
-        <v>10</v>
-      </c>
-      <c r="F69" s="11" t="s">
+      <c r="D69" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E69" s="6">
+        <v>60</v>
+      </c>
+      <c r="F69" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2699,19 +2719,19 @@
         <f t="shared" si="1"/>
         <v>30401401</v>
       </c>
-      <c r="B70" s="8">
+      <c r="B70" s="7">
         <v>304014</v>
       </c>
-      <c r="C70" s="8">
+      <c r="C70" s="7">
         <v>1</v>
       </c>
-      <c r="D70" s="9">
-        <v>25</v>
-      </c>
-      <c r="E70" s="10">
-        <v>2</v>
-      </c>
-      <c r="F70" s="11" t="s">
+      <c r="D70" s="5">
+        <v>20</v>
+      </c>
+      <c r="E70" s="6">
+        <v>12</v>
+      </c>
+      <c r="F70" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2720,19 +2740,19 @@
         <f t="shared" si="1"/>
         <v>30401402</v>
       </c>
-      <c r="B71" s="8">
+      <c r="B71" s="7">
         <v>304014</v>
       </c>
-      <c r="C71" s="8">
+      <c r="C71" s="7">
         <v>2</v>
       </c>
-      <c r="D71" s="9">
-        <v>35</v>
-      </c>
-      <c r="E71" s="10">
-        <v>4</v>
-      </c>
-      <c r="F71" s="11" t="s">
+      <c r="D71" s="5">
+        <v>60</v>
+      </c>
+      <c r="E71" s="6">
+        <v>24</v>
+      </c>
+      <c r="F71" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2741,19 +2761,19 @@
         <f t="shared" si="1"/>
         <v>30401403</v>
       </c>
-      <c r="B72" s="8">
+      <c r="B72" s="7">
         <v>304014</v>
       </c>
-      <c r="C72" s="8">
+      <c r="C72" s="7">
         <v>3</v>
       </c>
-      <c r="D72" s="9">
-        <v>45</v>
-      </c>
-      <c r="E72" s="10">
-        <v>6</v>
-      </c>
-      <c r="F72" s="11" t="s">
+      <c r="D72" s="5">
+        <v>180</v>
+      </c>
+      <c r="E72" s="6">
+        <v>36</v>
+      </c>
+      <c r="F72" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2762,19 +2782,19 @@
         <f t="shared" si="1"/>
         <v>30401404</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="7">
         <v>304014</v>
       </c>
-      <c r="C73" s="8">
+      <c r="C73" s="7">
         <v>4</v>
       </c>
-      <c r="D73" s="9">
-        <v>55</v>
-      </c>
-      <c r="E73" s="10">
-        <v>8</v>
-      </c>
-      <c r="F73" s="11" t="s">
+      <c r="D73" s="5">
+        <v>540</v>
+      </c>
+      <c r="E73" s="6">
+        <v>48</v>
+      </c>
+      <c r="F73" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2783,17 +2803,19 @@
         <f t="shared" si="1"/>
         <v>30401405</v>
       </c>
-      <c r="B74" s="8">
+      <c r="B74" s="7">
         <v>304014</v>
       </c>
-      <c r="C74" s="8">
+      <c r="C74" s="7">
         <v>5</v>
       </c>
-      <c r="D74" s="8"/>
-      <c r="E74" s="10">
-        <v>10</v>
-      </c>
-      <c r="F74" s="11" t="s">
+      <c r="D74" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E74" s="6">
+        <v>60</v>
+      </c>
+      <c r="F74" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2802,19 +2824,19 @@
         <f t="shared" si="1"/>
         <v>30501501</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="7">
         <v>305015</v>
       </c>
-      <c r="C75" s="8">
+      <c r="C75" s="7">
         <v>1</v>
       </c>
-      <c r="D75" s="9">
-        <v>30</v>
-      </c>
-      <c r="E75" s="10">
-        <v>2</v>
-      </c>
-      <c r="F75" s="11" t="s">
+      <c r="D75" s="5">
+        <v>20</v>
+      </c>
+      <c r="E75" s="6">
+        <v>12</v>
+      </c>
+      <c r="F75" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2823,19 +2845,19 @@
         <f t="shared" si="1"/>
         <v>30501502</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="7">
         <v>305015</v>
       </c>
-      <c r="C76" s="8">
+      <c r="C76" s="7">
         <v>2</v>
       </c>
-      <c r="D76" s="9">
-        <v>40</v>
-      </c>
-      <c r="E76" s="10">
-        <v>4</v>
-      </c>
-      <c r="F76" s="11" t="s">
+      <c r="D76" s="5">
+        <v>60</v>
+      </c>
+      <c r="E76" s="6">
+        <v>24</v>
+      </c>
+      <c r="F76" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2844,19 +2866,19 @@
         <f t="shared" si="1"/>
         <v>30501503</v>
       </c>
-      <c r="B77" s="8">
+      <c r="B77" s="7">
         <v>305015</v>
       </c>
-      <c r="C77" s="8">
+      <c r="C77" s="7">
         <v>3</v>
       </c>
-      <c r="D77" s="9">
-        <v>50</v>
-      </c>
-      <c r="E77" s="10">
-        <v>6</v>
-      </c>
-      <c r="F77" s="11" t="s">
+      <c r="D77" s="5">
+        <v>180</v>
+      </c>
+      <c r="E77" s="6">
+        <v>36</v>
+      </c>
+      <c r="F77" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2865,19 +2887,19 @@
         <f t="shared" si="1"/>
         <v>30501504</v>
       </c>
-      <c r="B78" s="8">
+      <c r="B78" s="7">
         <v>305015</v>
       </c>
-      <c r="C78" s="8">
+      <c r="C78" s="7">
         <v>4</v>
       </c>
-      <c r="D78" s="9">
-        <v>60</v>
-      </c>
-      <c r="E78" s="10">
-        <v>8</v>
-      </c>
-      <c r="F78" s="11" t="s">
+      <c r="D78" s="5">
+        <v>540</v>
+      </c>
+      <c r="E78" s="6">
+        <v>48</v>
+      </c>
+      <c r="F78" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2886,17 +2908,19 @@
         <f t="shared" si="1"/>
         <v>30501505</v>
       </c>
-      <c r="B79" s="8">
+      <c r="B79" s="7">
         <v>305015</v>
       </c>
-      <c r="C79" s="8">
+      <c r="C79" s="7">
         <v>5</v>
       </c>
-      <c r="D79" s="8"/>
-      <c r="E79" s="10">
-        <v>10</v>
-      </c>
-      <c r="F79" s="11" t="s">
+      <c r="D79" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E79" s="6">
+        <v>60</v>
+      </c>
+      <c r="F79" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2912,12 +2936,12 @@
         <v>1</v>
       </c>
       <c r="D80" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E80" s="6">
-        <v>2</v>
-      </c>
-      <c r="F80" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2933,12 +2957,12 @@
         <v>2</v>
       </c>
       <c r="D81" s="5">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E81" s="6">
-        <v>4</v>
-      </c>
-      <c r="F81" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2954,12 +2978,12 @@
         <v>3</v>
       </c>
       <c r="D82" s="5">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="E82" s="6">
-        <v>6</v>
-      </c>
-      <c r="F82" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2975,12 +2999,12 @@
         <v>4</v>
       </c>
       <c r="D83" s="5">
-        <v>40</v>
+        <v>540</v>
       </c>
       <c r="E83" s="6">
-        <v>8</v>
-      </c>
-      <c r="F83" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F83" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2995,11 +3019,13 @@
       <c r="C84" s="4">
         <v>5</v>
       </c>
-      <c r="D84" s="4"/>
+      <c r="D84" s="5">
+        <v>999999</v>
+      </c>
       <c r="E84" s="6">
-        <v>10</v>
-      </c>
-      <c r="F84" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F84" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3011,16 +3037,16 @@
       <c r="B85" s="1">
         <v>102017</v>
       </c>
-      <c r="C85" s="8">
+      <c r="C85" s="7">
         <v>1</v>
       </c>
-      <c r="D85" s="9">
-        <v>15</v>
-      </c>
-      <c r="E85" s="10">
-        <v>2</v>
-      </c>
-      <c r="F85" s="7" t="s">
+      <c r="D85" s="5">
+        <v>20</v>
+      </c>
+      <c r="E85" s="6">
+        <v>12</v>
+      </c>
+      <c r="F85" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3032,16 +3058,16 @@
       <c r="B86" s="1">
         <v>102017</v>
       </c>
-      <c r="C86" s="8">
+      <c r="C86" s="7">
         <v>2</v>
       </c>
-      <c r="D86" s="9">
-        <v>25</v>
-      </c>
-      <c r="E86" s="10">
-        <v>4</v>
-      </c>
-      <c r="F86" s="7" t="s">
+      <c r="D86" s="5">
+        <v>60</v>
+      </c>
+      <c r="E86" s="6">
+        <v>24</v>
+      </c>
+      <c r="F86" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3053,16 +3079,16 @@
       <c r="B87" s="1">
         <v>102017</v>
       </c>
-      <c r="C87" s="8">
+      <c r="C87" s="7">
         <v>3</v>
       </c>
-      <c r="D87" s="9">
-        <v>35</v>
-      </c>
-      <c r="E87" s="10">
-        <v>6</v>
-      </c>
-      <c r="F87" s="7" t="s">
+      <c r="D87" s="5">
+        <v>180</v>
+      </c>
+      <c r="E87" s="6">
+        <v>36</v>
+      </c>
+      <c r="F87" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3074,16 +3100,16 @@
       <c r="B88" s="1">
         <v>102017</v>
       </c>
-      <c r="C88" s="8">
+      <c r="C88" s="7">
         <v>4</v>
       </c>
-      <c r="D88" s="9">
-        <v>45</v>
-      </c>
-      <c r="E88" s="10">
-        <v>8</v>
-      </c>
-      <c r="F88" s="7" t="s">
+      <c r="D88" s="5">
+        <v>540</v>
+      </c>
+      <c r="E88" s="6">
+        <v>48</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3095,14 +3121,16 @@
       <c r="B89" s="1">
         <v>102017</v>
       </c>
-      <c r="C89" s="8">
+      <c r="C89" s="7">
         <v>5</v>
       </c>
-      <c r="D89" s="8"/>
-      <c r="E89" s="10">
-        <v>10</v>
-      </c>
-      <c r="F89" s="7" t="s">
+      <c r="D89" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E89" s="6">
+        <v>60</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3111,19 +3139,19 @@
         <f t="shared" si="2"/>
         <v>10301801</v>
       </c>
-      <c r="B90" s="8">
+      <c r="B90" s="7">
         <v>103018</v>
       </c>
-      <c r="C90" s="8">
+      <c r="C90" s="7">
         <v>1</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="5">
         <v>20</v>
       </c>
-      <c r="E90" s="10">
-        <v>2</v>
-      </c>
-      <c r="F90" s="7" t="s">
+      <c r="E90" s="6">
+        <v>12</v>
+      </c>
+      <c r="F90" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3132,19 +3160,19 @@
         <f t="shared" si="2"/>
         <v>10301802</v>
       </c>
-      <c r="B91" s="8">
+      <c r="B91" s="7">
         <v>103018</v>
       </c>
-      <c r="C91" s="8">
+      <c r="C91" s="7">
         <v>2</v>
       </c>
-      <c r="D91" s="9">
-        <v>30</v>
-      </c>
-      <c r="E91" s="10">
-        <v>4</v>
-      </c>
-      <c r="F91" s="7" t="s">
+      <c r="D91" s="5">
+        <v>60</v>
+      </c>
+      <c r="E91" s="6">
+        <v>24</v>
+      </c>
+      <c r="F91" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3153,19 +3181,19 @@
         <f t="shared" si="2"/>
         <v>10301803</v>
       </c>
-      <c r="B92" s="8">
+      <c r="B92" s="7">
         <v>103018</v>
       </c>
-      <c r="C92" s="8">
+      <c r="C92" s="7">
         <v>3</v>
       </c>
-      <c r="D92" s="9">
-        <v>40</v>
-      </c>
-      <c r="E92" s="10">
-        <v>6</v>
-      </c>
-      <c r="F92" s="7" t="s">
+      <c r="D92" s="5">
+        <v>180</v>
+      </c>
+      <c r="E92" s="6">
+        <v>36</v>
+      </c>
+      <c r="F92" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3174,19 +3202,19 @@
         <f t="shared" si="2"/>
         <v>10301804</v>
       </c>
-      <c r="B93" s="8">
+      <c r="B93" s="7">
         <v>103018</v>
       </c>
-      <c r="C93" s="8">
+      <c r="C93" s="7">
         <v>4</v>
       </c>
-      <c r="D93" s="9">
-        <v>50</v>
-      </c>
-      <c r="E93" s="10">
-        <v>8</v>
-      </c>
-      <c r="F93" s="7" t="s">
+      <c r="D93" s="5">
+        <v>540</v>
+      </c>
+      <c r="E93" s="6">
+        <v>48</v>
+      </c>
+      <c r="F93" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3195,17 +3223,19 @@
         <f t="shared" si="2"/>
         <v>10301805</v>
       </c>
-      <c r="B94" s="8">
+      <c r="B94" s="7">
         <v>103018</v>
       </c>
-      <c r="C94" s="8">
+      <c r="C94" s="7">
         <v>5</v>
       </c>
-      <c r="D94" s="8"/>
-      <c r="E94" s="10">
-        <v>10</v>
-      </c>
-      <c r="F94" s="7" t="s">
+      <c r="D94" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E94" s="6">
+        <v>60</v>
+      </c>
+      <c r="F94" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3214,19 +3244,19 @@
         <f t="shared" si="2"/>
         <v>10401901</v>
       </c>
-      <c r="B95" s="8">
+      <c r="B95" s="7">
         <v>104019</v>
       </c>
-      <c r="C95" s="8">
+      <c r="C95" s="7">
         <v>1</v>
       </c>
-      <c r="D95" s="9">
-        <v>25</v>
-      </c>
-      <c r="E95" s="10">
-        <v>2</v>
-      </c>
-      <c r="F95" s="7" t="s">
+      <c r="D95" s="5">
+        <v>20</v>
+      </c>
+      <c r="E95" s="6">
+        <v>12</v>
+      </c>
+      <c r="F95" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3235,19 +3265,19 @@
         <f t="shared" si="2"/>
         <v>10401902</v>
       </c>
-      <c r="B96" s="8">
+      <c r="B96" s="7">
         <v>104019</v>
       </c>
-      <c r="C96" s="8">
+      <c r="C96" s="7">
         <v>2</v>
       </c>
-      <c r="D96" s="9">
-        <v>35</v>
-      </c>
-      <c r="E96" s="10">
-        <v>4</v>
-      </c>
-      <c r="F96" s="7" t="s">
+      <c r="D96" s="5">
+        <v>60</v>
+      </c>
+      <c r="E96" s="6">
+        <v>24</v>
+      </c>
+      <c r="F96" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3256,19 +3286,19 @@
         <f t="shared" si="2"/>
         <v>10401903</v>
       </c>
-      <c r="B97" s="8">
+      <c r="B97" s="7">
         <v>104019</v>
       </c>
-      <c r="C97" s="8">
+      <c r="C97" s="7">
         <v>3</v>
       </c>
-      <c r="D97" s="9">
-        <v>45</v>
-      </c>
-      <c r="E97" s="10">
-        <v>6</v>
-      </c>
-      <c r="F97" s="7" t="s">
+      <c r="D97" s="5">
+        <v>180</v>
+      </c>
+      <c r="E97" s="6">
+        <v>36</v>
+      </c>
+      <c r="F97" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3277,19 +3307,19 @@
         <f t="shared" si="2"/>
         <v>10401904</v>
       </c>
-      <c r="B98" s="8">
+      <c r="B98" s="7">
         <v>104019</v>
       </c>
-      <c r="C98" s="8">
+      <c r="C98" s="7">
         <v>4</v>
       </c>
-      <c r="D98" s="9">
-        <v>55</v>
-      </c>
-      <c r="E98" s="10">
-        <v>8</v>
-      </c>
-      <c r="F98" s="7" t="s">
+      <c r="D98" s="5">
+        <v>540</v>
+      </c>
+      <c r="E98" s="6">
+        <v>48</v>
+      </c>
+      <c r="F98" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3298,17 +3328,19 @@
         <f t="shared" si="2"/>
         <v>10401905</v>
       </c>
-      <c r="B99" s="8">
+      <c r="B99" s="7">
         <v>104019</v>
       </c>
-      <c r="C99" s="8">
+      <c r="C99" s="7">
         <v>5</v>
       </c>
-      <c r="D99" s="8"/>
-      <c r="E99" s="10">
-        <v>10</v>
-      </c>
-      <c r="F99" s="7" t="s">
+      <c r="D99" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E99" s="6">
+        <v>60</v>
+      </c>
+      <c r="F99" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3317,19 +3349,19 @@
         <f t="shared" si="2"/>
         <v>10502001</v>
       </c>
-      <c r="B100" s="8">
+      <c r="B100" s="7">
         <v>105020</v>
       </c>
-      <c r="C100" s="8">
+      <c r="C100" s="7">
         <v>1</v>
       </c>
-      <c r="D100" s="9">
-        <v>30</v>
-      </c>
-      <c r="E100" s="10">
-        <v>2</v>
-      </c>
-      <c r="F100" s="7" t="s">
+      <c r="D100" s="5">
+        <v>20</v>
+      </c>
+      <c r="E100" s="6">
+        <v>12</v>
+      </c>
+      <c r="F100" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3338,19 +3370,19 @@
         <f t="shared" si="2"/>
         <v>10502002</v>
       </c>
-      <c r="B101" s="8">
+      <c r="B101" s="7">
         <v>105020</v>
       </c>
-      <c r="C101" s="8">
+      <c r="C101" s="7">
         <v>2</v>
       </c>
-      <c r="D101" s="9">
-        <v>40</v>
-      </c>
-      <c r="E101" s="10">
-        <v>4</v>
-      </c>
-      <c r="F101" s="7" t="s">
+      <c r="D101" s="5">
+        <v>60</v>
+      </c>
+      <c r="E101" s="6">
+        <v>24</v>
+      </c>
+      <c r="F101" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3359,19 +3391,19 @@
         <f t="shared" si="2"/>
         <v>10502003</v>
       </c>
-      <c r="B102" s="8">
+      <c r="B102" s="7">
         <v>105020</v>
       </c>
-      <c r="C102" s="8">
+      <c r="C102" s="7">
         <v>3</v>
       </c>
-      <c r="D102" s="9">
-        <v>50</v>
-      </c>
-      <c r="E102" s="10">
-        <v>6</v>
-      </c>
-      <c r="F102" s="7" t="s">
+      <c r="D102" s="5">
+        <v>180</v>
+      </c>
+      <c r="E102" s="6">
+        <v>36</v>
+      </c>
+      <c r="F102" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3380,19 +3412,19 @@
         <f t="shared" si="2"/>
         <v>10502004</v>
       </c>
-      <c r="B103" s="8">
+      <c r="B103" s="7">
         <v>105020</v>
       </c>
-      <c r="C103" s="8">
+      <c r="C103" s="7">
         <v>4</v>
       </c>
-      <c r="D103" s="9">
-        <v>60</v>
-      </c>
-      <c r="E103" s="10">
-        <v>8</v>
-      </c>
-      <c r="F103" s="7" t="s">
+      <c r="D103" s="5">
+        <v>540</v>
+      </c>
+      <c r="E103" s="6">
+        <v>48</v>
+      </c>
+      <c r="F103" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3401,17 +3433,19 @@
         <f t="shared" si="2"/>
         <v>10502005</v>
       </c>
-      <c r="B104" s="8">
+      <c r="B104" s="7">
         <v>105020</v>
       </c>
-      <c r="C104" s="8">
+      <c r="C104" s="7">
         <v>5</v>
       </c>
-      <c r="D104" s="8"/>
-      <c r="E104" s="10">
-        <v>10</v>
-      </c>
-      <c r="F104" s="7" t="s">
+      <c r="D104" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E104" s="6">
+        <v>60</v>
+      </c>
+      <c r="F104" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3420,19 +3454,19 @@
         <f t="shared" si="2"/>
         <v>20102101</v>
       </c>
-      <c r="B105" s="8">
+      <c r="B105" s="7">
         <v>201021</v>
       </c>
-      <c r="C105" s="8">
+      <c r="C105" s="7">
         <v>1</v>
       </c>
       <c r="D105" s="5">
-        <v>10</v>
-      </c>
-      <c r="E105" s="10">
-        <v>2</v>
-      </c>
-      <c r="F105" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E105" s="6">
+        <v>12</v>
+      </c>
+      <c r="F105" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3441,19 +3475,19 @@
         <f t="shared" si="2"/>
         <v>20102102</v>
       </c>
-      <c r="B106" s="8">
+      <c r="B106" s="7">
         <v>201021</v>
       </c>
-      <c r="C106" s="8">
+      <c r="C106" s="7">
         <v>2</v>
       </c>
       <c r="D106" s="5">
-        <v>20</v>
-      </c>
-      <c r="E106" s="10">
-        <v>4</v>
-      </c>
-      <c r="F106" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E106" s="6">
+        <v>24</v>
+      </c>
+      <c r="F106" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3462,19 +3496,19 @@
         <f t="shared" si="2"/>
         <v>20102103</v>
       </c>
-      <c r="B107" s="8">
+      <c r="B107" s="7">
         <v>201021</v>
       </c>
-      <c r="C107" s="8">
+      <c r="C107" s="7">
         <v>3</v>
       </c>
       <c r="D107" s="5">
-        <v>30</v>
-      </c>
-      <c r="E107" s="10">
-        <v>6</v>
-      </c>
-      <c r="F107" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E107" s="6">
+        <v>36</v>
+      </c>
+      <c r="F107" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3483,19 +3517,19 @@
         <f t="shared" si="2"/>
         <v>20102104</v>
       </c>
-      <c r="B108" s="8">
+      <c r="B108" s="7">
         <v>201021</v>
       </c>
-      <c r="C108" s="8">
+      <c r="C108" s="7">
         <v>4</v>
       </c>
       <c r="D108" s="5">
-        <v>40</v>
-      </c>
-      <c r="E108" s="10">
-        <v>8</v>
-      </c>
-      <c r="F108" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="E108" s="6">
+        <v>48</v>
+      </c>
+      <c r="F108" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3504,17 +3538,19 @@
         <f t="shared" si="2"/>
         <v>20102105</v>
       </c>
-      <c r="B109" s="8">
+      <c r="B109" s="7">
         <v>201021</v>
       </c>
-      <c r="C109" s="8">
+      <c r="C109" s="7">
         <v>5</v>
       </c>
-      <c r="D109" s="4"/>
-      <c r="E109" s="10">
-        <v>10</v>
-      </c>
-      <c r="F109" s="11" t="s">
+      <c r="D109" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E109" s="6">
+        <v>60</v>
+      </c>
+      <c r="F109" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3523,19 +3559,19 @@
         <f t="shared" si="2"/>
         <v>20202201</v>
       </c>
-      <c r="B110" s="8">
+      <c r="B110" s="7">
         <v>202022</v>
       </c>
-      <c r="C110" s="8">
+      <c r="C110" s="7">
         <v>1</v>
       </c>
-      <c r="D110" s="9">
-        <v>15</v>
-      </c>
-      <c r="E110" s="10">
-        <v>2</v>
-      </c>
-      <c r="F110" s="11" t="s">
+      <c r="D110" s="5">
+        <v>20</v>
+      </c>
+      <c r="E110" s="6">
+        <v>12</v>
+      </c>
+      <c r="F110" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3544,19 +3580,19 @@
         <f t="shared" si="2"/>
         <v>20202202</v>
       </c>
-      <c r="B111" s="8">
+      <c r="B111" s="7">
         <v>202022</v>
       </c>
-      <c r="C111" s="8">
+      <c r="C111" s="7">
         <v>2</v>
       </c>
-      <c r="D111" s="9">
-        <v>25</v>
-      </c>
-      <c r="E111" s="10">
-        <v>4</v>
-      </c>
-      <c r="F111" s="11" t="s">
+      <c r="D111" s="5">
+        <v>60</v>
+      </c>
+      <c r="E111" s="6">
+        <v>24</v>
+      </c>
+      <c r="F111" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3565,19 +3601,19 @@
         <f t="shared" ref="A112:A154" si="3">B112*100+C112</f>
         <v>20202203</v>
       </c>
-      <c r="B112" s="8">
+      <c r="B112" s="7">
         <v>202022</v>
       </c>
-      <c r="C112" s="8">
+      <c r="C112" s="7">
         <v>3</v>
       </c>
-      <c r="D112" s="9">
-        <v>35</v>
-      </c>
-      <c r="E112" s="10">
-        <v>6</v>
-      </c>
-      <c r="F112" s="11" t="s">
+      <c r="D112" s="5">
+        <v>180</v>
+      </c>
+      <c r="E112" s="6">
+        <v>36</v>
+      </c>
+      <c r="F112" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3586,19 +3622,19 @@
         <f t="shared" si="3"/>
         <v>20202204</v>
       </c>
-      <c r="B113" s="8">
+      <c r="B113" s="7">
         <v>202022</v>
       </c>
-      <c r="C113" s="8">
+      <c r="C113" s="7">
         <v>4</v>
       </c>
-      <c r="D113" s="9">
-        <v>45</v>
-      </c>
-      <c r="E113" s="10">
-        <v>8</v>
-      </c>
-      <c r="F113" s="11" t="s">
+      <c r="D113" s="5">
+        <v>540</v>
+      </c>
+      <c r="E113" s="6">
+        <v>48</v>
+      </c>
+      <c r="F113" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3607,17 +3643,19 @@
         <f t="shared" si="3"/>
         <v>20202205</v>
       </c>
-      <c r="B114" s="8">
+      <c r="B114" s="7">
         <v>202022</v>
       </c>
-      <c r="C114" s="8">
+      <c r="C114" s="7">
         <v>5</v>
       </c>
-      <c r="D114" s="8"/>
-      <c r="E114" s="10">
-        <v>10</v>
-      </c>
-      <c r="F114" s="11" t="s">
+      <c r="D114" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E114" s="6">
+        <v>60</v>
+      </c>
+      <c r="F114" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3626,19 +3664,19 @@
         <f t="shared" si="3"/>
         <v>20302301</v>
       </c>
-      <c r="B115" s="8">
+      <c r="B115" s="7">
         <v>203023</v>
       </c>
-      <c r="C115" s="8">
+      <c r="C115" s="7">
         <v>1</v>
       </c>
-      <c r="D115" s="9">
+      <c r="D115" s="5">
         <v>20</v>
       </c>
-      <c r="E115" s="10">
-        <v>2</v>
-      </c>
-      <c r="F115" s="11" t="s">
+      <c r="E115" s="6">
+        <v>12</v>
+      </c>
+      <c r="F115" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3647,19 +3685,19 @@
         <f t="shared" si="3"/>
         <v>20302302</v>
       </c>
-      <c r="B116" s="8">
+      <c r="B116" s="7">
         <v>203023</v>
       </c>
-      <c r="C116" s="8">
+      <c r="C116" s="7">
         <v>2</v>
       </c>
-      <c r="D116" s="9">
-        <v>30</v>
-      </c>
-      <c r="E116" s="10">
-        <v>4</v>
-      </c>
-      <c r="F116" s="11" t="s">
+      <c r="D116" s="5">
+        <v>60</v>
+      </c>
+      <c r="E116" s="6">
+        <v>24</v>
+      </c>
+      <c r="F116" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3668,19 +3706,19 @@
         <f t="shared" si="3"/>
         <v>20302303</v>
       </c>
-      <c r="B117" s="8">
+      <c r="B117" s="7">
         <v>203023</v>
       </c>
-      <c r="C117" s="8">
+      <c r="C117" s="7">
         <v>3</v>
       </c>
-      <c r="D117" s="9">
-        <v>40</v>
-      </c>
-      <c r="E117" s="10">
-        <v>6</v>
-      </c>
-      <c r="F117" s="11" t="s">
+      <c r="D117" s="5">
+        <v>180</v>
+      </c>
+      <c r="E117" s="6">
+        <v>36</v>
+      </c>
+      <c r="F117" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3689,19 +3727,19 @@
         <f t="shared" si="3"/>
         <v>20302304</v>
       </c>
-      <c r="B118" s="8">
+      <c r="B118" s="7">
         <v>203023</v>
       </c>
-      <c r="C118" s="8">
+      <c r="C118" s="7">
         <v>4</v>
       </c>
-      <c r="D118" s="9">
-        <v>50</v>
-      </c>
-      <c r="E118" s="10">
-        <v>8</v>
-      </c>
-      <c r="F118" s="11" t="s">
+      <c r="D118" s="5">
+        <v>540</v>
+      </c>
+      <c r="E118" s="6">
+        <v>48</v>
+      </c>
+      <c r="F118" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3710,17 +3748,19 @@
         <f t="shared" si="3"/>
         <v>20302305</v>
       </c>
-      <c r="B119" s="8">
+      <c r="B119" s="7">
         <v>203023</v>
       </c>
-      <c r="C119" s="8">
+      <c r="C119" s="7">
         <v>5</v>
       </c>
-      <c r="D119" s="8"/>
-      <c r="E119" s="10">
-        <v>10</v>
-      </c>
-      <c r="F119" s="11" t="s">
+      <c r="D119" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E119" s="6">
+        <v>60</v>
+      </c>
+      <c r="F119" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3729,19 +3769,19 @@
         <f t="shared" si="3"/>
         <v>20402401</v>
       </c>
-      <c r="B120" s="8">
+      <c r="B120" s="7">
         <v>204024</v>
       </c>
-      <c r="C120" s="8">
+      <c r="C120" s="7">
         <v>1</v>
       </c>
-      <c r="D120" s="9">
-        <v>25</v>
-      </c>
-      <c r="E120" s="10">
-        <v>2</v>
-      </c>
-      <c r="F120" s="11" t="s">
+      <c r="D120" s="5">
+        <v>20</v>
+      </c>
+      <c r="E120" s="6">
+        <v>12</v>
+      </c>
+      <c r="F120" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3750,19 +3790,19 @@
         <f t="shared" si="3"/>
         <v>20402402</v>
       </c>
-      <c r="B121" s="8">
+      <c r="B121" s="7">
         <v>204024</v>
       </c>
-      <c r="C121" s="8">
+      <c r="C121" s="7">
         <v>2</v>
       </c>
-      <c r="D121" s="9">
-        <v>35</v>
-      </c>
-      <c r="E121" s="10">
-        <v>4</v>
-      </c>
-      <c r="F121" s="11" t="s">
+      <c r="D121" s="5">
+        <v>60</v>
+      </c>
+      <c r="E121" s="6">
+        <v>24</v>
+      </c>
+      <c r="F121" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3771,19 +3811,19 @@
         <f t="shared" si="3"/>
         <v>20402403</v>
       </c>
-      <c r="B122" s="8">
+      <c r="B122" s="7">
         <v>204024</v>
       </c>
-      <c r="C122" s="8">
+      <c r="C122" s="7">
         <v>3</v>
       </c>
-      <c r="D122" s="9">
-        <v>45</v>
-      </c>
-      <c r="E122" s="10">
-        <v>6</v>
-      </c>
-      <c r="F122" s="11" t="s">
+      <c r="D122" s="5">
+        <v>180</v>
+      </c>
+      <c r="E122" s="6">
+        <v>36</v>
+      </c>
+      <c r="F122" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3792,19 +3832,19 @@
         <f t="shared" si="3"/>
         <v>20402404</v>
       </c>
-      <c r="B123" s="8">
+      <c r="B123" s="7">
         <v>204024</v>
       </c>
-      <c r="C123" s="8">
+      <c r="C123" s="7">
         <v>4</v>
       </c>
-      <c r="D123" s="9">
-        <v>55</v>
-      </c>
-      <c r="E123" s="10">
-        <v>8</v>
-      </c>
-      <c r="F123" s="11" t="s">
+      <c r="D123" s="5">
+        <v>540</v>
+      </c>
+      <c r="E123" s="6">
+        <v>48</v>
+      </c>
+      <c r="F123" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3813,17 +3853,19 @@
         <f t="shared" si="3"/>
         <v>20402405</v>
       </c>
-      <c r="B124" s="8">
+      <c r="B124" s="7">
         <v>204024</v>
       </c>
-      <c r="C124" s="8">
+      <c r="C124" s="7">
         <v>5</v>
       </c>
-      <c r="D124" s="8"/>
-      <c r="E124" s="10">
-        <v>10</v>
-      </c>
-      <c r="F124" s="11" t="s">
+      <c r="D124" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E124" s="6">
+        <v>60</v>
+      </c>
+      <c r="F124" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3832,19 +3874,19 @@
         <f t="shared" si="3"/>
         <v>20502501</v>
       </c>
-      <c r="B125" s="8">
+      <c r="B125" s="7">
         <v>205025</v>
       </c>
-      <c r="C125" s="8">
+      <c r="C125" s="7">
         <v>1</v>
       </c>
-      <c r="D125" s="9">
-        <v>30</v>
-      </c>
-      <c r="E125" s="10">
-        <v>2</v>
-      </c>
-      <c r="F125" s="11" t="s">
+      <c r="D125" s="5">
+        <v>20</v>
+      </c>
+      <c r="E125" s="6">
+        <v>12</v>
+      </c>
+      <c r="F125" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3853,19 +3895,19 @@
         <f t="shared" si="3"/>
         <v>20502502</v>
       </c>
-      <c r="B126" s="8">
+      <c r="B126" s="7">
         <v>205025</v>
       </c>
-      <c r="C126" s="8">
+      <c r="C126" s="7">
         <v>2</v>
       </c>
-      <c r="D126" s="9">
-        <v>40</v>
-      </c>
-      <c r="E126" s="10">
-        <v>4</v>
-      </c>
-      <c r="F126" s="11" t="s">
+      <c r="D126" s="5">
+        <v>60</v>
+      </c>
+      <c r="E126" s="6">
+        <v>24</v>
+      </c>
+      <c r="F126" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3874,19 +3916,19 @@
         <f t="shared" si="3"/>
         <v>20502503</v>
       </c>
-      <c r="B127" s="8">
+      <c r="B127" s="7">
         <v>205025</v>
       </c>
-      <c r="C127" s="8">
+      <c r="C127" s="7">
         <v>3</v>
       </c>
-      <c r="D127" s="9">
-        <v>50</v>
-      </c>
-      <c r="E127" s="10">
-        <v>6</v>
-      </c>
-      <c r="F127" s="11" t="s">
+      <c r="D127" s="5">
+        <v>180</v>
+      </c>
+      <c r="E127" s="6">
+        <v>36</v>
+      </c>
+      <c r="F127" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3895,19 +3937,19 @@
         <f t="shared" si="3"/>
         <v>20502504</v>
       </c>
-      <c r="B128" s="8">
+      <c r="B128" s="7">
         <v>205025</v>
       </c>
-      <c r="C128" s="8">
+      <c r="C128" s="7">
         <v>4</v>
       </c>
-      <c r="D128" s="9">
-        <v>60</v>
-      </c>
-      <c r="E128" s="10">
-        <v>8</v>
-      </c>
-      <c r="F128" s="11" t="s">
+      <c r="D128" s="5">
+        <v>540</v>
+      </c>
+      <c r="E128" s="6">
+        <v>48</v>
+      </c>
+      <c r="F128" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3916,17 +3958,19 @@
         <f t="shared" si="3"/>
         <v>20502505</v>
       </c>
-      <c r="B129" s="8">
+      <c r="B129" s="7">
         <v>205025</v>
       </c>
-      <c r="C129" s="8">
+      <c r="C129" s="7">
         <v>5</v>
       </c>
-      <c r="D129" s="8"/>
-      <c r="E129" s="10">
-        <v>10</v>
-      </c>
-      <c r="F129" s="11" t="s">
+      <c r="D129" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E129" s="6">
+        <v>60</v>
+      </c>
+      <c r="F129" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3935,19 +3979,19 @@
         <f t="shared" si="3"/>
         <v>30102601</v>
       </c>
-      <c r="B130" s="8">
+      <c r="B130" s="7">
         <v>301026</v>
       </c>
-      <c r="C130" s="8">
+      <c r="C130" s="7">
         <v>1</v>
       </c>
       <c r="D130" s="5">
-        <v>10</v>
-      </c>
-      <c r="E130" s="10">
-        <v>2</v>
-      </c>
-      <c r="F130" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E130" s="6">
+        <v>12</v>
+      </c>
+      <c r="F130" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3956,19 +4000,19 @@
         <f t="shared" si="3"/>
         <v>30102602</v>
       </c>
-      <c r="B131" s="8">
+      <c r="B131" s="7">
         <v>301026</v>
       </c>
-      <c r="C131" s="8">
+      <c r="C131" s="7">
         <v>2</v>
       </c>
       <c r="D131" s="5">
-        <v>20</v>
-      </c>
-      <c r="E131" s="10">
-        <v>4</v>
-      </c>
-      <c r="F131" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E131" s="6">
+        <v>24</v>
+      </c>
+      <c r="F131" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3977,19 +4021,19 @@
         <f t="shared" si="3"/>
         <v>30102603</v>
       </c>
-      <c r="B132" s="8">
+      <c r="B132" s="7">
         <v>301026</v>
       </c>
-      <c r="C132" s="8">
+      <c r="C132" s="7">
         <v>3</v>
       </c>
       <c r="D132" s="5">
-        <v>30</v>
-      </c>
-      <c r="E132" s="10">
-        <v>6</v>
-      </c>
-      <c r="F132" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E132" s="6">
+        <v>36</v>
+      </c>
+      <c r="F132" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3998,19 +4042,19 @@
         <f t="shared" si="3"/>
         <v>30102604</v>
       </c>
-      <c r="B133" s="8">
+      <c r="B133" s="7">
         <v>301026</v>
       </c>
-      <c r="C133" s="8">
+      <c r="C133" s="7">
         <v>4</v>
       </c>
       <c r="D133" s="5">
-        <v>40</v>
-      </c>
-      <c r="E133" s="10">
-        <v>8</v>
-      </c>
-      <c r="F133" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="E133" s="6">
+        <v>48</v>
+      </c>
+      <c r="F133" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4019,17 +4063,19 @@
         <f t="shared" si="3"/>
         <v>30102605</v>
       </c>
-      <c r="B134" s="8">
+      <c r="B134" s="7">
         <v>301026</v>
       </c>
-      <c r="C134" s="8">
+      <c r="C134" s="7">
         <v>5</v>
       </c>
-      <c r="D134" s="4"/>
-      <c r="E134" s="10">
-        <v>10</v>
-      </c>
-      <c r="F134" s="11" t="s">
+      <c r="D134" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E134" s="6">
+        <v>60</v>
+      </c>
+      <c r="F134" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4038,19 +4084,19 @@
         <f t="shared" si="3"/>
         <v>30202701</v>
       </c>
-      <c r="B135" s="8">
+      <c r="B135" s="7">
         <v>302027</v>
       </c>
-      <c r="C135" s="8">
+      <c r="C135" s="7">
         <v>1</v>
       </c>
-      <c r="D135" s="9">
-        <v>15</v>
-      </c>
-      <c r="E135" s="10">
-        <v>2</v>
-      </c>
-      <c r="F135" s="11" t="s">
+      <c r="D135" s="5">
+        <v>20</v>
+      </c>
+      <c r="E135" s="6">
+        <v>12</v>
+      </c>
+      <c r="F135" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4059,19 +4105,19 @@
         <f t="shared" si="3"/>
         <v>30202702</v>
       </c>
-      <c r="B136" s="8">
+      <c r="B136" s="7">
         <v>302027</v>
       </c>
-      <c r="C136" s="8">
+      <c r="C136" s="7">
         <v>2</v>
       </c>
-      <c r="D136" s="9">
-        <v>25</v>
-      </c>
-      <c r="E136" s="10">
-        <v>4</v>
-      </c>
-      <c r="F136" s="11" t="s">
+      <c r="D136" s="5">
+        <v>60</v>
+      </c>
+      <c r="E136" s="6">
+        <v>24</v>
+      </c>
+      <c r="F136" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4080,19 +4126,19 @@
         <f t="shared" si="3"/>
         <v>30202703</v>
       </c>
-      <c r="B137" s="8">
+      <c r="B137" s="7">
         <v>302027</v>
       </c>
-      <c r="C137" s="8">
+      <c r="C137" s="7">
         <v>3</v>
       </c>
-      <c r="D137" s="9">
-        <v>35</v>
-      </c>
-      <c r="E137" s="10">
-        <v>6</v>
-      </c>
-      <c r="F137" s="11" t="s">
+      <c r="D137" s="5">
+        <v>180</v>
+      </c>
+      <c r="E137" s="6">
+        <v>36</v>
+      </c>
+      <c r="F137" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4101,19 +4147,19 @@
         <f t="shared" si="3"/>
         <v>30202704</v>
       </c>
-      <c r="B138" s="8">
+      <c r="B138" s="7">
         <v>302027</v>
       </c>
-      <c r="C138" s="8">
+      <c r="C138" s="7">
         <v>4</v>
       </c>
-      <c r="D138" s="9">
-        <v>45</v>
-      </c>
-      <c r="E138" s="10">
-        <v>8</v>
-      </c>
-      <c r="F138" s="11" t="s">
+      <c r="D138" s="5">
+        <v>540</v>
+      </c>
+      <c r="E138" s="6">
+        <v>48</v>
+      </c>
+      <c r="F138" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4122,17 +4168,19 @@
         <f t="shared" si="3"/>
         <v>30202705</v>
       </c>
-      <c r="B139" s="8">
+      <c r="B139" s="7">
         <v>302027</v>
       </c>
-      <c r="C139" s="8">
+      <c r="C139" s="7">
         <v>5</v>
       </c>
-      <c r="D139" s="8"/>
-      <c r="E139" s="10">
-        <v>10</v>
-      </c>
-      <c r="F139" s="11" t="s">
+      <c r="D139" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E139" s="6">
+        <v>60</v>
+      </c>
+      <c r="F139" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4141,19 +4189,19 @@
         <f t="shared" si="3"/>
         <v>30302801</v>
       </c>
-      <c r="B140" s="10">
+      <c r="B140" s="9">
         <v>303028</v>
       </c>
-      <c r="C140" s="8">
+      <c r="C140" s="7">
         <v>1</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D140" s="5">
         <v>20</v>
       </c>
-      <c r="E140" s="10">
-        <v>2</v>
-      </c>
-      <c r="F140" s="11" t="s">
+      <c r="E140" s="6">
+        <v>12</v>
+      </c>
+      <c r="F140" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4162,19 +4210,19 @@
         <f t="shared" si="3"/>
         <v>30302802</v>
       </c>
-      <c r="B141" s="10">
+      <c r="B141" s="9">
         <v>303028</v>
       </c>
-      <c r="C141" s="8">
+      <c r="C141" s="7">
         <v>2</v>
       </c>
-      <c r="D141" s="9">
-        <v>30</v>
-      </c>
-      <c r="E141" s="10">
-        <v>4</v>
-      </c>
-      <c r="F141" s="11" t="s">
+      <c r="D141" s="5">
+        <v>60</v>
+      </c>
+      <c r="E141" s="6">
+        <v>24</v>
+      </c>
+      <c r="F141" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4183,19 +4231,19 @@
         <f t="shared" si="3"/>
         <v>30302803</v>
       </c>
-      <c r="B142" s="10">
+      <c r="B142" s="9">
         <v>303028</v>
       </c>
-      <c r="C142" s="8">
+      <c r="C142" s="7">
         <v>3</v>
       </c>
-      <c r="D142" s="9">
-        <v>40</v>
-      </c>
-      <c r="E142" s="10">
-        <v>6</v>
-      </c>
-      <c r="F142" s="11" t="s">
+      <c r="D142" s="5">
+        <v>180</v>
+      </c>
+      <c r="E142" s="6">
+        <v>36</v>
+      </c>
+      <c r="F142" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4204,19 +4252,19 @@
         <f t="shared" si="3"/>
         <v>30302804</v>
       </c>
-      <c r="B143" s="10">
+      <c r="B143" s="9">
         <v>303028</v>
       </c>
-      <c r="C143" s="8">
+      <c r="C143" s="7">
         <v>4</v>
       </c>
-      <c r="D143" s="9">
-        <v>50</v>
-      </c>
-      <c r="E143" s="10">
-        <v>8</v>
-      </c>
-      <c r="F143" s="11" t="s">
+      <c r="D143" s="5">
+        <v>540</v>
+      </c>
+      <c r="E143" s="6">
+        <v>48</v>
+      </c>
+      <c r="F143" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4225,17 +4273,19 @@
         <f t="shared" si="3"/>
         <v>30302805</v>
       </c>
-      <c r="B144" s="10">
+      <c r="B144" s="9">
         <v>303028</v>
       </c>
-      <c r="C144" s="8">
+      <c r="C144" s="7">
         <v>5</v>
       </c>
-      <c r="D144" s="8"/>
-      <c r="E144" s="10">
-        <v>10</v>
-      </c>
-      <c r="F144" s="11" t="s">
+      <c r="D144" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E144" s="6">
+        <v>60</v>
+      </c>
+      <c r="F144" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4244,19 +4294,19 @@
         <f t="shared" si="3"/>
         <v>30402901</v>
       </c>
-      <c r="B145" s="8">
+      <c r="B145" s="7">
         <v>304029</v>
       </c>
-      <c r="C145" s="8">
+      <c r="C145" s="7">
         <v>1</v>
       </c>
-      <c r="D145" s="9">
-        <v>25</v>
-      </c>
-      <c r="E145" s="10">
-        <v>2</v>
-      </c>
-      <c r="F145" s="11" t="s">
+      <c r="D145" s="5">
+        <v>20</v>
+      </c>
+      <c r="E145" s="6">
+        <v>12</v>
+      </c>
+      <c r="F145" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4265,19 +4315,19 @@
         <f t="shared" si="3"/>
         <v>30402902</v>
       </c>
-      <c r="B146" s="8">
+      <c r="B146" s="7">
         <v>304029</v>
       </c>
-      <c r="C146" s="8">
+      <c r="C146" s="7">
         <v>2</v>
       </c>
-      <c r="D146" s="9">
-        <v>35</v>
-      </c>
-      <c r="E146" s="10">
-        <v>4</v>
-      </c>
-      <c r="F146" s="11" t="s">
+      <c r="D146" s="5">
+        <v>60</v>
+      </c>
+      <c r="E146" s="6">
+        <v>24</v>
+      </c>
+      <c r="F146" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4286,19 +4336,19 @@
         <f t="shared" si="3"/>
         <v>30402903</v>
       </c>
-      <c r="B147" s="8">
+      <c r="B147" s="7">
         <v>304029</v>
       </c>
-      <c r="C147" s="8">
+      <c r="C147" s="7">
         <v>3</v>
       </c>
-      <c r="D147" s="9">
-        <v>45</v>
-      </c>
-      <c r="E147" s="10">
-        <v>6</v>
-      </c>
-      <c r="F147" s="11" t="s">
+      <c r="D147" s="5">
+        <v>180</v>
+      </c>
+      <c r="E147" s="6">
+        <v>36</v>
+      </c>
+      <c r="F147" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4307,19 +4357,19 @@
         <f t="shared" si="3"/>
         <v>30402904</v>
       </c>
-      <c r="B148" s="8">
+      <c r="B148" s="7">
         <v>304029</v>
       </c>
-      <c r="C148" s="8">
+      <c r="C148" s="7">
         <v>4</v>
       </c>
-      <c r="D148" s="9">
-        <v>55</v>
-      </c>
-      <c r="E148" s="10">
-        <v>8</v>
-      </c>
-      <c r="F148" s="11" t="s">
+      <c r="D148" s="5">
+        <v>540</v>
+      </c>
+      <c r="E148" s="6">
+        <v>48</v>
+      </c>
+      <c r="F148" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4328,17 +4378,19 @@
         <f t="shared" si="3"/>
         <v>30402905</v>
       </c>
-      <c r="B149" s="8">
+      <c r="B149" s="7">
         <v>304029</v>
       </c>
-      <c r="C149" s="8">
+      <c r="C149" s="7">
         <v>5</v>
       </c>
-      <c r="D149" s="8"/>
-      <c r="E149" s="10">
-        <v>10</v>
-      </c>
-      <c r="F149" s="11" t="s">
+      <c r="D149" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E149" s="6">
+        <v>60</v>
+      </c>
+      <c r="F149" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4347,19 +4399,19 @@
         <f t="shared" si="3"/>
         <v>30503001</v>
       </c>
-      <c r="B150" s="8">
+      <c r="B150" s="7">
         <v>305030</v>
       </c>
-      <c r="C150" s="8">
+      <c r="C150" s="7">
         <v>1</v>
       </c>
-      <c r="D150" s="9">
-        <v>30</v>
-      </c>
-      <c r="E150" s="10">
-        <v>2</v>
-      </c>
-      <c r="F150" s="11" t="s">
+      <c r="D150" s="5">
+        <v>20</v>
+      </c>
+      <c r="E150" s="6">
+        <v>12</v>
+      </c>
+      <c r="F150" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4368,19 +4420,19 @@
         <f t="shared" si="3"/>
         <v>30503002</v>
       </c>
-      <c r="B151" s="8">
+      <c r="B151" s="7">
         <v>305030</v>
       </c>
-      <c r="C151" s="8">
+      <c r="C151" s="7">
         <v>2</v>
       </c>
-      <c r="D151" s="9">
-        <v>40</v>
-      </c>
-      <c r="E151" s="10">
-        <v>4</v>
-      </c>
-      <c r="F151" s="11" t="s">
+      <c r="D151" s="5">
+        <v>60</v>
+      </c>
+      <c r="E151" s="6">
+        <v>24</v>
+      </c>
+      <c r="F151" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4389,19 +4441,19 @@
         <f t="shared" si="3"/>
         <v>30503003</v>
       </c>
-      <c r="B152" s="8">
+      <c r="B152" s="7">
         <v>305030</v>
       </c>
-      <c r="C152" s="8">
+      <c r="C152" s="7">
         <v>3</v>
       </c>
-      <c r="D152" s="9">
-        <v>50</v>
-      </c>
-      <c r="E152" s="10">
-        <v>6</v>
-      </c>
-      <c r="F152" s="11" t="s">
+      <c r="D152" s="5">
+        <v>180</v>
+      </c>
+      <c r="E152" s="6">
+        <v>36</v>
+      </c>
+      <c r="F152" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4410,19 +4462,19 @@
         <f t="shared" si="3"/>
         <v>30503004</v>
       </c>
-      <c r="B153" s="8">
+      <c r="B153" s="7">
         <v>305030</v>
       </c>
-      <c r="C153" s="8">
+      <c r="C153" s="7">
         <v>4</v>
       </c>
-      <c r="D153" s="9">
-        <v>60</v>
-      </c>
-      <c r="E153" s="10">
-        <v>8</v>
-      </c>
-      <c r="F153" s="11" t="s">
+      <c r="D153" s="5">
+        <v>540</v>
+      </c>
+      <c r="E153" s="6">
+        <v>48</v>
+      </c>
+      <c r="F153" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4431,17 +4483,19 @@
         <f t="shared" si="3"/>
         <v>30503005</v>
       </c>
-      <c r="B154" s="8">
+      <c r="B154" s="7">
         <v>305030</v>
       </c>
-      <c r="C154" s="8">
+      <c r="C154" s="7">
         <v>5</v>
       </c>
-      <c r="D154" s="8"/>
-      <c r="E154" s="10">
-        <v>10</v>
-      </c>
-      <c r="F154" s="11" t="s">
+      <c r="D154" s="5">
+        <v>999999</v>
+      </c>
+      <c r="E154" s="6">
+        <v>60</v>
+      </c>
+      <c r="F154" s="8" t="s">
         <v>16</v>
       </c>
     </row>

--- a/hall/resources/sample/EmployeeStar.xlsx
+++ b/hall/resources/sample/EmployeeStar.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="EmployeeStar" sheetId="1" r:id="rId1"/>
@@ -243,7 +248,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,6 +258,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,7 +601,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -614,16 +625,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -632,89 +643,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -730,10 +741,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1361,12 +1375,12 @@
         <v>1</v>
       </c>
       <c r="D5" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E5" s="6">
         <v>12</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1382,12 +1396,12 @@
         <v>2</v>
       </c>
       <c r="D6" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E6" s="6">
         <v>24</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1403,12 +1417,12 @@
         <v>3</v>
       </c>
       <c r="D7" s="5">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E7" s="6">
         <v>36</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1424,12 +1438,12 @@
         <v>4</v>
       </c>
       <c r="D8" s="5">
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="E8" s="6">
         <v>48</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1444,13 +1458,13 @@
       <c r="C9" s="4">
         <v>5</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="7">
         <v>999999</v>
       </c>
       <c r="E9" s="6">
         <v>60</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1462,16 +1476,17 @@
       <c r="B10" s="1">
         <v>102002</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>1</v>
       </c>
-      <c r="D10" s="5">
-        <v>20</v>
+      <c r="D10" s="7">
+        <f t="shared" ref="D10:D13" si="1">D5</f>
+        <v>10</v>
       </c>
       <c r="E10" s="6">
         <v>12</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1483,16 +1498,17 @@
       <c r="B11" s="1">
         <v>102002</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <v>2</v>
       </c>
-      <c r="D11" s="5">
-        <v>60</v>
+      <c r="D11" s="7">
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
       <c r="E11" s="6">
         <v>24</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1504,16 +1520,17 @@
       <c r="B12" s="1">
         <v>102002</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>3</v>
       </c>
-      <c r="D12" s="5">
-        <v>180</v>
+      <c r="D12" s="7">
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
       <c r="E12" s="6">
         <v>36</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1525,16 +1542,17 @@
       <c r="B13" s="1">
         <v>102002</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <v>4</v>
       </c>
-      <c r="D13" s="5">
-        <v>540</v>
+      <c r="D13" s="7">
+        <f t="shared" si="1"/>
+        <v>360</v>
       </c>
       <c r="E13" s="6">
         <v>48</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1546,16 +1564,16 @@
       <c r="B14" s="1">
         <v>102002</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <v>5</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="7">
         <v>999999</v>
       </c>
       <c r="E14" s="6">
         <v>60</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1564,19 +1582,20 @@
         <f t="shared" si="0"/>
         <v>10300301</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <v>103003</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <v>1</v>
       </c>
-      <c r="D15" s="5">
-        <v>20</v>
+      <c r="D15" s="7">
+        <f t="shared" ref="D15:D18" si="2">D10</f>
+        <v>10</v>
       </c>
       <c r="E15" s="6">
         <v>12</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1585,19 +1604,20 @@
         <f t="shared" si="0"/>
         <v>10300302</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <v>103003</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <v>2</v>
       </c>
-      <c r="D16" s="5">
-        <v>60</v>
+      <c r="D16" s="7">
+        <f t="shared" si="2"/>
+        <v>40</v>
       </c>
       <c r="E16" s="6">
         <v>24</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1606,19 +1626,20 @@
         <f t="shared" si="0"/>
         <v>10300303</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <v>103003</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <v>3</v>
       </c>
-      <c r="D17" s="5">
-        <v>180</v>
+      <c r="D17" s="7">
+        <f t="shared" si="2"/>
+        <v>120</v>
       </c>
       <c r="E17" s="6">
         <v>36</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1627,19 +1648,20 @@
         <f t="shared" si="0"/>
         <v>10300304</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="8">
         <v>103003</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <v>4</v>
       </c>
-      <c r="D18" s="5">
-        <v>540</v>
+      <c r="D18" s="7">
+        <f t="shared" si="2"/>
+        <v>360</v>
       </c>
       <c r="E18" s="6">
         <v>48</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1648,19 +1670,19 @@
         <f t="shared" si="0"/>
         <v>10300305</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <v>103003</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>5</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="7">
         <v>999999</v>
       </c>
       <c r="E19" s="6">
         <v>60</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1669,19 +1691,20 @@
         <f t="shared" si="0"/>
         <v>10400401</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="8">
         <v>104004</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>1</v>
       </c>
-      <c r="D20" s="5">
-        <v>20</v>
+      <c r="D20" s="7">
+        <f t="shared" ref="D20:D23" si="3">D15</f>
+        <v>10</v>
       </c>
       <c r="E20" s="6">
         <v>12</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1690,19 +1713,20 @@
         <f t="shared" si="0"/>
         <v>10400402</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="8">
         <v>104004</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <v>2</v>
       </c>
-      <c r="D21" s="5">
-        <v>60</v>
+      <c r="D21" s="7">
+        <f t="shared" si="3"/>
+        <v>40</v>
       </c>
       <c r="E21" s="6">
         <v>24</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1711,19 +1735,20 @@
         <f t="shared" si="0"/>
         <v>10400403</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="8">
         <v>104004</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <v>3</v>
       </c>
-      <c r="D22" s="5">
-        <v>180</v>
+      <c r="D22" s="7">
+        <f t="shared" si="3"/>
+        <v>120</v>
       </c>
       <c r="E22" s="6">
         <v>36</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1732,19 +1757,20 @@
         <f t="shared" si="0"/>
         <v>10400404</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="8">
         <v>104004</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <v>4</v>
       </c>
-      <c r="D23" s="5">
-        <v>540</v>
+      <c r="D23" s="7">
+        <f t="shared" si="3"/>
+        <v>360</v>
       </c>
       <c r="E23" s="6">
         <v>48</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1753,19 +1779,19 @@
         <f t="shared" si="0"/>
         <v>10400405</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="8">
         <v>104004</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="8">
         <v>5</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="7">
         <v>999999</v>
       </c>
       <c r="E24" s="6">
         <v>60</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1774,19 +1800,20 @@
         <f t="shared" si="0"/>
         <v>10500501</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="8">
         <v>105005</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="8">
         <v>1</v>
       </c>
-      <c r="D25" s="5">
-        <v>20</v>
+      <c r="D25" s="7">
+        <f t="shared" ref="D25:D28" si="4">D20</f>
+        <v>10</v>
       </c>
       <c r="E25" s="6">
         <v>12</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1795,19 +1822,20 @@
         <f t="shared" si="0"/>
         <v>10500502</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="8">
         <v>105005</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="8">
         <v>2</v>
       </c>
-      <c r="D26" s="5">
-        <v>60</v>
+      <c r="D26" s="7">
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="E26" s="6">
         <v>24</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1816,19 +1844,20 @@
         <f t="shared" si="0"/>
         <v>10500503</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="8">
         <v>105005</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <v>3</v>
       </c>
-      <c r="D27" s="5">
-        <v>180</v>
+      <c r="D27" s="7">
+        <f t="shared" si="4"/>
+        <v>120</v>
       </c>
       <c r="E27" s="6">
         <v>36</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1837,19 +1866,20 @@
         <f t="shared" si="0"/>
         <v>10500504</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="8">
         <v>105005</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="8">
         <v>4</v>
       </c>
-      <c r="D28" s="5">
-        <v>540</v>
+      <c r="D28" s="7">
+        <f t="shared" si="4"/>
+        <v>360</v>
       </c>
       <c r="E28" s="6">
         <v>48</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1858,19 +1888,19 @@
         <f t="shared" si="0"/>
         <v>10500505</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="8">
         <v>105005</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="8">
         <v>5</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="7">
         <v>999999</v>
       </c>
       <c r="E29" s="6">
         <v>60</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1879,19 +1909,20 @@
         <f t="shared" si="0"/>
         <v>20100601</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="8">
         <v>201006</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="8">
         <v>1</v>
       </c>
-      <c r="D30" s="5">
-        <v>20</v>
+      <c r="D30" s="7">
+        <f t="shared" ref="D30:D33" si="5">D25</f>
+        <v>10</v>
       </c>
       <c r="E30" s="6">
         <v>12</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1900,19 +1931,20 @@
         <f t="shared" si="0"/>
         <v>20100602</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="8">
         <v>201006</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="8">
         <v>2</v>
       </c>
-      <c r="D31" s="5">
-        <v>60</v>
+      <c r="D31" s="7">
+        <f t="shared" si="5"/>
+        <v>40</v>
       </c>
       <c r="E31" s="6">
         <v>24</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1921,19 +1953,20 @@
         <f t="shared" si="0"/>
         <v>20100603</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="8">
         <v>201006</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="8">
         <v>3</v>
       </c>
-      <c r="D32" s="5">
-        <v>180</v>
+      <c r="D32" s="7">
+        <f t="shared" si="5"/>
+        <v>120</v>
       </c>
       <c r="E32" s="6">
         <v>36</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1942,19 +1975,20 @@
         <f t="shared" si="0"/>
         <v>20100604</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="8">
         <v>201006</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="8">
         <v>4</v>
       </c>
-      <c r="D33" s="5">
-        <v>540</v>
+      <c r="D33" s="7">
+        <f t="shared" si="5"/>
+        <v>360</v>
       </c>
       <c r="E33" s="6">
         <v>48</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1963,19 +1997,19 @@
         <f t="shared" si="0"/>
         <v>20100605</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="8">
         <v>201006</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="8">
         <v>5</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="7">
         <v>999999</v>
       </c>
       <c r="E34" s="6">
         <v>60</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1984,19 +2018,19 @@
         <f t="shared" si="0"/>
         <v>20200701</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="8">
         <v>202007</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="8">
         <v>1</v>
       </c>
       <c r="D35" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E35" s="6">
         <v>12</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2005,19 +2039,19 @@
         <f t="shared" si="0"/>
         <v>20200702</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="8">
         <v>202007</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="8">
         <v>2</v>
       </c>
       <c r="D36" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E36" s="6">
         <v>24</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2026,907 +2060,943 @@
         <f t="shared" si="0"/>
         <v>20200703</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="8">
         <v>202007</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="8">
         <v>3</v>
       </c>
       <c r="D37" s="5">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E37" s="6">
         <v>36</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="3">
-        <f t="shared" ref="A38:A79" si="1">B38*100+C38</f>
+        <f t="shared" ref="A38:A79" si="6">B38*100+C38</f>
         <v>20200704</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="8">
         <v>202007</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="8">
         <v>4</v>
       </c>
       <c r="D38" s="5">
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="E38" s="6">
         <v>48</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="F38" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20200705</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="8">
         <v>202007</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="8">
         <v>5</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="7">
         <v>999999</v>
       </c>
       <c r="E39" s="6">
         <v>60</v>
       </c>
-      <c r="F39" s="8" t="s">
+      <c r="F39" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20300801</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="8">
         <v>203008</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="8">
         <v>1</v>
       </c>
-      <c r="D40" s="5">
-        <v>20</v>
+      <c r="D40" s="7">
+        <f t="shared" ref="D40:D64" si="7">D35</f>
+        <v>10</v>
       </c>
       <c r="E40" s="6">
         <v>12</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20300802</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="8">
         <v>203008</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="8">
         <v>2</v>
       </c>
-      <c r="D41" s="5">
-        <v>60</v>
+      <c r="D41" s="7">
+        <f t="shared" si="7"/>
+        <v>40</v>
       </c>
       <c r="E41" s="6">
         <v>24</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20300803</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="8">
         <v>203008</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="8">
         <v>3</v>
       </c>
-      <c r="D42" s="5">
-        <v>180</v>
+      <c r="D42" s="7">
+        <f t="shared" si="7"/>
+        <v>120</v>
       </c>
       <c r="E42" s="6">
         <v>36</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20300804</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="8">
         <v>203008</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="8">
         <v>4</v>
       </c>
-      <c r="D43" s="5">
-        <v>540</v>
+      <c r="D43" s="7">
+        <f t="shared" si="7"/>
+        <v>360</v>
       </c>
       <c r="E43" s="6">
         <v>48</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20300805</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="8">
         <v>203008</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="8">
         <v>5</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="7">
+        <f t="shared" si="7"/>
         <v>999999</v>
       </c>
       <c r="E44" s="6">
         <v>60</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20400901</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="8">
         <v>204009</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="8">
         <v>1</v>
       </c>
-      <c r="D45" s="5">
-        <v>20</v>
+      <c r="D45" s="7">
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="E45" s="6">
         <v>12</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F45" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20400902</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="8">
         <v>204009</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="8">
         <v>2</v>
       </c>
-      <c r="D46" s="5">
-        <v>60</v>
+      <c r="D46" s="7">
+        <f t="shared" si="7"/>
+        <v>40</v>
       </c>
       <c r="E46" s="6">
         <v>24</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20400903</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="8">
         <v>204009</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="8">
         <v>3</v>
       </c>
-      <c r="D47" s="5">
-        <v>180</v>
+      <c r="D47" s="7">
+        <f t="shared" si="7"/>
+        <v>120</v>
       </c>
       <c r="E47" s="6">
         <v>36</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20400904</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="8">
         <v>204009</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C48" s="8">
         <v>4</v>
       </c>
-      <c r="D48" s="5">
-        <v>540</v>
+      <c r="D48" s="7">
+        <f t="shared" si="7"/>
+        <v>360</v>
       </c>
       <c r="E48" s="6">
         <v>48</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F48" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20400905</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="8">
         <v>204009</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="8">
         <v>5</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="7">
+        <f t="shared" si="7"/>
         <v>999999</v>
       </c>
       <c r="E49" s="6">
         <v>60</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="F49" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20501001</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="8">
         <v>205010</v>
       </c>
-      <c r="C50" s="7">
+      <c r="C50" s="8">
         <v>1</v>
       </c>
-      <c r="D50" s="5">
-        <v>20</v>
+      <c r="D50" s="7">
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="E50" s="6">
         <v>12</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20501002</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="8">
         <v>205010</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C51" s="8">
         <v>2</v>
       </c>
-      <c r="D51" s="5">
-        <v>60</v>
+      <c r="D51" s="7">
+        <f t="shared" si="7"/>
+        <v>40</v>
       </c>
       <c r="E51" s="6">
         <v>24</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="F51" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20501003</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="8">
         <v>205010</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="8">
         <v>3</v>
       </c>
-      <c r="D52" s="5">
-        <v>180</v>
+      <c r="D52" s="7">
+        <f t="shared" si="7"/>
+        <v>120</v>
       </c>
       <c r="E52" s="6">
         <v>36</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="F52" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20501004</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="8">
         <v>205010</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C53" s="8">
         <v>4</v>
       </c>
-      <c r="D53" s="5">
-        <v>540</v>
+      <c r="D53" s="7">
+        <f t="shared" si="7"/>
+        <v>360</v>
       </c>
       <c r="E53" s="6">
         <v>48</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="F53" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20501005</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="8">
         <v>205010</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C54" s="8">
         <v>5</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D54" s="7">
+        <f t="shared" si="7"/>
         <v>999999</v>
       </c>
       <c r="E54" s="6">
         <v>60</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F54" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30101101</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="8">
         <v>301011</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C55" s="8">
         <v>1</v>
       </c>
-      <c r="D55" s="5">
-        <v>20</v>
+      <c r="D55" s="7">
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="E55" s="6">
         <v>12</v>
       </c>
-      <c r="F55" s="8" t="s">
+      <c r="F55" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30101102</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="8">
         <v>301011</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="8">
         <v>2</v>
       </c>
-      <c r="D56" s="5">
-        <v>60</v>
+      <c r="D56" s="7">
+        <f t="shared" si="7"/>
+        <v>40</v>
       </c>
       <c r="E56" s="6">
         <v>24</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="F56" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30101103</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="8">
         <v>301011</v>
       </c>
-      <c r="C57" s="7">
+      <c r="C57" s="8">
         <v>3</v>
       </c>
-      <c r="D57" s="5">
-        <v>180</v>
+      <c r="D57" s="7">
+        <f t="shared" si="7"/>
+        <v>120</v>
       </c>
       <c r="E57" s="6">
         <v>36</v>
       </c>
-      <c r="F57" s="8" t="s">
+      <c r="F57" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30101104</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="8">
         <v>301011</v>
       </c>
-      <c r="C58" s="7">
+      <c r="C58" s="8">
         <v>4</v>
       </c>
-      <c r="D58" s="5">
-        <v>540</v>
+      <c r="D58" s="7">
+        <f t="shared" si="7"/>
+        <v>360</v>
       </c>
       <c r="E58" s="6">
         <v>48</v>
       </c>
-      <c r="F58" s="8" t="s">
+      <c r="F58" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30101105</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="8">
         <v>301011</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C59" s="8">
         <v>5</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="7">
+        <f t="shared" si="7"/>
         <v>999999</v>
       </c>
       <c r="E59" s="6">
         <v>60</v>
       </c>
-      <c r="F59" s="8" t="s">
+      <c r="F59" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30201201</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="8">
         <v>302012</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="8">
         <v>1</v>
       </c>
-      <c r="D60" s="5">
-        <v>20</v>
+      <c r="D60" s="7">
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="E60" s="6">
         <v>12</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="F60" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30201202</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="8">
         <v>302012</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="8">
         <v>2</v>
       </c>
-      <c r="D61" s="5">
-        <v>60</v>
+      <c r="D61" s="7">
+        <f t="shared" si="7"/>
+        <v>40</v>
       </c>
       <c r="E61" s="6">
         <v>24</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="F61" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30201203</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="8">
         <v>302012</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="8">
         <v>3</v>
       </c>
-      <c r="D62" s="5">
-        <v>180</v>
+      <c r="D62" s="7">
+        <f t="shared" si="7"/>
+        <v>120</v>
       </c>
       <c r="E62" s="6">
         <v>36</v>
       </c>
-      <c r="F62" s="8" t="s">
+      <c r="F62" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30201204</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="8">
         <v>302012</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="8">
         <v>4</v>
       </c>
-      <c r="D63" s="5">
-        <v>540</v>
+      <c r="D63" s="7">
+        <f t="shared" si="7"/>
+        <v>360</v>
       </c>
       <c r="E63" s="6">
         <v>48</v>
       </c>
-      <c r="F63" s="8" t="s">
+      <c r="F63" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30201205</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="8">
         <v>302012</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C64" s="8">
         <v>5</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64" s="7">
+        <f t="shared" si="7"/>
         <v>999999</v>
       </c>
       <c r="E64" s="6">
         <v>60</v>
       </c>
-      <c r="F64" s="8" t="s">
+      <c r="F64" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30301301</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="10">
         <v>303013</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="8">
         <v>1</v>
       </c>
       <c r="D65" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E65" s="6">
         <v>12</v>
       </c>
-      <c r="F65" s="8" t="s">
+      <c r="F65" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30301302</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="10">
         <v>303013</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="8">
         <v>2</v>
       </c>
       <c r="D66" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E66" s="6">
         <v>24</v>
       </c>
-      <c r="F66" s="8" t="s">
+      <c r="F66" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30301303</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="10">
         <v>303013</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C67" s="8">
         <v>3</v>
       </c>
       <c r="D67" s="5">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E67" s="6">
         <v>36</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30301304</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="10">
         <v>303013</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="8">
         <v>4</v>
       </c>
       <c r="D68" s="5">
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="E68" s="6">
         <v>48</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F68" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30301305</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="10">
         <v>303013</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="8">
         <v>5</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="7">
+        <f t="shared" ref="D69:D94" si="8">D64</f>
         <v>999999</v>
       </c>
       <c r="E69" s="6">
         <v>60</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F69" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30401401</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="8">
         <v>304014</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="8">
         <v>1</v>
       </c>
-      <c r="D70" s="5">
-        <v>20</v>
+      <c r="D70" s="7">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="E70" s="6">
         <v>12</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F70" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30401402</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="8">
         <v>304014</v>
       </c>
-      <c r="C71" s="7">
+      <c r="C71" s="8">
         <v>2</v>
       </c>
-      <c r="D71" s="5">
-        <v>60</v>
+      <c r="D71" s="7">
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="E71" s="6">
         <v>24</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F71" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30401403</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="8">
         <v>304014</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C72" s="8">
         <v>3</v>
       </c>
-      <c r="D72" s="5">
-        <v>180</v>
+      <c r="D72" s="7">
+        <f t="shared" si="8"/>
+        <v>120</v>
       </c>
       <c r="E72" s="6">
         <v>36</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="F72" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30401404</v>
       </c>
-      <c r="B73" s="7">
+      <c r="B73" s="8">
         <v>304014</v>
       </c>
-      <c r="C73" s="7">
+      <c r="C73" s="8">
         <v>4</v>
       </c>
-      <c r="D73" s="5">
-        <v>540</v>
+      <c r="D73" s="7">
+        <f t="shared" si="8"/>
+        <v>360</v>
       </c>
       <c r="E73" s="6">
         <v>48</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F73" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30401405</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="8">
         <v>304014</v>
       </c>
-      <c r="C74" s="7">
+      <c r="C74" s="8">
         <v>5</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="7">
+        <f t="shared" si="8"/>
         <v>999999</v>
       </c>
       <c r="E74" s="6">
         <v>60</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30501501</v>
       </c>
-      <c r="B75" s="7">
+      <c r="B75" s="8">
         <v>305015</v>
       </c>
-      <c r="C75" s="7">
+      <c r="C75" s="8">
         <v>1</v>
       </c>
-      <c r="D75" s="5">
-        <v>20</v>
+      <c r="D75" s="7">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="E75" s="6">
         <v>12</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="F75" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30501502</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="8">
         <v>305015</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C76" s="8">
         <v>2</v>
       </c>
-      <c r="D76" s="5">
-        <v>60</v>
+      <c r="D76" s="7">
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="E76" s="6">
         <v>24</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F76" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30501503</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77" s="8">
         <v>305015</v>
       </c>
-      <c r="C77" s="7">
+      <c r="C77" s="8">
         <v>3</v>
       </c>
-      <c r="D77" s="5">
-        <v>180</v>
+      <c r="D77" s="7">
+        <f t="shared" si="8"/>
+        <v>120</v>
       </c>
       <c r="E77" s="6">
         <v>36</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="F77" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30501504</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78" s="8">
         <v>305015</v>
       </c>
-      <c r="C78" s="7">
+      <c r="C78" s="8">
         <v>4</v>
       </c>
-      <c r="D78" s="5">
-        <v>540</v>
+      <c r="D78" s="7">
+        <f t="shared" si="8"/>
+        <v>360</v>
       </c>
       <c r="E78" s="6">
         <v>48</v>
       </c>
-      <c r="F78" s="8" t="s">
+      <c r="F78" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>30501505</v>
       </c>
-      <c r="B79" s="7">
+      <c r="B79" s="8">
         <v>305015</v>
       </c>
-      <c r="C79" s="7">
+      <c r="C79" s="8">
         <v>5</v>
       </c>
-      <c r="D79" s="5">
+      <c r="D79" s="7">
+        <f t="shared" si="8"/>
         <v>999999</v>
       </c>
       <c r="E79" s="6">
         <v>60</v>
       </c>
-      <c r="F79" s="8" t="s">
+      <c r="F79" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="3">
-        <f t="shared" ref="A80:A111" si="2">B80*100+C80</f>
+        <f t="shared" ref="A80:A111" si="9">B80*100+C80</f>
         <v>10101601</v>
       </c>
       <c r="B80" s="4">
@@ -2935,19 +3005,20 @@
       <c r="C80" s="4">
         <v>1</v>
       </c>
-      <c r="D80" s="5">
-        <v>20</v>
+      <c r="D80" s="7">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="E80" s="6">
         <v>12</v>
       </c>
-      <c r="F80" s="5" t="s">
+      <c r="F80" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10101602</v>
       </c>
       <c r="B81" s="4">
@@ -2956,19 +3027,20 @@
       <c r="C81" s="4">
         <v>2</v>
       </c>
-      <c r="D81" s="5">
-        <v>60</v>
+      <c r="D81" s="7">
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="E81" s="6">
         <v>24</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="F81" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10101603</v>
       </c>
       <c r="B82" s="4">
@@ -2977,19 +3049,20 @@
       <c r="C82" s="4">
         <v>3</v>
       </c>
-      <c r="D82" s="5">
-        <v>180</v>
+      <c r="D82" s="7">
+        <f t="shared" si="8"/>
+        <v>120</v>
       </c>
       <c r="E82" s="6">
         <v>36</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="F82" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10101604</v>
       </c>
       <c r="B83" s="4">
@@ -2998,19 +3071,20 @@
       <c r="C83" s="4">
         <v>4</v>
       </c>
-      <c r="D83" s="5">
-        <v>540</v>
+      <c r="D83" s="7">
+        <f t="shared" si="8"/>
+        <v>360</v>
       </c>
       <c r="E83" s="6">
         <v>48</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="F83" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10101605</v>
       </c>
       <c r="B84" s="4">
@@ -3019,1483 +3093,1546 @@
       <c r="C84" s="4">
         <v>5</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D84" s="7">
+        <f t="shared" si="8"/>
         <v>999999</v>
       </c>
       <c r="E84" s="6">
         <v>60</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="F84" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10201701</v>
       </c>
       <c r="B85" s="1">
         <v>102017</v>
       </c>
-      <c r="C85" s="7">
+      <c r="C85" s="8">
         <v>1</v>
       </c>
-      <c r="D85" s="5">
-        <v>20</v>
+      <c r="D85" s="7">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="E85" s="6">
         <v>12</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="F85" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10201702</v>
       </c>
       <c r="B86" s="1">
         <v>102017</v>
       </c>
-      <c r="C86" s="7">
+      <c r="C86" s="8">
         <v>2</v>
       </c>
-      <c r="D86" s="5">
-        <v>60</v>
+      <c r="D86" s="7">
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="E86" s="6">
         <v>24</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="F86" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10201703</v>
       </c>
       <c r="B87" s="1">
         <v>102017</v>
       </c>
-      <c r="C87" s="7">
+      <c r="C87" s="8">
         <v>3</v>
       </c>
-      <c r="D87" s="5">
-        <v>180</v>
+      <c r="D87" s="7">
+        <f t="shared" si="8"/>
+        <v>120</v>
       </c>
       <c r="E87" s="6">
         <v>36</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="F87" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10201704</v>
       </c>
       <c r="B88" s="1">
         <v>102017</v>
       </c>
-      <c r="C88" s="7">
+      <c r="C88" s="8">
         <v>4</v>
       </c>
-      <c r="D88" s="5">
-        <v>540</v>
+      <c r="D88" s="7">
+        <f t="shared" si="8"/>
+        <v>360</v>
       </c>
       <c r="E88" s="6">
         <v>48</v>
       </c>
-      <c r="F88" s="5" t="s">
+      <c r="F88" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10201705</v>
       </c>
       <c r="B89" s="1">
         <v>102017</v>
       </c>
-      <c r="C89" s="7">
+      <c r="C89" s="8">
         <v>5</v>
       </c>
-      <c r="D89" s="5">
+      <c r="D89" s="7">
+        <f t="shared" si="8"/>
         <v>999999</v>
       </c>
       <c r="E89" s="6">
         <v>60</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F89" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10301801</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90" s="8">
         <v>103018</v>
       </c>
-      <c r="C90" s="7">
+      <c r="C90" s="8">
         <v>1</v>
       </c>
-      <c r="D90" s="5">
-        <v>20</v>
+      <c r="D90" s="7">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="E90" s="6">
         <v>12</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F90" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10301802</v>
       </c>
-      <c r="B91" s="7">
+      <c r="B91" s="8">
         <v>103018</v>
       </c>
-      <c r="C91" s="7">
+      <c r="C91" s="8">
         <v>2</v>
       </c>
-      <c r="D91" s="5">
-        <v>60</v>
+      <c r="D91" s="7">
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="E91" s="6">
         <v>24</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="F91" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10301803</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92" s="8">
         <v>103018</v>
       </c>
-      <c r="C92" s="7">
+      <c r="C92" s="8">
         <v>3</v>
       </c>
-      <c r="D92" s="5">
-        <v>180</v>
+      <c r="D92" s="7">
+        <f t="shared" si="8"/>
+        <v>120</v>
       </c>
       <c r="E92" s="6">
         <v>36</v>
       </c>
-      <c r="F92" s="5" t="s">
+      <c r="F92" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10301804</v>
       </c>
-      <c r="B93" s="7">
+      <c r="B93" s="8">
         <v>103018</v>
       </c>
-      <c r="C93" s="7">
+      <c r="C93" s="8">
         <v>4</v>
       </c>
-      <c r="D93" s="5">
-        <v>540</v>
+      <c r="D93" s="7">
+        <f t="shared" si="8"/>
+        <v>360</v>
       </c>
       <c r="E93" s="6">
         <v>48</v>
       </c>
-      <c r="F93" s="5" t="s">
+      <c r="F93" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10301805</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="8">
         <v>103018</v>
       </c>
-      <c r="C94" s="7">
+      <c r="C94" s="8">
         <v>5</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D94" s="7">
+        <f t="shared" si="8"/>
         <v>999999</v>
       </c>
       <c r="E94" s="6">
         <v>60</v>
       </c>
-      <c r="F94" s="5" t="s">
+      <c r="F94" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10401901</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95" s="8">
         <v>104019</v>
       </c>
-      <c r="C95" s="7">
+      <c r="C95" s="8">
         <v>1</v>
       </c>
       <c r="D95" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E95" s="6">
         <v>12</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="F95" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10401902</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="8">
         <v>104019</v>
       </c>
-      <c r="C96" s="7">
+      <c r="C96" s="8">
         <v>2</v>
       </c>
       <c r="D96" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E96" s="6">
         <v>24</v>
       </c>
-      <c r="F96" s="5" t="s">
+      <c r="F96" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10401903</v>
       </c>
-      <c r="B97" s="7">
+      <c r="B97" s="8">
         <v>104019</v>
       </c>
-      <c r="C97" s="7">
+      <c r="C97" s="8">
         <v>3</v>
       </c>
       <c r="D97" s="5">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E97" s="6">
         <v>36</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="F97" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10401904</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="8">
         <v>104019</v>
       </c>
-      <c r="C98" s="7">
+      <c r="C98" s="8">
         <v>4</v>
       </c>
       <c r="D98" s="5">
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="E98" s="6">
         <v>48</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="F98" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10401905</v>
       </c>
-      <c r="B99" s="7">
+      <c r="B99" s="8">
         <v>104019</v>
       </c>
-      <c r="C99" s="7">
+      <c r="C99" s="8">
         <v>5</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D99" s="7">
+        <f t="shared" ref="D99:D124" si="10">D94</f>
         <v>999999</v>
       </c>
       <c r="E99" s="6">
         <v>60</v>
       </c>
-      <c r="F99" s="5" t="s">
+      <c r="F99" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10502001</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100" s="8">
         <v>105020</v>
       </c>
-      <c r="C100" s="7">
+      <c r="C100" s="8">
         <v>1</v>
       </c>
-      <c r="D100" s="5">
-        <v>20</v>
+      <c r="D100" s="7">
+        <f t="shared" si="10"/>
+        <v>10</v>
       </c>
       <c r="E100" s="6">
         <v>12</v>
       </c>
-      <c r="F100" s="5" t="s">
+      <c r="F100" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10502002</v>
       </c>
-      <c r="B101" s="7">
+      <c r="B101" s="8">
         <v>105020</v>
       </c>
-      <c r="C101" s="7">
+      <c r="C101" s="8">
         <v>2</v>
       </c>
-      <c r="D101" s="5">
-        <v>60</v>
+      <c r="D101" s="7">
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="E101" s="6">
         <v>24</v>
       </c>
-      <c r="F101" s="5" t="s">
+      <c r="F101" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10502003</v>
       </c>
-      <c r="B102" s="7">
+      <c r="B102" s="8">
         <v>105020</v>
       </c>
-      <c r="C102" s="7">
+      <c r="C102" s="8">
         <v>3</v>
       </c>
-      <c r="D102" s="5">
-        <v>180</v>
+      <c r="D102" s="7">
+        <f t="shared" si="10"/>
+        <v>120</v>
       </c>
       <c r="E102" s="6">
         <v>36</v>
       </c>
-      <c r="F102" s="5" t="s">
+      <c r="F102" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10502004</v>
       </c>
-      <c r="B103" s="7">
+      <c r="B103" s="8">
         <v>105020</v>
       </c>
-      <c r="C103" s="7">
+      <c r="C103" s="8">
         <v>4</v>
       </c>
-      <c r="D103" s="5">
-        <v>540</v>
+      <c r="D103" s="7">
+        <f t="shared" si="10"/>
+        <v>360</v>
       </c>
       <c r="E103" s="6">
         <v>48</v>
       </c>
-      <c r="F103" s="5" t="s">
+      <c r="F103" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>10502005</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="8">
         <v>105020</v>
       </c>
-      <c r="C104" s="7">
+      <c r="C104" s="8">
         <v>5</v>
       </c>
-      <c r="D104" s="5">
+      <c r="D104" s="7">
+        <f t="shared" si="10"/>
         <v>999999</v>
       </c>
       <c r="E104" s="6">
         <v>60</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="F104" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20102101</v>
       </c>
-      <c r="B105" s="7">
+      <c r="B105" s="8">
         <v>201021</v>
       </c>
-      <c r="C105" s="7">
+      <c r="C105" s="8">
         <v>1</v>
       </c>
-      <c r="D105" s="5">
-        <v>20</v>
+      <c r="D105" s="7">
+        <f t="shared" si="10"/>
+        <v>10</v>
       </c>
       <c r="E105" s="6">
         <v>12</v>
       </c>
-      <c r="F105" s="8" t="s">
+      <c r="F105" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20102102</v>
       </c>
-      <c r="B106" s="7">
+      <c r="B106" s="8">
         <v>201021</v>
       </c>
-      <c r="C106" s="7">
+      <c r="C106" s="8">
         <v>2</v>
       </c>
-      <c r="D106" s="5">
-        <v>60</v>
+      <c r="D106" s="7">
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="E106" s="6">
         <v>24</v>
       </c>
-      <c r="F106" s="8" t="s">
+      <c r="F106" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20102103</v>
       </c>
-      <c r="B107" s="7">
+      <c r="B107" s="8">
         <v>201021</v>
       </c>
-      <c r="C107" s="7">
+      <c r="C107" s="8">
         <v>3</v>
       </c>
-      <c r="D107" s="5">
-        <v>180</v>
+      <c r="D107" s="7">
+        <f t="shared" si="10"/>
+        <v>120</v>
       </c>
       <c r="E107" s="6">
         <v>36</v>
       </c>
-      <c r="F107" s="8" t="s">
+      <c r="F107" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20102104</v>
       </c>
-      <c r="B108" s="7">
+      <c r="B108" s="8">
         <v>201021</v>
       </c>
-      <c r="C108" s="7">
+      <c r="C108" s="8">
         <v>4</v>
       </c>
-      <c r="D108" s="5">
-        <v>540</v>
+      <c r="D108" s="7">
+        <f t="shared" si="10"/>
+        <v>360</v>
       </c>
       <c r="E108" s="6">
         <v>48</v>
       </c>
-      <c r="F108" s="8" t="s">
+      <c r="F108" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20102105</v>
       </c>
-      <c r="B109" s="7">
+      <c r="B109" s="8">
         <v>201021</v>
       </c>
-      <c r="C109" s="7">
+      <c r="C109" s="8">
         <v>5</v>
       </c>
-      <c r="D109" s="5">
+      <c r="D109" s="7">
+        <f t="shared" si="10"/>
         <v>999999</v>
       </c>
       <c r="E109" s="6">
         <v>60</v>
       </c>
-      <c r="F109" s="8" t="s">
+      <c r="F109" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20202201</v>
       </c>
-      <c r="B110" s="7">
+      <c r="B110" s="8">
         <v>202022</v>
       </c>
-      <c r="C110" s="7">
+      <c r="C110" s="8">
         <v>1</v>
       </c>
-      <c r="D110" s="5">
-        <v>20</v>
+      <c r="D110" s="7">
+        <f t="shared" si="10"/>
+        <v>10</v>
       </c>
       <c r="E110" s="6">
         <v>12</v>
       </c>
-      <c r="F110" s="8" t="s">
+      <c r="F110" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20202202</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="8">
         <v>202022</v>
       </c>
-      <c r="C111" s="7">
+      <c r="C111" s="8">
         <v>2</v>
       </c>
-      <c r="D111" s="5">
-        <v>60</v>
+      <c r="D111" s="7">
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="E111" s="6">
         <v>24</v>
       </c>
-      <c r="F111" s="8" t="s">
+      <c r="F111" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="3">
-        <f t="shared" ref="A112:A154" si="3">B112*100+C112</f>
+        <f t="shared" ref="A112:A154" si="11">B112*100+C112</f>
         <v>20202203</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="8">
         <v>202022</v>
       </c>
-      <c r="C112" s="7">
+      <c r="C112" s="8">
         <v>3</v>
       </c>
-      <c r="D112" s="5">
-        <v>180</v>
+      <c r="D112" s="7">
+        <f t="shared" si="10"/>
+        <v>120</v>
       </c>
       <c r="E112" s="6">
         <v>36</v>
       </c>
-      <c r="F112" s="8" t="s">
+      <c r="F112" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20202204</v>
       </c>
-      <c r="B113" s="7">
+      <c r="B113" s="8">
         <v>202022</v>
       </c>
-      <c r="C113" s="7">
+      <c r="C113" s="8">
         <v>4</v>
       </c>
-      <c r="D113" s="5">
-        <v>540</v>
+      <c r="D113" s="7">
+        <f t="shared" si="10"/>
+        <v>360</v>
       </c>
       <c r="E113" s="6">
         <v>48</v>
       </c>
-      <c r="F113" s="8" t="s">
+      <c r="F113" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20202205</v>
       </c>
-      <c r="B114" s="7">
+      <c r="B114" s="8">
         <v>202022</v>
       </c>
-      <c r="C114" s="7">
+      <c r="C114" s="8">
         <v>5</v>
       </c>
-      <c r="D114" s="5">
+      <c r="D114" s="7">
+        <f t="shared" si="10"/>
         <v>999999</v>
       </c>
       <c r="E114" s="6">
         <v>60</v>
       </c>
-      <c r="F114" s="8" t="s">
+      <c r="F114" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20302301</v>
       </c>
-      <c r="B115" s="7">
+      <c r="B115" s="8">
         <v>203023</v>
       </c>
-      <c r="C115" s="7">
+      <c r="C115" s="8">
         <v>1</v>
       </c>
-      <c r="D115" s="5">
-        <v>20</v>
+      <c r="D115" s="7">
+        <f t="shared" si="10"/>
+        <v>10</v>
       </c>
       <c r="E115" s="6">
         <v>12</v>
       </c>
-      <c r="F115" s="8" t="s">
+      <c r="F115" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20302302</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="8">
         <v>203023</v>
       </c>
-      <c r="C116" s="7">
+      <c r="C116" s="8">
         <v>2</v>
       </c>
-      <c r="D116" s="5">
-        <v>60</v>
+      <c r="D116" s="7">
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="E116" s="6">
         <v>24</v>
       </c>
-      <c r="F116" s="8" t="s">
+      <c r="F116" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20302303</v>
       </c>
-      <c r="B117" s="7">
+      <c r="B117" s="8">
         <v>203023</v>
       </c>
-      <c r="C117" s="7">
+      <c r="C117" s="8">
         <v>3</v>
       </c>
-      <c r="D117" s="5">
-        <v>180</v>
+      <c r="D117" s="7">
+        <f t="shared" si="10"/>
+        <v>120</v>
       </c>
       <c r="E117" s="6">
         <v>36</v>
       </c>
-      <c r="F117" s="8" t="s">
+      <c r="F117" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20302304</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="8">
         <v>203023</v>
       </c>
-      <c r="C118" s="7">
+      <c r="C118" s="8">
         <v>4</v>
       </c>
-      <c r="D118" s="5">
-        <v>540</v>
+      <c r="D118" s="7">
+        <f t="shared" si="10"/>
+        <v>360</v>
       </c>
       <c r="E118" s="6">
         <v>48</v>
       </c>
-      <c r="F118" s="8" t="s">
+      <c r="F118" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20302305</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="8">
         <v>203023</v>
       </c>
-      <c r="C119" s="7">
+      <c r="C119" s="8">
         <v>5</v>
       </c>
-      <c r="D119" s="5">
+      <c r="D119" s="7">
+        <f t="shared" si="10"/>
         <v>999999</v>
       </c>
       <c r="E119" s="6">
         <v>60</v>
       </c>
-      <c r="F119" s="8" t="s">
+      <c r="F119" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20402401</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="8">
         <v>204024</v>
       </c>
-      <c r="C120" s="7">
+      <c r="C120" s="8">
         <v>1</v>
       </c>
-      <c r="D120" s="5">
-        <v>20</v>
+      <c r="D120" s="7">
+        <f t="shared" si="10"/>
+        <v>10</v>
       </c>
       <c r="E120" s="6">
         <v>12</v>
       </c>
-      <c r="F120" s="8" t="s">
+      <c r="F120" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20402402</v>
       </c>
-      <c r="B121" s="7">
+      <c r="B121" s="8">
         <v>204024</v>
       </c>
-      <c r="C121" s="7">
+      <c r="C121" s="8">
         <v>2</v>
       </c>
-      <c r="D121" s="5">
-        <v>60</v>
+      <c r="D121" s="7">
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="E121" s="6">
         <v>24</v>
       </c>
-      <c r="F121" s="8" t="s">
+      <c r="F121" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20402403</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="8">
         <v>204024</v>
       </c>
-      <c r="C122" s="7">
+      <c r="C122" s="8">
         <v>3</v>
       </c>
-      <c r="D122" s="5">
-        <v>180</v>
+      <c r="D122" s="7">
+        <f t="shared" si="10"/>
+        <v>120</v>
       </c>
       <c r="E122" s="6">
         <v>36</v>
       </c>
-      <c r="F122" s="8" t="s">
+      <c r="F122" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20402404</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="8">
         <v>204024</v>
       </c>
-      <c r="C123" s="7">
+      <c r="C123" s="8">
         <v>4</v>
       </c>
-      <c r="D123" s="5">
-        <v>540</v>
+      <c r="D123" s="7">
+        <f t="shared" si="10"/>
+        <v>360</v>
       </c>
       <c r="E123" s="6">
         <v>48</v>
       </c>
-      <c r="F123" s="8" t="s">
+      <c r="F123" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20402405</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="8">
         <v>204024</v>
       </c>
-      <c r="C124" s="7">
+      <c r="C124" s="8">
         <v>5</v>
       </c>
-      <c r="D124" s="5">
+      <c r="D124" s="7">
+        <f t="shared" si="10"/>
         <v>999999</v>
       </c>
       <c r="E124" s="6">
         <v>60</v>
       </c>
-      <c r="F124" s="8" t="s">
+      <c r="F124" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20502501</v>
       </c>
-      <c r="B125" s="7">
+      <c r="B125" s="8">
         <v>205025</v>
       </c>
-      <c r="C125" s="7">
+      <c r="C125" s="8">
         <v>1</v>
       </c>
       <c r="D125" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E125" s="6">
         <v>12</v>
       </c>
-      <c r="F125" s="8" t="s">
+      <c r="F125" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20502502</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="8">
         <v>205025</v>
       </c>
-      <c r="C126" s="7">
+      <c r="C126" s="8">
         <v>2</v>
       </c>
       <c r="D126" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E126" s="6">
         <v>24</v>
       </c>
-      <c r="F126" s="8" t="s">
+      <c r="F126" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20502503</v>
       </c>
-      <c r="B127" s="7">
+      <c r="B127" s="8">
         <v>205025</v>
       </c>
-      <c r="C127" s="7">
+      <c r="C127" s="8">
         <v>3</v>
       </c>
       <c r="D127" s="5">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E127" s="6">
         <v>36</v>
       </c>
-      <c r="F127" s="8" t="s">
+      <c r="F127" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20502504</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="8">
         <v>205025</v>
       </c>
-      <c r="C128" s="7">
+      <c r="C128" s="8">
         <v>4</v>
       </c>
       <c r="D128" s="5">
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="E128" s="6">
         <v>48</v>
       </c>
-      <c r="F128" s="8" t="s">
+      <c r="F128" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>20502505</v>
       </c>
-      <c r="B129" s="7">
+      <c r="B129" s="8">
         <v>205025</v>
       </c>
-      <c r="C129" s="7">
+      <c r="C129" s="8">
         <v>5</v>
       </c>
-      <c r="D129" s="5">
+      <c r="D129" s="7">
+        <f t="shared" ref="D129:D154" si="12">D124</f>
         <v>999999</v>
       </c>
       <c r="E129" s="6">
         <v>60</v>
       </c>
-      <c r="F129" s="8" t="s">
+      <c r="F129" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30102601</v>
       </c>
-      <c r="B130" s="7">
+      <c r="B130" s="8">
         <v>301026</v>
       </c>
-      <c r="C130" s="7">
+      <c r="C130" s="8">
         <v>1</v>
       </c>
-      <c r="D130" s="5">
-        <v>20</v>
+      <c r="D130" s="7">
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="E130" s="6">
         <v>12</v>
       </c>
-      <c r="F130" s="8" t="s">
+      <c r="F130" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30102602</v>
       </c>
-      <c r="B131" s="7">
+      <c r="B131" s="8">
         <v>301026</v>
       </c>
-      <c r="C131" s="7">
+      <c r="C131" s="8">
         <v>2</v>
       </c>
-      <c r="D131" s="5">
-        <v>60</v>
+      <c r="D131" s="7">
+        <f t="shared" si="12"/>
+        <v>40</v>
       </c>
       <c r="E131" s="6">
         <v>24</v>
       </c>
-      <c r="F131" s="8" t="s">
+      <c r="F131" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30102603</v>
       </c>
-      <c r="B132" s="7">
+      <c r="B132" s="8">
         <v>301026</v>
       </c>
-      <c r="C132" s="7">
+      <c r="C132" s="8">
         <v>3</v>
       </c>
-      <c r="D132" s="5">
-        <v>180</v>
+      <c r="D132" s="7">
+        <f t="shared" si="12"/>
+        <v>120</v>
       </c>
       <c r="E132" s="6">
         <v>36</v>
       </c>
-      <c r="F132" s="8" t="s">
+      <c r="F132" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30102604</v>
       </c>
-      <c r="B133" s="7">
+      <c r="B133" s="8">
         <v>301026</v>
       </c>
-      <c r="C133" s="7">
+      <c r="C133" s="8">
         <v>4</v>
       </c>
-      <c r="D133" s="5">
-        <v>540</v>
+      <c r="D133" s="7">
+        <f t="shared" si="12"/>
+        <v>360</v>
       </c>
       <c r="E133" s="6">
         <v>48</v>
       </c>
-      <c r="F133" s="8" t="s">
+      <c r="F133" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30102605</v>
       </c>
-      <c r="B134" s="7">
+      <c r="B134" s="8">
         <v>301026</v>
       </c>
-      <c r="C134" s="7">
+      <c r="C134" s="8">
         <v>5</v>
       </c>
-      <c r="D134" s="5">
+      <c r="D134" s="7">
+        <f t="shared" si="12"/>
         <v>999999</v>
       </c>
       <c r="E134" s="6">
         <v>60</v>
       </c>
-      <c r="F134" s="8" t="s">
+      <c r="F134" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30202701</v>
       </c>
-      <c r="B135" s="7">
+      <c r="B135" s="8">
         <v>302027</v>
       </c>
-      <c r="C135" s="7">
+      <c r="C135" s="8">
         <v>1</v>
       </c>
-      <c r="D135" s="5">
-        <v>20</v>
+      <c r="D135" s="7">
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="E135" s="6">
         <v>12</v>
       </c>
-      <c r="F135" s="8" t="s">
+      <c r="F135" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30202702</v>
       </c>
-      <c r="B136" s="7">
+      <c r="B136" s="8">
         <v>302027</v>
       </c>
-      <c r="C136" s="7">
+      <c r="C136" s="8">
         <v>2</v>
       </c>
-      <c r="D136" s="5">
-        <v>60</v>
+      <c r="D136" s="7">
+        <f t="shared" si="12"/>
+        <v>40</v>
       </c>
       <c r="E136" s="6">
         <v>24</v>
       </c>
-      <c r="F136" s="8" t="s">
+      <c r="F136" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30202703</v>
       </c>
-      <c r="B137" s="7">
+      <c r="B137" s="8">
         <v>302027</v>
       </c>
-      <c r="C137" s="7">
+      <c r="C137" s="8">
         <v>3</v>
       </c>
-      <c r="D137" s="5">
-        <v>180</v>
+      <c r="D137" s="7">
+        <f t="shared" si="12"/>
+        <v>120</v>
       </c>
       <c r="E137" s="6">
         <v>36</v>
       </c>
-      <c r="F137" s="8" t="s">
+      <c r="F137" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30202704</v>
       </c>
-      <c r="B138" s="7">
+      <c r="B138" s="8">
         <v>302027</v>
       </c>
-      <c r="C138" s="7">
+      <c r="C138" s="8">
         <v>4</v>
       </c>
-      <c r="D138" s="5">
-        <v>540</v>
+      <c r="D138" s="7">
+        <f t="shared" si="12"/>
+        <v>360</v>
       </c>
       <c r="E138" s="6">
         <v>48</v>
       </c>
-      <c r="F138" s="8" t="s">
+      <c r="F138" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30202705</v>
       </c>
-      <c r="B139" s="7">
+      <c r="B139" s="8">
         <v>302027</v>
       </c>
-      <c r="C139" s="7">
+      <c r="C139" s="8">
         <v>5</v>
       </c>
-      <c r="D139" s="5">
+      <c r="D139" s="7">
+        <f t="shared" si="12"/>
         <v>999999</v>
       </c>
       <c r="E139" s="6">
         <v>60</v>
       </c>
-      <c r="F139" s="8" t="s">
+      <c r="F139" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30302801</v>
       </c>
-      <c r="B140" s="9">
+      <c r="B140" s="10">
         <v>303028</v>
       </c>
-      <c r="C140" s="7">
+      <c r="C140" s="8">
         <v>1</v>
       </c>
-      <c r="D140" s="5">
-        <v>20</v>
+      <c r="D140" s="7">
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="E140" s="6">
         <v>12</v>
       </c>
-      <c r="F140" s="8" t="s">
+      <c r="F140" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30302802</v>
       </c>
-      <c r="B141" s="9">
+      <c r="B141" s="10">
         <v>303028</v>
       </c>
-      <c r="C141" s="7">
+      <c r="C141" s="8">
         <v>2</v>
       </c>
-      <c r="D141" s="5">
-        <v>60</v>
+      <c r="D141" s="7">
+        <f t="shared" si="12"/>
+        <v>40</v>
       </c>
       <c r="E141" s="6">
         <v>24</v>
       </c>
-      <c r="F141" s="8" t="s">
+      <c r="F141" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30302803</v>
       </c>
-      <c r="B142" s="9">
+      <c r="B142" s="10">
         <v>303028</v>
       </c>
-      <c r="C142" s="7">
+      <c r="C142" s="8">
         <v>3</v>
       </c>
-      <c r="D142" s="5">
-        <v>180</v>
+      <c r="D142" s="7">
+        <f t="shared" si="12"/>
+        <v>120</v>
       </c>
       <c r="E142" s="6">
         <v>36</v>
       </c>
-      <c r="F142" s="8" t="s">
+      <c r="F142" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30302804</v>
       </c>
-      <c r="B143" s="9">
+      <c r="B143" s="10">
         <v>303028</v>
       </c>
-      <c r="C143" s="7">
+      <c r="C143" s="8">
         <v>4</v>
       </c>
-      <c r="D143" s="5">
-        <v>540</v>
+      <c r="D143" s="7">
+        <f t="shared" si="12"/>
+        <v>360</v>
       </c>
       <c r="E143" s="6">
         <v>48</v>
       </c>
-      <c r="F143" s="8" t="s">
+      <c r="F143" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30302805</v>
       </c>
-      <c r="B144" s="9">
+      <c r="B144" s="10">
         <v>303028</v>
       </c>
-      <c r="C144" s="7">
+      <c r="C144" s="8">
         <v>5</v>
       </c>
-      <c r="D144" s="5">
+      <c r="D144" s="7">
+        <f t="shared" si="12"/>
         <v>999999</v>
       </c>
       <c r="E144" s="6">
         <v>60</v>
       </c>
-      <c r="F144" s="8" t="s">
+      <c r="F144" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30402901</v>
       </c>
-      <c r="B145" s="7">
+      <c r="B145" s="8">
         <v>304029</v>
       </c>
-      <c r="C145" s="7">
+      <c r="C145" s="8">
         <v>1</v>
       </c>
-      <c r="D145" s="5">
-        <v>20</v>
+      <c r="D145" s="7">
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="E145" s="6">
         <v>12</v>
       </c>
-      <c r="F145" s="8" t="s">
+      <c r="F145" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30402902</v>
       </c>
-      <c r="B146" s="7">
+      <c r="B146" s="8">
         <v>304029</v>
       </c>
-      <c r="C146" s="7">
+      <c r="C146" s="8">
         <v>2</v>
       </c>
-      <c r="D146" s="5">
-        <v>60</v>
+      <c r="D146" s="7">
+        <f t="shared" si="12"/>
+        <v>40</v>
       </c>
       <c r="E146" s="6">
         <v>24</v>
       </c>
-      <c r="F146" s="8" t="s">
+      <c r="F146" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30402903</v>
       </c>
-      <c r="B147" s="7">
+      <c r="B147" s="8">
         <v>304029</v>
       </c>
-      <c r="C147" s="7">
+      <c r="C147" s="8">
         <v>3</v>
       </c>
-      <c r="D147" s="5">
-        <v>180</v>
+      <c r="D147" s="7">
+        <f t="shared" si="12"/>
+        <v>120</v>
       </c>
       <c r="E147" s="6">
         <v>36</v>
       </c>
-      <c r="F147" s="8" t="s">
+      <c r="F147" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30402904</v>
       </c>
-      <c r="B148" s="7">
+      <c r="B148" s="8">
         <v>304029</v>
       </c>
-      <c r="C148" s="7">
+      <c r="C148" s="8">
         <v>4</v>
       </c>
-      <c r="D148" s="5">
-        <v>540</v>
+      <c r="D148" s="7">
+        <f t="shared" si="12"/>
+        <v>360</v>
       </c>
       <c r="E148" s="6">
         <v>48</v>
       </c>
-      <c r="F148" s="8" t="s">
+      <c r="F148" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30402905</v>
       </c>
-      <c r="B149" s="7">
+      <c r="B149" s="8">
         <v>304029</v>
       </c>
-      <c r="C149" s="7">
+      <c r="C149" s="8">
         <v>5</v>
       </c>
-      <c r="D149" s="5">
+      <c r="D149" s="7">
+        <f t="shared" si="12"/>
         <v>999999</v>
       </c>
       <c r="E149" s="6">
         <v>60</v>
       </c>
-      <c r="F149" s="8" t="s">
+      <c r="F149" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30503001</v>
       </c>
-      <c r="B150" s="7">
+      <c r="B150" s="8">
         <v>305030</v>
       </c>
-      <c r="C150" s="7">
+      <c r="C150" s="8">
         <v>1</v>
       </c>
-      <c r="D150" s="5">
-        <v>20</v>
+      <c r="D150" s="7">
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="E150" s="6">
         <v>12</v>
       </c>
-      <c r="F150" s="8" t="s">
+      <c r="F150" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30503002</v>
       </c>
-      <c r="B151" s="7">
+      <c r="B151" s="8">
         <v>305030</v>
       </c>
-      <c r="C151" s="7">
+      <c r="C151" s="8">
         <v>2</v>
       </c>
-      <c r="D151" s="5">
-        <v>60</v>
+      <c r="D151" s="7">
+        <f t="shared" si="12"/>
+        <v>40</v>
       </c>
       <c r="E151" s="6">
         <v>24</v>
       </c>
-      <c r="F151" s="8" t="s">
+      <c r="F151" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30503003</v>
       </c>
-      <c r="B152" s="7">
+      <c r="B152" s="8">
         <v>305030</v>
       </c>
-      <c r="C152" s="7">
+      <c r="C152" s="8">
         <v>3</v>
       </c>
-      <c r="D152" s="5">
-        <v>180</v>
+      <c r="D152" s="7">
+        <f t="shared" si="12"/>
+        <v>120</v>
       </c>
       <c r="E152" s="6">
         <v>36</v>
       </c>
-      <c r="F152" s="8" t="s">
+      <c r="F152" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30503004</v>
       </c>
-      <c r="B153" s="7">
+      <c r="B153" s="8">
         <v>305030</v>
       </c>
-      <c r="C153" s="7">
+      <c r="C153" s="8">
         <v>4</v>
       </c>
-      <c r="D153" s="5">
-        <v>540</v>
+      <c r="D153" s="7">
+        <f t="shared" si="12"/>
+        <v>360</v>
       </c>
       <c r="E153" s="6">
         <v>48</v>
       </c>
-      <c r="F153" s="8" t="s">
+      <c r="F153" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>30503005</v>
       </c>
-      <c r="B154" s="7">
+      <c r="B154" s="8">
         <v>305030</v>
       </c>
-      <c r="C154" s="7">
+      <c r="C154" s="8">
         <v>5</v>
       </c>
-      <c r="D154" s="5">
+      <c r="D154" s="7">
+        <f t="shared" si="12"/>
         <v>999999</v>
       </c>
       <c r="E154" s="6">
         <v>60</v>
       </c>
-      <c r="F154" s="8" t="s">
+      <c r="F154" s="9" t="s">
         <v>16</v>
       </c>
     </row>
